--- a/internacional/Contraste_fisica.xlsx
+++ b/internacional/Contraste_fisica.xlsx
@@ -765,7 +765,7 @@
         <v>9.5</v>
       </c>
       <c r="M5" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -836,6 +836,9 @@
       <c r="L6" t="n">
         <v>9.5</v>
       </c>
+      <c r="M6" t="n">
+        <v>7</v>
+      </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
@@ -1232,9 +1235,15 @@
       <c r="F13" t="n">
         <v>8</v>
       </c>
+      <c r="J13" t="n">
+        <v>7</v>
+      </c>
       <c r="K13" t="n">
         <v>9</v>
       </c>
+      <c r="M13" t="n">
+        <v>7</v>
+      </c>
       <c r="O13" t="n">
         <v>1</v>
       </c>
@@ -1268,9 +1277,15 @@
       <c r="G14" t="n">
         <v>6</v>
       </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
       <c r="K14" t="n">
         <v>9</v>
       </c>
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
@@ -1361,11 +1376,14 @@
       <c r="I16" t="n">
         <v>9.5</v>
       </c>
+      <c r="J16" t="n">
+        <v>7</v>
+      </c>
       <c r="L16" t="n">
         <v>9.5</v>
       </c>
       <c r="M16" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -1481,9 +1499,15 @@
       <c r="I18" t="n">
         <v>7</v>
       </c>
+      <c r="J18" t="n">
+        <v>7</v>
+      </c>
       <c r="L18" t="n">
         <v>9.5</v>
       </c>
+      <c r="M18" t="n">
+        <v>7</v>
+      </c>
       <c r="O18" t="n">
         <v>1</v>
       </c>
@@ -1601,12 +1625,18 @@
       <c r="I20" t="n">
         <v>6</v>
       </c>
+      <c r="J20" t="n">
+        <v>7</v>
+      </c>
       <c r="K20" t="n">
         <v>9</v>
       </c>
       <c r="L20" t="n">
         <v>9.5</v>
       </c>
+      <c r="M20" t="n">
+        <v>7</v>
+      </c>
       <c r="O20" t="n">
         <v>1</v>
       </c>
@@ -1652,11 +1682,14 @@
       <c r="F21" t="n">
         <v>8</v>
       </c>
+      <c r="J21" t="n">
+        <v>7</v>
+      </c>
       <c r="L21" t="n">
         <v>9.5</v>
       </c>
       <c r="M21" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -1718,9 +1751,18 @@
       <c r="I22" t="n">
         <v>7</v>
       </c>
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>8</v>
+      </c>
       <c r="L22" t="n">
         <v>9.5</v>
       </c>
+      <c r="M22" t="n">
+        <v>7</v>
+      </c>
       <c r="O22" t="n">
         <v>1</v>
       </c>
@@ -1931,6 +1973,9 @@
       <c r="K26" t="n">
         <v>9</v>
       </c>
+      <c r="M26" t="n">
+        <v>7</v>
+      </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
@@ -2241,7 +2286,7 @@
         <v>9.5</v>
       </c>
       <c r="M31" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
@@ -2297,6 +2342,9 @@
       <c r="G32" t="n">
         <v>8.5</v>
       </c>
+      <c r="M32" t="n">
+        <v>7</v>
+      </c>
       <c r="O32" t="n">
         <v>1</v>
       </c>
@@ -2403,7 +2451,7 @@
         <v>9.5</v>
       </c>
       <c r="J34" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L34" t="n">
         <v>11</v>
@@ -2531,6 +2579,9 @@
       <c r="I36" t="n">
         <v>9.5</v>
       </c>
+      <c r="J36" t="n">
+        <v>7</v>
+      </c>
       <c r="M36" t="n">
         <v>9.5</v>
       </c>
@@ -2607,7 +2658,7 @@
         <v>9.5</v>
       </c>
       <c r="M37" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="N37" t="n">
         <v>1</v>
@@ -2675,11 +2726,14 @@
       <c r="I38" t="n">
         <v>5</v>
       </c>
+      <c r="J38" t="n">
+        <v>7</v>
+      </c>
       <c r="L38" t="n">
         <v>9.5</v>
       </c>
       <c r="M38" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O38" t="n">
         <v>1</v>
@@ -2759,6 +2813,9 @@
       <c r="L40" t="n">
         <v>9.5</v>
       </c>
+      <c r="M40" t="n">
+        <v>7</v>
+      </c>
       <c r="P40" t="n">
         <v>1</v>
       </c>
@@ -2801,6 +2858,9 @@
       <c r="I41" t="n">
         <v>2</v>
       </c>
+      <c r="J41" t="n">
+        <v>7</v>
+      </c>
       <c r="L41" t="n">
         <v>9.5</v>
       </c>
@@ -2856,11 +2916,14 @@
         <v>9.5</v>
       </c>
       <c r="J42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L42" t="n">
         <v>9.5</v>
       </c>
+      <c r="M42" t="n">
+        <v>7</v>
+      </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
@@ -2918,6 +2981,9 @@
       <c r="L43" t="n">
         <v>11</v>
       </c>
+      <c r="M43" t="n">
+        <v>7</v>
+      </c>
       <c r="O43" t="n">
         <v>1</v>
       </c>
@@ -2973,7 +3039,7 @@
         <v>9.5</v>
       </c>
       <c r="J44" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L44" t="n">
         <v>9.5</v>
@@ -3044,9 +3110,15 @@
       <c r="I45" t="n">
         <v>2</v>
       </c>
+      <c r="J45" t="n">
+        <v>7</v>
+      </c>
       <c r="L45" t="n">
         <v>9.5</v>
       </c>
+      <c r="M45" t="n">
+        <v>7</v>
+      </c>
       <c r="O45" t="n">
         <v>1</v>
       </c>
@@ -3098,11 +3170,14 @@
       <c r="I46" t="n">
         <v>9.5</v>
       </c>
+      <c r="J46" t="n">
+        <v>7</v>
+      </c>
       <c r="L46" t="n">
         <v>9.5</v>
       </c>
       <c r="M46" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
@@ -3161,11 +3236,14 @@
       <c r="I47" t="n">
         <v>3</v>
       </c>
+      <c r="J47" t="n">
+        <v>7</v>
+      </c>
       <c r="L47" t="n">
         <v>9.5</v>
       </c>
       <c r="M47" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
@@ -3234,13 +3312,13 @@
         <v>7</v>
       </c>
       <c r="J48" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L48" t="n">
         <v>9.5</v>
       </c>
       <c r="M48" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O48" t="n">
         <v>1</v>
@@ -3308,6 +3386,12 @@
       <c r="G49" t="n">
         <v>8.5</v>
       </c>
+      <c r="J49" t="n">
+        <v>7</v>
+      </c>
+      <c r="M49" t="n">
+        <v>7</v>
+      </c>
       <c r="O49" t="n">
         <v>1</v>
       </c>
@@ -3359,11 +3443,17 @@
       <c r="I50" t="n">
         <v>7</v>
       </c>
+      <c r="J50" t="n">
+        <v>7</v>
+      </c>
+      <c r="K50" t="n">
+        <v>8</v>
+      </c>
       <c r="L50" t="n">
         <v>9.5</v>
       </c>
       <c r="M50" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O50" t="n">
         <v>1</v>
@@ -3428,9 +3518,18 @@
       <c r="I51" t="n">
         <v>2</v>
       </c>
+      <c r="J51" t="n">
+        <v>7</v>
+      </c>
+      <c r="K51" t="n">
+        <v>8</v>
+      </c>
       <c r="L51" t="n">
         <v>9.5</v>
       </c>
+      <c r="M51" t="n">
+        <v>7</v>
+      </c>
       <c r="O51" t="n">
         <v>1</v>
       </c>
@@ -3488,6 +3587,12 @@
       <c r="I52" t="n">
         <v>3</v>
       </c>
+      <c r="J52" t="n">
+        <v>7</v>
+      </c>
+      <c r="K52" t="n">
+        <v>8</v>
+      </c>
       <c r="L52" t="n">
         <v>9.5</v>
       </c>
@@ -3603,11 +3708,14 @@
         <v>6</v>
       </c>
       <c r="J54" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K54" t="n">
         <v>9</v>
       </c>
+      <c r="M54" t="n">
+        <v>7</v>
+      </c>
       <c r="O54" t="n">
         <v>1</v>
       </c>
@@ -3660,11 +3768,17 @@
         <v>2</v>
       </c>
       <c r="J55" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K55" t="n">
+        <v>8</v>
       </c>
       <c r="L55" t="n">
         <v>9.5</v>
       </c>
+      <c r="M55" t="n">
+        <v>7</v>
+      </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
@@ -3719,9 +3833,15 @@
       <c r="I56" t="n">
         <v>8</v>
       </c>
+      <c r="J56" t="n">
+        <v>7</v>
+      </c>
       <c r="L56" t="n">
         <v>9.5</v>
       </c>
+      <c r="M56" t="n">
+        <v>7</v>
+      </c>
       <c r="O56" t="n">
         <v>1</v>
       </c>
@@ -3842,11 +3962,17 @@
       <c r="I58" t="n">
         <v>3</v>
       </c>
+      <c r="J58" t="n">
+        <v>7</v>
+      </c>
+      <c r="K58" t="n">
+        <v>8</v>
+      </c>
       <c r="L58" t="n">
         <v>9.5</v>
       </c>
       <c r="M58" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
@@ -3915,7 +4041,10 @@
         <v>10</v>
       </c>
       <c r="J59" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K59" t="n">
+        <v>8</v>
       </c>
       <c r="M59" t="n">
         <v>9.5</v>
@@ -3986,9 +4115,15 @@
       <c r="I60" t="n">
         <v>2</v>
       </c>
+      <c r="J60" t="n">
+        <v>7</v>
+      </c>
       <c r="L60" t="n">
         <v>9.5</v>
       </c>
+      <c r="M60" t="n">
+        <v>7</v>
+      </c>
       <c r="O60" t="n">
         <v>1</v>
       </c>
@@ -4034,9 +4169,15 @@
       <c r="I61" t="n">
         <v>3</v>
       </c>
+      <c r="J61" t="n">
+        <v>7</v>
+      </c>
       <c r="L61" t="n">
         <v>9.5</v>
       </c>
+      <c r="M61" t="n">
+        <v>7</v>
+      </c>
       <c r="O61" t="n">
         <v>1</v>
       </c>
@@ -4098,13 +4239,16 @@
         <v>8</v>
       </c>
       <c r="J63" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K63" t="n">
+        <v>8</v>
       </c>
       <c r="L63" t="n">
         <v>9.5</v>
       </c>
       <c r="M63" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
@@ -4169,9 +4313,15 @@
       <c r="I64" t="n">
         <v>4</v>
       </c>
+      <c r="J64" t="n">
+        <v>7</v>
+      </c>
       <c r="L64" t="n">
         <v>9.5</v>
       </c>
+      <c r="M64" t="n">
+        <v>7</v>
+      </c>
       <c r="O64" t="n">
         <v>1</v>
       </c>
@@ -4236,13 +4386,13 @@
         <v>8</v>
       </c>
       <c r="J65" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L65" t="n">
         <v>9.5</v>
       </c>
       <c r="M65" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="P65" t="n">
         <v>1</v>
@@ -4310,9 +4460,15 @@
       <c r="I66" t="n">
         <v>8</v>
       </c>
+      <c r="J66" t="n">
+        <v>7</v>
+      </c>
       <c r="L66" t="n">
         <v>9.5</v>
       </c>
+      <c r="M66" t="n">
+        <v>7</v>
+      </c>
       <c r="P66" t="n">
         <v>1</v>
       </c>
@@ -4370,11 +4526,14 @@
       <c r="G67" t="n">
         <v>6</v>
       </c>
+      <c r="J67" t="n">
+        <v>7</v>
+      </c>
       <c r="L67" t="n">
         <v>9.5</v>
       </c>
       <c r="M67" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O67" t="n">
         <v>1</v>
@@ -4427,9 +4586,15 @@
       <c r="I68" t="n">
         <v>6</v>
       </c>
+      <c r="J68" t="n">
+        <v>7</v>
+      </c>
       <c r="L68" t="n">
         <v>9.5</v>
       </c>
+      <c r="M68" t="n">
+        <v>7</v>
+      </c>
       <c r="P68" t="n">
         <v>1</v>
       </c>
@@ -4484,9 +4649,15 @@
       <c r="I69" t="n">
         <v>3</v>
       </c>
+      <c r="J69" t="n">
+        <v>7</v>
+      </c>
       <c r="L69" t="n">
         <v>9.5</v>
       </c>
+      <c r="M69" t="n">
+        <v>7</v>
+      </c>
       <c r="O69" t="n">
         <v>1</v>
       </c>
@@ -4541,6 +4712,9 @@
       <c r="G70" t="n">
         <v>6</v>
       </c>
+      <c r="M70" t="n">
+        <v>7</v>
+      </c>
       <c r="O70" t="n">
         <v>1</v>
       </c>
@@ -4577,11 +4751,14 @@
       <c r="I71" t="n">
         <v>5</v>
       </c>
+      <c r="J71" t="n">
+        <v>7</v>
+      </c>
       <c r="L71" t="n">
         <v>9.5</v>
       </c>
       <c r="M71" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O71" t="n">
         <v>1</v>
@@ -4643,8 +4820,11 @@
       <c r="J72" t="n">
         <v>9</v>
       </c>
+      <c r="K72" t="n">
+        <v>8</v>
+      </c>
       <c r="M72" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -4709,6 +4889,9 @@
       <c r="I73" t="n">
         <v>2</v>
       </c>
+      <c r="J73" t="n">
+        <v>7</v>
+      </c>
       <c r="L73" t="n">
         <v>11</v>
       </c>
@@ -4781,6 +4964,9 @@
       <c r="L74" t="n">
         <v>9.5</v>
       </c>
+      <c r="M74" t="n">
+        <v>7</v>
+      </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
@@ -4829,9 +5015,15 @@
       <c r="I75" t="n">
         <v>6</v>
       </c>
+      <c r="J75" t="n">
+        <v>7</v>
+      </c>
       <c r="L75" t="n">
         <v>9.5</v>
       </c>
+      <c r="M75" t="n">
+        <v>7</v>
+      </c>
       <c r="N75" t="n">
         <v>1</v>
       </c>
@@ -4955,11 +5147,14 @@
       <c r="I77" t="n">
         <v>9.5</v>
       </c>
+      <c r="J77" t="n">
+        <v>7</v>
+      </c>
       <c r="L77" t="n">
         <v>9.5</v>
       </c>
       <c r="M77" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O77" t="n">
         <v>1</v>
@@ -5009,6 +5204,9 @@
       <c r="I78" t="n">
         <v>9.5</v>
       </c>
+      <c r="J78" t="n">
+        <v>7</v>
+      </c>
       <c r="L78" t="n">
         <v>9.5</v>
       </c>
@@ -5076,11 +5274,14 @@
         <v>9.5</v>
       </c>
       <c r="J79" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L79" t="n">
         <v>9.5</v>
       </c>
+      <c r="M79" t="n">
+        <v>7</v>
+      </c>
       <c r="O79" t="n">
         <v>1</v>
       </c>
@@ -5142,7 +5343,7 @@
         <v>9.5</v>
       </c>
       <c r="M80" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O80" t="n">
         <v>1</v>
@@ -5262,7 +5463,7 @@
         <v>9</v>
       </c>
       <c r="M82" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O82" t="n">
         <v>1</v>
@@ -5426,11 +5627,14 @@
       <c r="I85" t="n">
         <v>9.5</v>
       </c>
+      <c r="J85" t="n">
+        <v>7</v>
+      </c>
       <c r="L85" t="n">
         <v>9.5</v>
       </c>
       <c r="M85" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O85" t="n">
         <v>1</v>
@@ -5498,9 +5702,15 @@
       <c r="I86" t="n">
         <v>5</v>
       </c>
+      <c r="J86" t="n">
+        <v>7</v>
+      </c>
       <c r="L86" t="n">
         <v>9.5</v>
       </c>
+      <c r="M86" t="n">
+        <v>7</v>
+      </c>
       <c r="O86" t="n">
         <v>1</v>
       </c>
@@ -5540,6 +5750,9 @@
       <c r="L87" t="n">
         <v>9.5</v>
       </c>
+      <c r="M87" t="n">
+        <v>7</v>
+      </c>
       <c r="O87" t="n">
         <v>1</v>
       </c>
@@ -5648,9 +5861,15 @@
       <c r="I89" t="n">
         <v>3</v>
       </c>
+      <c r="J89" t="n">
+        <v>7</v>
+      </c>
       <c r="L89" t="n">
         <v>9.5</v>
       </c>
+      <c r="M89" t="n">
+        <v>7</v>
+      </c>
       <c r="O89" t="n">
         <v>1</v>
       </c>
@@ -5718,7 +5937,7 @@
         <v>9.5</v>
       </c>
       <c r="M90" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O90" t="n">
         <v>1</v>
@@ -5789,11 +6008,17 @@
       <c r="I91" t="n">
         <v>9.5</v>
       </c>
+      <c r="J91" t="n">
+        <v>7</v>
+      </c>
+      <c r="K91" t="n">
+        <v>8</v>
+      </c>
       <c r="L91" t="n">
         <v>9.5</v>
       </c>
       <c r="M91" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O91" t="n">
         <v>1</v>
@@ -5975,6 +6200,9 @@
       <c r="L94" t="n">
         <v>11</v>
       </c>
+      <c r="M94" t="n">
+        <v>7</v>
+      </c>
       <c r="O94" t="n">
         <v>1</v>
       </c>
@@ -6101,6 +6329,9 @@
       <c r="I96" t="n">
         <v>8</v>
       </c>
+      <c r="J96" t="n">
+        <v>7</v>
+      </c>
       <c r="L96" t="n">
         <v>9.5</v>
       </c>
@@ -6239,6 +6470,9 @@
       <c r="I98" t="n">
         <v>9.5</v>
       </c>
+      <c r="M98" t="n">
+        <v>7</v>
+      </c>
       <c r="O98" t="n">
         <v>1</v>
       </c>
@@ -6297,7 +6531,7 @@
         <v>9.5</v>
       </c>
       <c r="M99" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="P99" t="n">
         <v>1</v>
@@ -6428,6 +6662,9 @@
       <c r="I101" t="n">
         <v>4</v>
       </c>
+      <c r="J101" t="n">
+        <v>7</v>
+      </c>
       <c r="O101" t="n">
         <v>1</v>
       </c>
@@ -6473,6 +6710,9 @@
       <c r="L102" t="n">
         <v>9.5</v>
       </c>
+      <c r="M102" t="n">
+        <v>7</v>
+      </c>
       <c r="O102" t="n">
         <v>1</v>
       </c>
@@ -6530,11 +6770,17 @@
       <c r="I103" t="n">
         <v>7</v>
       </c>
+      <c r="J103" t="n">
+        <v>7</v>
+      </c>
+      <c r="K103" t="n">
+        <v>8</v>
+      </c>
       <c r="L103" t="n">
         <v>9.5</v>
       </c>
       <c r="M103" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O103" t="n">
         <v>1</v>
@@ -6605,6 +6851,9 @@
       <c r="L104" t="n">
         <v>9.5</v>
       </c>
+      <c r="M104" t="n">
+        <v>7</v>
+      </c>
       <c r="O104" t="n">
         <v>1</v>
       </c>
@@ -6659,6 +6908,9 @@
       <c r="L105" t="n">
         <v>9.5</v>
       </c>
+      <c r="M105" t="n">
+        <v>7</v>
+      </c>
       <c r="O105" t="n">
         <v>1</v>
       </c>
@@ -6707,6 +6959,9 @@
       <c r="I106" t="n">
         <v>7</v>
       </c>
+      <c r="M106" t="n">
+        <v>7</v>
+      </c>
       <c r="O106" t="n">
         <v>1</v>
       </c>
@@ -6750,13 +7005,13 @@
         <v>8</v>
       </c>
       <c r="J107" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L107" t="n">
         <v>9.5</v>
       </c>
       <c r="M107" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="N107" t="n">
         <v>1</v>
@@ -6827,6 +7082,12 @@
       <c r="I108" t="n">
         <v>8</v>
       </c>
+      <c r="J108" t="n">
+        <v>7</v>
+      </c>
+      <c r="M108" t="n">
+        <v>7</v>
+      </c>
       <c r="O108" t="n">
         <v>1</v>
       </c>
@@ -6887,6 +7148,9 @@
       <c r="F110" t="n">
         <v>8</v>
       </c>
+      <c r="M110" t="n">
+        <v>7</v>
+      </c>
       <c r="O110" t="n">
         <v>1</v>
       </c>
@@ -6924,11 +7188,14 @@
         <v>2</v>
       </c>
       <c r="J111" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K111" t="n">
         <v>9</v>
       </c>
+      <c r="M111" t="n">
+        <v>7</v>
+      </c>
       <c r="O111" t="n">
         <v>1</v>
       </c>
@@ -6980,9 +7247,15 @@
       <c r="I112" t="n">
         <v>8</v>
       </c>
+      <c r="J112" t="n">
+        <v>7</v>
+      </c>
       <c r="L112" t="n">
         <v>9.5</v>
       </c>
+      <c r="M112" t="n">
+        <v>7</v>
+      </c>
       <c r="O112" t="n">
         <v>1</v>
       </c>
@@ -7046,6 +7319,9 @@
       <c r="I113" t="n">
         <v>2</v>
       </c>
+      <c r="J113" t="n">
+        <v>7</v>
+      </c>
       <c r="K113" t="n">
         <v>9</v>
       </c>
@@ -7053,7 +7329,7 @@
         <v>9.5</v>
       </c>
       <c r="M113" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O113" t="n">
         <v>1</v>
@@ -7119,7 +7395,7 @@
         <v>6</v>
       </c>
       <c r="J114" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K114" t="n">
         <v>9</v>
@@ -7128,7 +7404,7 @@
         <v>9.5</v>
       </c>
       <c r="M114" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O114" t="n">
         <v>1</v>
@@ -7193,6 +7469,9 @@
       <c r="G115" t="n">
         <v>8.5</v>
       </c>
+      <c r="J115" t="n">
+        <v>7</v>
+      </c>
       <c r="L115" t="n">
         <v>9.5</v>
       </c>
@@ -7251,13 +7530,13 @@
         <v>8</v>
       </c>
       <c r="J116" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L116" t="n">
         <v>9.5</v>
       </c>
       <c r="M116" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="N116" t="n">
         <v>1</v>
@@ -7332,13 +7611,13 @@
         <v>9</v>
       </c>
       <c r="K117" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L117" t="n">
         <v>9.5</v>
       </c>
       <c r="M117" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O117" t="n">
         <v>1</v>
@@ -7403,11 +7682,14 @@
       <c r="I118" t="n">
         <v>6</v>
       </c>
+      <c r="J118" t="n">
+        <v>7</v>
+      </c>
       <c r="L118" t="n">
         <v>9.5</v>
       </c>
       <c r="M118" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O118" t="n">
         <v>1</v>
@@ -7478,6 +7760,9 @@
       <c r="I119" t="n">
         <v>8</v>
       </c>
+      <c r="J119" t="n">
+        <v>7</v>
+      </c>
       <c r="L119" t="n">
         <v>9.5</v>
       </c>
@@ -7545,7 +7830,7 @@
         <v>9.5</v>
       </c>
       <c r="J120" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M120" t="n">
         <v>9.5</v>
@@ -7635,7 +7920,7 @@
         <v>9.5</v>
       </c>
       <c r="M122" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="N122" t="n">
         <v>1</v>
@@ -7703,9 +7988,15 @@
       <c r="I123" t="n">
         <v>2</v>
       </c>
+      <c r="J123" t="n">
+        <v>7</v>
+      </c>
       <c r="L123" t="n">
         <v>9.5</v>
       </c>
+      <c r="M123" t="n">
+        <v>7</v>
+      </c>
       <c r="O123" t="n">
         <v>1</v>
       </c>
@@ -7757,6 +8048,9 @@
       <c r="L124" t="n">
         <v>9.5</v>
       </c>
+      <c r="M124" t="n">
+        <v>7</v>
+      </c>
       <c r="P124" t="n">
         <v>1</v>
       </c>
@@ -7808,11 +8102,14 @@
       <c r="I125" t="n">
         <v>8</v>
       </c>
+      <c r="J125" t="n">
+        <v>7</v>
+      </c>
       <c r="L125" t="n">
         <v>9.5</v>
       </c>
       <c r="M125" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O125" t="n">
         <v>1</v>
@@ -7881,13 +8178,16 @@
         <v>5</v>
       </c>
       <c r="J126" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K126" t="n">
+        <v>8</v>
       </c>
       <c r="L126" t="n">
         <v>9.5</v>
       </c>
       <c r="M126" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O126" t="n">
         <v>1</v>
@@ -7955,6 +8255,9 @@
       <c r="I127" t="n">
         <v>5</v>
       </c>
+      <c r="M127" t="n">
+        <v>7</v>
+      </c>
       <c r="O127" t="n">
         <v>1</v>
       </c>
@@ -8342,6 +8645,9 @@
       <c r="D138" t="n">
         <v>10</v>
       </c>
+      <c r="J138" t="n">
+        <v>7</v>
+      </c>
       <c r="L138" t="n">
         <v>9.5</v>
       </c>
@@ -8463,7 +8769,7 @@
         <v>11</v>
       </c>
       <c r="M141" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O141" t="n">
         <v>1</v>

--- a/internacional/Contraste_fisica.xlsx
+++ b/internacional/Contraste_fisica.xlsx
@@ -2625,109 +2625,49 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Absorción de radiación y efecto invernadero</t>
+          <t>Materiales opacos, transparentes y translúcidos</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
-      </c>
-      <c r="E37" t="n">
-        <v>9</v>
-      </c>
-      <c r="F37" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I37" t="n">
-        <v>10</v>
-      </c>
-      <c r="J37" t="n">
-        <v>9</v>
-      </c>
-      <c r="K37" t="n">
-        <v>9</v>
-      </c>
-      <c r="L37" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M37" t="n">
-        <v>7</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
       </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1</v>
-      </c>
       <c r="Y37" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC37" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>La energía y sus usos</t>
+          <t>Movimiento, reposo y tipos de trayectoria</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>2</v>
       </c>
-      <c r="F38" t="n">
-        <v>8</v>
+      <c r="E38" t="n">
+        <v>2</v>
       </c>
       <c r="G38" t="n">
+        <v>6</v>
+      </c>
+      <c r="I38" t="n">
         <v>2</v>
-      </c>
-      <c r="I38" t="n">
-        <v>5</v>
-      </c>
-      <c r="J38" t="n">
-        <v>7</v>
       </c>
       <c r="L38" t="n">
         <v>9.5</v>
@@ -2735,38 +2675,26 @@
       <c r="M38" t="n">
         <v>7</v>
       </c>
-      <c r="O38" t="n">
-        <v>1</v>
-      </c>
       <c r="P38" t="n">
         <v>1</v>
       </c>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
       <c r="U38" t="n">
         <v>1</v>
       </c>
-      <c r="V38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1</v>
-      </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
-      <c r="AB38" t="n">
-        <v>1</v>
-      </c>
       <c r="AC38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Materiales opacos, transparentes y translúcidos</t>
+          <t>El sonido se produce por vibraciones</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2777,38 +2705,80 @@
       <c r="C39" t="n">
         <v>2</v>
       </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8</v>
+      </c>
       <c r="G39" t="n">
         <v>2</v>
       </c>
-      <c r="P39" t="n">
+      <c r="I39" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>7</v>
+      </c>
+      <c r="L39" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
         <v>1</v>
       </c>
       <c r="Y39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Movimiento, reposo y tipos de trayectoria</t>
+          <t>Absorción de radiación y efecto invernadero</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="F40" t="n">
+        <v>10.5</v>
       </c>
       <c r="G40" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="J40" t="n">
+        <v>9</v>
+      </c>
+      <c r="K40" t="n">
+        <v>9</v>
       </c>
       <c r="L40" t="n">
         <v>9.5</v>
@@ -2816,47 +2786,74 @@
       <c r="M40" t="n">
         <v>7</v>
       </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
       <c r="P40" t="n">
         <v>1</v>
       </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
       <c r="U40" t="n">
         <v>1</v>
       </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1</v>
+      </c>
       <c r="Z40" t="n">
         <v>1</v>
       </c>
+      <c r="AB40" t="n">
+        <v>1</v>
+      </c>
       <c r="AC40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD40" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>El sonido se produce por vibraciones</t>
+          <t>Aceleración</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E41" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
       </c>
       <c r="F41" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="J41" t="n">
         <v>7</v>
@@ -2864,12 +2861,27 @@
       <c r="L41" t="n">
         <v>9.5</v>
       </c>
+      <c r="M41" t="n">
+        <v>7</v>
+      </c>
       <c r="O41" t="n">
         <v>1</v>
       </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
       <c r="U41" t="n">
         <v>1</v>
       </c>
+      <c r="W41" t="n">
+        <v>1</v>
+      </c>
       <c r="Y41" t="n">
         <v>1</v>
       </c>
@@ -2883,16 +2895,13 @@
         <v>1</v>
       </c>
       <c r="AD41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE41" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Aceleración</t>
+          <t>Aceleración y fuerza centrípeta</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2909,17 +2918,8 @@
       <c r="F42" t="n">
         <v>10.5</v>
       </c>
-      <c r="G42" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I42" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J42" t="n">
-        <v>7</v>
-      </c>
       <c r="L42" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="M42" t="n">
         <v>7</v>
@@ -2927,15 +2927,6 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="P42" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1</v>
-      </c>
       <c r="U42" t="n">
         <v>1</v>
       </c>
@@ -2948,6 +2939,9 @@
       <c r="Z42" t="n">
         <v>1</v>
       </c>
+      <c r="AA42" t="n">
+        <v>1</v>
+      </c>
       <c r="AB42" t="n">
         <v>1</v>
       </c>
@@ -2955,13 +2949,16 @@
         <v>1</v>
       </c>
       <c r="AD42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE42" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Aceleración y fuerza centrípeta</t>
+          <t>Caída libre</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2975,21 +2972,36 @@
       <c r="D43" t="n">
         <v>10</v>
       </c>
-      <c r="F43" t="n">
-        <v>10.5</v>
+      <c r="G43" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I43" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>7</v>
       </c>
       <c r="L43" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M43" t="n">
-        <v>7</v>
-      </c>
-      <c r="O43" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
+      <c r="S43" t="n">
         <v>1</v>
       </c>
       <c r="U43" t="n">
         <v>1</v>
       </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
       <c r="W43" t="n">
         <v>1</v>
       </c>
@@ -2997,12 +3009,6 @@
         <v>1</v>
       </c>
       <c r="Z43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB43" t="n">
         <v>1</v>
       </c>
       <c r="AC43" t="n">
@@ -3018,7 +3024,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Caída libre</t>
+          <t>Calentamiento y enfriamiento</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3027,16 +3033,22 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
         <v>10</v>
       </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="n">
+        <v>8</v>
+      </c>
       <c r="G44" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>9.5</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>7</v>
@@ -3045,23 +3057,17 @@
         <v>9.5</v>
       </c>
       <c r="M44" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
-      <c r="R44" t="n">
-        <v>1</v>
-      </c>
-      <c r="S44" t="n">
-        <v>1</v>
-      </c>
       <c r="U44" t="n">
         <v>1</v>
       </c>
-      <c r="V44" t="n">
-        <v>1</v>
-      </c>
       <c r="W44" t="n">
         <v>1</v>
       </c>
@@ -3071,20 +3077,17 @@
       <c r="Z44" t="n">
         <v>1</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AB44" t="n">
         <v>1</v>
       </c>
       <c r="AD44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE44" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Calentamiento y enfriamiento</t>
+          <t>Calor como energía en tránsito</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3093,13 +3096,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F45" t="n">
         <v>8</v>
@@ -3108,7 +3108,7 @@
         <v>6</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="J45" t="n">
         <v>7</v>
@@ -3125,7 +3125,13 @@
       <c r="P45" t="n">
         <v>1</v>
       </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
       <c r="U45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" t="n">
         <v>1</v>
       </c>
       <c r="W45" t="n">
@@ -3147,7 +3153,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Calor como energía en tránsito</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3156,7 +3162,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
         <v>9</v>
@@ -3168,7 +3174,7 @@
         <v>6</v>
       </c>
       <c r="I46" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
         <v>7</v>
@@ -3197,13 +3203,22 @@
       <c r="W46" t="n">
         <v>1</v>
       </c>
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
       <c r="Y46" t="n">
         <v>1</v>
       </c>
       <c r="Z46" t="n">
         <v>1</v>
       </c>
+      <c r="AA46" t="n">
+        <v>1</v>
+      </c>
       <c r="AB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC46" t="n">
         <v>1</v>
       </c>
       <c r="AD46" t="n">
@@ -3213,7 +3228,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Campo magnético y magnetismo terrestre</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3222,7 +3237,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
         <v>9</v>
@@ -3234,7 +3249,7 @@
         <v>6</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J47" t="n">
         <v>7</v>
@@ -3254,6 +3269,9 @@
       <c r="R47" t="n">
         <v>1</v>
       </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
       <c r="U47" t="n">
         <v>1</v>
       </c>
@@ -3263,9 +3281,6 @@
       <c r="W47" t="n">
         <v>1</v>
       </c>
-      <c r="X47" t="n">
-        <v>1</v>
-      </c>
       <c r="Y47" t="n">
         <v>1</v>
       </c>
@@ -3282,13 +3297,16 @@
         <v>1</v>
       </c>
       <c r="AD47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE47" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Campo magnético y magnetismo terrestre</t>
+          <t>Capacidad calorífica y calor específico</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3297,7 +3315,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
         <v>9</v>
@@ -3306,17 +3324,11 @@
         <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
-      </c>
-      <c r="I48" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="J48" t="n">
         <v>7</v>
       </c>
-      <c r="L48" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M48" t="n">
         <v>7</v>
       </c>
@@ -3326,18 +3338,6 @@
       <c r="P48" t="n">
         <v>1</v>
       </c>
-      <c r="R48" t="n">
-        <v>1</v>
-      </c>
-      <c r="S48" t="n">
-        <v>1</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1</v>
-      </c>
       <c r="W48" t="n">
         <v>1</v>
       </c>
@@ -3347,9 +3347,6 @@
       <c r="Z48" t="n">
         <v>1</v>
       </c>
-      <c r="AA48" t="n">
-        <v>1</v>
-      </c>
       <c r="AB48" t="n">
         <v>1</v>
       </c>
@@ -3357,16 +3354,13 @@
         <v>1</v>
       </c>
       <c r="AD48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Capacidad calorífica y calor específico</t>
+          <t>Carga eléctrica y electrización</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3375,7 +3369,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
         <v>9</v>
@@ -3384,11 +3378,20 @@
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="I49" t="n">
+        <v>7</v>
       </c>
       <c r="J49" t="n">
         <v>7</v>
       </c>
+      <c r="K49" t="n">
+        <v>8</v>
+      </c>
+      <c r="L49" t="n">
+        <v>9.5</v>
+      </c>
       <c r="M49" t="n">
         <v>7</v>
       </c>
@@ -3398,6 +3401,12 @@
       <c r="P49" t="n">
         <v>1</v>
       </c>
+      <c r="U49" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
       <c r="W49" t="n">
         <v>1</v>
       </c>
@@ -3407,20 +3416,23 @@
       <c r="Z49" t="n">
         <v>1</v>
       </c>
+      <c r="AA49" t="n">
+        <v>1</v>
+      </c>
       <c r="AB49" t="n">
         <v>1</v>
       </c>
-      <c r="AC49" t="n">
-        <v>1</v>
-      </c>
       <c r="AD49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE49" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Carga eléctrica y electrización</t>
+          <t>Circuito eléctrico simple</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3429,19 +3441,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
         <v>9</v>
       </c>
+      <c r="E50" t="n">
+        <v>5</v>
+      </c>
       <c r="F50" t="n">
         <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>7</v>
@@ -3464,9 +3479,6 @@
       <c r="U50" t="n">
         <v>1</v>
       </c>
-      <c r="V50" t="n">
-        <v>1</v>
-      </c>
       <c r="W50" t="n">
         <v>1</v>
       </c>
@@ -3476,10 +3488,10 @@
       <c r="Z50" t="n">
         <v>1</v>
       </c>
-      <c r="AA50" t="n">
-        <v>1</v>
-      </c>
       <c r="AB50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC50" t="n">
         <v>1</v>
       </c>
       <c r="AD50" t="n">
@@ -3492,7 +3504,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Circuito eléctrico simple</t>
+          <t>Circuitos en serie y en paralelo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3501,22 +3513,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
         <v>9</v>
       </c>
-      <c r="E51" t="n">
-        <v>5</v>
-      </c>
       <c r="F51" t="n">
         <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J51" t="n">
         <v>7</v>
@@ -3527,9 +3536,6 @@
       <c r="L51" t="n">
         <v>9.5</v>
       </c>
-      <c r="M51" t="n">
-        <v>7</v>
-      </c>
       <c r="O51" t="n">
         <v>1</v>
       </c>
@@ -3549,9 +3555,6 @@
         <v>1</v>
       </c>
       <c r="AB51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC51" t="n">
         <v>1</v>
       </c>
       <c r="AD51" t="n">
@@ -3564,7 +3567,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Circuitos en serie y en paralelo</t>
+          <t>Colisiones elásticas e inelásticas</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3573,35 +3576,26 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="G52" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J52" t="n">
         <v>9</v>
       </c>
-      <c r="F52" t="n">
-        <v>8</v>
-      </c>
-      <c r="G52" t="n">
-        <v>6</v>
-      </c>
-      <c r="I52" t="n">
-        <v>3</v>
-      </c>
-      <c r="J52" t="n">
-        <v>7</v>
-      </c>
-      <c r="K52" t="n">
-        <v>8</v>
-      </c>
       <c r="L52" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O52" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
       </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
       <c r="U52" t="n">
         <v>1</v>
       </c>
@@ -3614,7 +3608,13 @@
       <c r="Z52" t="n">
         <v>1</v>
       </c>
+      <c r="AA52" t="n">
+        <v>1</v>
+      </c>
       <c r="AB52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC52" t="n">
         <v>1</v>
       </c>
       <c r="AD52" t="n">
@@ -3627,7 +3627,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Colisiones elásticas e inelásticas</t>
+          <t>Color y dispersión de la luz</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3636,30 +3636,33 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
         <v>10</v>
       </c>
+      <c r="F53" t="n">
+        <v>8</v>
+      </c>
       <c r="G53" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
+        <v>7</v>
+      </c>
+      <c r="K53" t="n">
         <v>9</v>
       </c>
-      <c r="L53" t="n">
-        <v>11</v>
-      </c>
-      <c r="P53" t="n">
+      <c r="M53" t="n">
+        <v>7</v>
+      </c>
+      <c r="O53" t="n">
         <v>1</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
       </c>
-      <c r="U53" t="n">
-        <v>1</v>
-      </c>
-      <c r="W53" t="n">
+      <c r="T53" t="n">
         <v>1</v>
       </c>
       <c r="Y53" t="n">
@@ -3668,26 +3671,17 @@
       <c r="Z53" t="n">
         <v>1</v>
       </c>
-      <c r="AA53" t="n">
-        <v>1</v>
-      </c>
       <c r="AB53" t="n">
         <v>1</v>
       </c>
       <c r="AC53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE53" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Color y dispersión de la luz</t>
+          <t>Conductores y aislantes eléctricos</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,22 +3690,31 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
         <v>10</v>
       </c>
+      <c r="E54" t="n">
+        <v>5</v>
+      </c>
       <c r="F54" t="n">
         <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>7</v>
       </c>
       <c r="K54" t="n">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="L54" t="n">
+        <v>9.5</v>
       </c>
       <c r="M54" t="n">
         <v>7</v>
@@ -3719,10 +3722,16 @@
       <c r="O54" t="n">
         <v>1</v>
       </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
       <c r="S54" t="n">
         <v>1</v>
       </c>
-      <c r="T54" t="n">
+      <c r="U54" t="n">
+        <v>1</v>
+      </c>
+      <c r="X54" t="n">
         <v>1</v>
       </c>
       <c r="Y54" t="n">
@@ -3734,14 +3743,14 @@
       <c r="AB54" t="n">
         <v>1</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AD54" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Conductores y aislantes eléctricos</t>
+          <t>Conservación de la energía mecánica</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3750,28 +3759,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F55" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I55" t="n">
         <v>8</v>
       </c>
-      <c r="G55" t="n">
-        <v>2</v>
-      </c>
-      <c r="I55" t="n">
-        <v>2</v>
-      </c>
       <c r="J55" t="n">
         <v>7</v>
-      </c>
-      <c r="K55" t="n">
-        <v>8</v>
       </c>
       <c r="L55" t="n">
         <v>9.5</v>
@@ -3782,35 +3785,41 @@
       <c r="O55" t="n">
         <v>1</v>
       </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
       <c r="R55" t="n">
         <v>1</v>
       </c>
-      <c r="S55" t="n">
-        <v>1</v>
-      </c>
       <c r="U55" t="n">
         <v>1</v>
       </c>
-      <c r="X55" t="n">
-        <v>1</v>
-      </c>
       <c r="Y55" t="n">
         <v>1</v>
       </c>
       <c r="Z55" t="n">
         <v>1</v>
       </c>
+      <c r="AA55" t="n">
+        <v>1</v>
+      </c>
       <c r="AB55" t="n">
         <v>1</v>
       </c>
+      <c r="AC55" t="n">
+        <v>1</v>
+      </c>
       <c r="AD55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE55" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Conservación de la energía mecánica</t>
+          <t>Conservación del momento lineal</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3819,10 +3828,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>10.5</v>
@@ -3830,17 +3839,8 @@
       <c r="G56" t="n">
         <v>8.5</v>
       </c>
-      <c r="I56" t="n">
-        <v>8</v>
-      </c>
-      <c r="J56" t="n">
-        <v>7</v>
-      </c>
       <c r="L56" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M56" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
@@ -3848,10 +3848,10 @@
       <c r="P56" t="n">
         <v>1</v>
       </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
       <c r="U56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>1</v>
       </c>
       <c r="Y56" t="n">
@@ -3879,7 +3879,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Conservación del momento lineal</t>
+          <t>Corriente, voltaje y resistencia</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3888,19 +3888,31 @@
         </is>
       </c>
       <c r="C57" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" t="n">
+        <v>9</v>
+      </c>
+      <c r="F57" t="n">
         <v>8</v>
       </c>
-      <c r="D57" t="n">
-        <v>10</v>
-      </c>
-      <c r="F57" t="n">
-        <v>10.5</v>
-      </c>
       <c r="G57" t="n">
-        <v>8.5</v>
+        <v>4</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" t="n">
+        <v>7</v>
+      </c>
+      <c r="K57" t="n">
+        <v>8</v>
       </c>
       <c r="L57" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M57" t="n">
+        <v>7</v>
       </c>
       <c r="O57" t="n">
         <v>1</v>
@@ -3908,7 +3920,13 @@
       <c r="P57" t="n">
         <v>1</v>
       </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
       <c r="U57" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" t="n">
         <v>1</v>
       </c>
       <c r="W57" t="n">
@@ -3939,7 +3957,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Corriente, voltaje y resistencia</t>
+          <t>Expansión del universo y Big Bang</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3948,19 +3966,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D58" t="n">
+        <v>11</v>
+      </c>
+      <c r="E58" t="n">
         <v>9</v>
       </c>
       <c r="F58" t="n">
-        <v>8</v>
-      </c>
-      <c r="G58" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J58" t="n">
         <v>7</v>
@@ -3968,22 +3986,19 @@
       <c r="K58" t="n">
         <v>8</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>9.5</v>
       </c>
-      <c r="M58" t="n">
-        <v>7</v>
+      <c r="N58" t="n">
+        <v>1</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="P58" t="n">
-        <v>1</v>
-      </c>
       <c r="R58" t="n">
         <v>1</v>
       </c>
-      <c r="U58" t="n">
+      <c r="S58" t="n">
         <v>1</v>
       </c>
       <c r="V58" t="n">
@@ -3992,6 +4007,9 @@
       <c r="W58" t="n">
         <v>1</v>
       </c>
+      <c r="X58" t="n">
+        <v>1</v>
+      </c>
       <c r="Y58" t="n">
         <v>1</v>
       </c>
@@ -4008,16 +4026,13 @@
         <v>1</v>
       </c>
       <c r="AD58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE58" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Expansión del universo y Big Bang</t>
+          <t>Densidad</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4026,63 +4041,42 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>11</v>
-      </c>
-      <c r="E59" t="n">
         <v>9</v>
       </c>
       <c r="F59" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G59" t="n">
+        <v>6</v>
       </c>
       <c r="I59" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>7</v>
       </c>
-      <c r="K59" t="n">
-        <v>8</v>
+      <c r="L59" t="n">
+        <v>9.5</v>
       </c>
       <c r="M59" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N59" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O59" t="n">
         <v>1</v>
       </c>
-      <c r="R59" t="n">
-        <v>1</v>
-      </c>
-      <c r="S59" t="n">
-        <v>1</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1</v>
-      </c>
-      <c r="X59" t="n">
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
         <v>1</v>
       </c>
       <c r="Y59" t="n">
         <v>1</v>
       </c>
       <c r="Z59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC59" t="n">
         <v>1</v>
       </c>
       <c r="AD59" t="n">
@@ -4092,7 +4086,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Densidad</t>
+          <t>Dilatación térmica</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4101,10 +4095,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F60" t="n">
         <v>8</v>
@@ -4113,7 +4107,7 @@
         <v>6</v>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>7</v>
@@ -4127,26 +4121,17 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
-      <c r="P60" t="n">
-        <v>1</v>
-      </c>
       <c r="U60" t="n">
         <v>1</v>
       </c>
-      <c r="Y60" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD60" t="n">
+      <c r="AB60" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dilatación térmica</t>
+          <t>Dinámica y energía de rotación</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4155,43 +4140,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
         <v>10</v>
       </c>
-      <c r="F61" t="n">
-        <v>8</v>
-      </c>
-      <c r="G61" t="n">
-        <v>6</v>
-      </c>
-      <c r="I61" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" t="n">
-        <v>7</v>
-      </c>
-      <c r="L61" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M61" t="n">
-        <v>7</v>
-      </c>
-      <c r="O61" t="n">
-        <v>1</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB61" t="n">
+      <c r="Z61" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Dinámica y energía de rotación</t>
+          <t>Disipación de energía y eficiencia</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4200,19 +4161,76 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E62" t="n">
+        <v>8</v>
+      </c>
+      <c r="F62" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I62" t="n">
+        <v>8</v>
+      </c>
+      <c r="J62" t="n">
+        <v>7</v>
+      </c>
+      <c r="K62" t="n">
+        <v>8</v>
+      </c>
+      <c r="L62" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M62" t="n">
+        <v>7</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1</v>
       </c>
       <c r="Z62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD62" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Disipación de energía y eficiencia</t>
+          <t>Electroimanes y efecto magnético de la corriente</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4221,28 +4239,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
         <v>9</v>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
         <v>8</v>
       </c>
-      <c r="F63" t="n">
-        <v>10.5</v>
-      </c>
       <c r="G63" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I63" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J63" t="n">
         <v>7</v>
-      </c>
-      <c r="K63" t="n">
-        <v>8</v>
       </c>
       <c r="L63" t="n">
         <v>9.5</v>
@@ -4256,27 +4268,24 @@
       <c r="P63" t="n">
         <v>1</v>
       </c>
-      <c r="R63" t="n">
-        <v>1</v>
-      </c>
-      <c r="S63" t="n">
-        <v>1</v>
-      </c>
       <c r="U63" t="n">
         <v>1</v>
       </c>
-      <c r="V63" t="n">
-        <v>1</v>
-      </c>
       <c r="W63" t="n">
         <v>1</v>
       </c>
+      <c r="X63" t="n">
+        <v>1</v>
+      </c>
       <c r="Y63" t="n">
         <v>1</v>
       </c>
       <c r="Z63" t="n">
         <v>1</v>
       </c>
+      <c r="AA63" t="n">
+        <v>1</v>
+      </c>
       <c r="AB63" t="n">
         <v>1</v>
       </c>
@@ -4284,13 +4293,16 @@
         <v>1</v>
       </c>
       <c r="AD63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Electroimanes y efecto magnético de la corriente</t>
+          <t>Energía cinética</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4299,19 +4311,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D64" t="n">
-        <v>9</v>
-      </c>
-      <c r="F64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="n">
+        <v>7</v>
+      </c>
+      <c r="G64" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I64" t="n">
         <v>8</v>
-      </c>
-      <c r="G64" t="n">
-        <v>6</v>
-      </c>
-      <c r="I64" t="n">
-        <v>4</v>
       </c>
       <c r="J64" t="n">
         <v>7</v>
@@ -4322,19 +4334,22 @@
       <c r="M64" t="n">
         <v>7</v>
       </c>
-      <c r="O64" t="n">
-        <v>1</v>
-      </c>
       <c r="P64" t="n">
         <v>1</v>
       </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
       <c r="U64" t="n">
         <v>1</v>
       </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
       <c r="W64" t="n">
-        <v>1</v>
-      </c>
-      <c r="X64" t="n">
         <v>1</v>
       </c>
       <c r="Y64" t="n">
@@ -4362,7 +4377,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Energía cinética</t>
+          <t>Energía potencial gravitatoria y elástica</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4380,7 +4395,7 @@
         <v>7</v>
       </c>
       <c r="G65" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I65" t="n">
         <v>8</v>
@@ -4400,15 +4415,9 @@
       <c r="R65" t="n">
         <v>1</v>
       </c>
-      <c r="S65" t="n">
-        <v>1</v>
-      </c>
       <c r="U65" t="n">
         <v>1</v>
       </c>
-      <c r="V65" t="n">
-        <v>1</v>
-      </c>
       <c r="W65" t="n">
         <v>1</v>
       </c>
@@ -4416,9 +4425,6 @@
         <v>1</v>
       </c>
       <c r="Z65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA65" t="n">
         <v>1</v>
       </c>
       <c r="AB65" t="n">
@@ -4437,7 +4443,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Energía potencial gravitatoria y elástica</t>
+          <t>La energía y sus usos</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4446,19 +4452,16 @@
         </is>
       </c>
       <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" t="n">
+        <v>8</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2</v>
+      </c>
+      <c r="I66" t="n">
         <v>5</v>
-      </c>
-      <c r="D66" t="n">
-        <v>10</v>
-      </c>
-      <c r="E66" t="n">
-        <v>7</v>
-      </c>
-      <c r="G66" t="n">
-        <v>6</v>
-      </c>
-      <c r="I66" t="n">
-        <v>8</v>
       </c>
       <c r="J66" t="n">
         <v>7</v>
@@ -4469,6 +4472,9 @@
       <c r="M66" t="n">
         <v>7</v>
       </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
       <c r="P66" t="n">
         <v>1</v>
       </c>
@@ -4478,7 +4484,7 @@
       <c r="U66" t="n">
         <v>1</v>
       </c>
-      <c r="W66" t="n">
+      <c r="V66" t="n">
         <v>1</v>
       </c>
       <c r="Y66" t="n">
@@ -4491,12 +4497,6 @@
         <v>1</v>
       </c>
       <c r="AC66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE66" t="n">
         <v>1</v>
       </c>
     </row>

--- a/internacional/Contraste_fisica.xlsx
+++ b/internacional/Contraste_fisica.xlsx
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -10095,7 +10095,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D131" t="n">
         <v>9</v>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH131" t="inlineStr">
@@ -10147,7 +10147,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D132" t="n">
         <v>9</v>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH132" t="inlineStr">
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D136" t="n">
         <v>10</v>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH136" t="inlineStr">
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D141" t="n">
         <v>10</v>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH141" t="inlineStr">

--- a/internacional/Contraste_fisica.xlsx
+++ b/internacional/Contraste_fisica.xlsx
@@ -626,6 +626,9 @@
       <c r="G2" t="n">
         <v>6</v>
       </c>
+      <c r="H2" t="n">
+        <v>7</v>
+      </c>
       <c r="L2" t="n">
         <v>9.5</v>
       </c>
@@ -1018,14 +1021,17 @@
       <c r="G7" t="n">
         <v>6</v>
       </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1164,12 +1170,18 @@
       <c r="F9" t="n">
         <v>8</v>
       </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
       <c r="J9" t="n">
         <v>7</v>
       </c>
       <c r="K9" t="n">
         <v>9</v>
       </c>
+      <c r="L9" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M9" t="n">
         <v>7</v>
       </c>
@@ -1219,12 +1231,18 @@
       <c r="G10" t="n">
         <v>6</v>
       </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K10" t="n">
         <v>9</v>
       </c>
+      <c r="L10" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M10" t="n">
         <v>7</v>
       </c>
@@ -1275,7 +1293,7 @@
         <v>9</v>
       </c>
       <c r="L11" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="M11" t="n">
         <v>7</v>
@@ -1359,17 +1377,23 @@
       <c r="G12" t="n">
         <v>2</v>
       </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
       <c r="I12" t="n">
         <v>9.5</v>
       </c>
       <c r="J12" t="n">
         <v>7</v>
       </c>
+      <c r="K12" t="n">
+        <v>5</v>
+      </c>
       <c r="L12" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1614,11 +1638,14 @@
       <c r="G15" t="n">
         <v>6</v>
       </c>
+      <c r="H15" t="n">
+        <v>5</v>
+      </c>
       <c r="I15" t="n">
         <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K15" t="n">
         <v>9</v>
@@ -1627,7 +1654,7 @@
         <v>9.5</v>
       </c>
       <c r="M15" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -1766,6 +1793,9 @@
       <c r="G17" t="n">
         <v>6</v>
       </c>
+      <c r="H17" t="n">
+        <v>7</v>
+      </c>
       <c r="I17" t="n">
         <v>7</v>
       </c>
@@ -1776,7 +1806,7 @@
         <v>8</v>
       </c>
       <c r="L17" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M17" t="n">
         <v>7</v>
@@ -1939,11 +1969,17 @@
       <c r="G19" t="n">
         <v>6</v>
       </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.5</v>
+      </c>
       <c r="K19" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
@@ -2000,6 +2036,9 @@
       <c r="G20" t="n">
         <v>6</v>
       </c>
+      <c r="H20" t="n">
+        <v>7</v>
+      </c>
       <c r="I20" t="n">
         <v>9.5</v>
       </c>
@@ -2007,10 +2046,10 @@
         <v>9</v>
       </c>
       <c r="L20" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -2091,6 +2130,9 @@
       <c r="G21" t="n">
         <v>8.5</v>
       </c>
+      <c r="H21" t="n">
+        <v>7</v>
+      </c>
       <c r="I21" t="n">
         <v>9.5</v>
       </c>
@@ -2098,7 +2140,7 @@
         <v>9.5</v>
       </c>
       <c r="M21" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -2137,7 +2179,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
@@ -2243,6 +2285,9 @@
       <c r="G23" t="n">
         <v>6</v>
       </c>
+      <c r="H23" t="n">
+        <v>5</v>
+      </c>
       <c r="I23" t="n">
         <v>7</v>
       </c>
@@ -2250,10 +2295,10 @@
         <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M23" t="n">
         <v>7</v>
@@ -2314,7 +2359,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Energía potencial y potencial eléctrico</t>
+          <t>Primera ley de la termodinámica</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2323,38 +2368,44 @@
         </is>
       </c>
       <c r="C24" t="n">
+        <v>9</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9</v>
+      </c>
+      <c r="F24" t="n">
         <v>8</v>
-      </c>
-      <c r="D24" t="n">
-        <v>11</v>
-      </c>
-      <c r="F24" t="n">
-        <v>10.5</v>
       </c>
       <c r="G24" t="n">
         <v>8.5</v>
       </c>
-      <c r="L24" t="n">
+      <c r="I24" t="n">
         <v>9.5</v>
       </c>
+      <c r="M24" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="n">
         <v>1</v>
       </c>
       <c r="W24" t="n">
         <v>1</v>
       </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
       <c r="Y24" t="n">
         <v>1</v>
       </c>
-      <c r="Z24" t="n">
-        <v>1</v>
-      </c>
       <c r="AA24" t="n">
         <v>1</v>
       </c>
@@ -2371,23 +2422,23 @@
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Primera ley de la termodinámica</t>
+          <t>Radiación ionizante: detección, efectos y aplicaciones</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2396,10 +2447,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
         <v>8</v>
@@ -2407,9 +2458,15 @@
       <c r="G25" t="n">
         <v>8.5</v>
       </c>
+      <c r="H25" t="n">
+        <v>7</v>
+      </c>
       <c r="I25" t="n">
         <v>9.5</v>
       </c>
+      <c r="L25" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M25" t="n">
         <v>9.5</v>
       </c>
@@ -2422,6 +2479,9 @@
       <c r="R25" t="n">
         <v>1</v>
       </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
       <c r="V25" t="n">
         <v>1</v>
       </c>
@@ -2434,10 +2494,7 @@
       <c r="Y25" t="n">
         <v>1</v>
       </c>
-      <c r="AA25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="Z25" t="n">
         <v>1</v>
       </c>
       <c r="AC25" t="n">
@@ -2450,23 +2507,23 @@
         <v>1</v>
       </c>
       <c r="AF25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Radiación ionizante: detección, efectos y aplicaciones</t>
+          <t>Reflexión interna total</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2475,56 +2532,26 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
-      </c>
-      <c r="F26" t="n">
-        <v>8</v>
-      </c>
-      <c r="G26" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I26" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L26" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M26" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1</v>
-      </c>
-      <c r="W26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7</v>
+      </c>
+      <c r="K26" t="n">
+        <v>9</v>
+      </c>
+      <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
         <v>1</v>
       </c>
-      <c r="Y26" t="n">
-        <v>1</v>
-      </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
-      <c r="AC26" t="n">
-        <v>1</v>
-      </c>
       <c r="AD26" t="n">
         <v>1</v>
       </c>
@@ -2532,23 +2559,23 @@
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rapidez de la luz</t>
+          <t>Relaciones presión-volumen-temperatura en gases</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2557,36 +2584,30 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="F27" t="n">
+        <v>10.5</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="K27" t="n">
-        <v>9</v>
-      </c>
-      <c r="L27" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="M27" t="n">
         <v>7</v>
       </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
       <c r="P27" t="n">
         <v>1</v>
       </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
         <v>1</v>
       </c>
       <c r="Y27" t="n">
@@ -2595,6 +2616,9 @@
       <c r="Z27" t="n">
         <v>1</v>
       </c>
+      <c r="AA27" t="n">
+        <v>1</v>
+      </c>
       <c r="AB27" t="n">
         <v>1</v>
       </c>
@@ -2605,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
@@ -2621,7 +2645,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Relaciones presión-volumen-temperatura en gases</t>
+          <t>Segunda ley de la termodinámica</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2630,7 +2654,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
         <v>9</v>
@@ -2638,16 +2662,22 @@
       <c r="F28" t="n">
         <v>10.5</v>
       </c>
-      <c r="G28" t="n">
-        <v>8.5</v>
+      <c r="I28" t="n">
+        <v>9.5</v>
       </c>
       <c r="M28" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>1</v>
       </c>
       <c r="X28" t="n">
@@ -2656,27 +2686,18 @@
       <c r="Y28" t="n">
         <v>1</v>
       </c>
-      <c r="Z28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1</v>
-      </c>
       <c r="AB28" t="n">
         <v>1</v>
       </c>
-      <c r="AD28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE28" t="n">
+      <c r="AC28" t="n">
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -2688,7 +2709,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Segunda ley de la termodinámica</t>
+          <t>Semiconductores y electrónica básica</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2697,7 +2718,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
         <v>9</v>
@@ -2705,34 +2726,49 @@
       <c r="F29" t="n">
         <v>10.5</v>
       </c>
+      <c r="G29" t="n">
+        <v>8.5</v>
+      </c>
       <c r="I29" t="n">
         <v>9.5</v>
       </c>
-      <c r="M29" t="n">
-        <v>9.5</v>
+      <c r="J29" t="n">
+        <v>7</v>
+      </c>
+      <c r="L29" t="n">
+        <v>11</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
       </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
       <c r="R29" t="n">
         <v>1</v>
       </c>
-      <c r="V29" t="n">
-        <v>1</v>
-      </c>
-      <c r="W29" t="n">
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Z29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="n">
         <v>1</v>
       </c>
       <c r="AB29" t="n">
         <v>1</v>
       </c>
       <c r="AC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1</v>
       </c>
       <c r="AF29" t="n">
@@ -2740,7 +2776,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -2752,7 +2788,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Semiconductores y electrónica básica</t>
+          <t>Superposición e interferencia de ondas</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2761,77 +2797,74 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F30" t="n">
         <v>10.5</v>
       </c>
       <c r="G30" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
         <v>9.5</v>
       </c>
-      <c r="J30" t="n">
-        <v>7</v>
-      </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="n">
         <v>11</v>
       </c>
-      <c r="O30" t="n">
-        <v>1</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>9</v>
-      </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Superposición e interferencia de ondas</t>
+          <t>Gas ideal y teoría cinética</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2840,10 +2873,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F31" t="n">
         <v>10.5</v>
@@ -2854,12 +2887,18 @@
       <c r="I31" t="n">
         <v>9.5</v>
       </c>
+      <c r="J31" t="n">
+        <v>2.5</v>
+      </c>
       <c r="M31" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
       </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
       <c r="R31" t="n">
         <v>1</v>
       </c>
@@ -2891,58 +2930,58 @@
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gas ideal y teoría cinética</t>
+          <t>Rapidez de la luz</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
-      </c>
-      <c r="F32" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
         <v>6</v>
       </c>
-      <c r="I32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J32" t="n">
+      <c r="H32" t="n">
         <v>7</v>
       </c>
+      <c r="K32" t="n">
+        <v>9</v>
+      </c>
+      <c r="L32" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
         <v>1</v>
       </c>
       <c r="V32" t="n">
@@ -2957,15 +2996,9 @@
       <c r="Z32" t="n">
         <v>1</v>
       </c>
-      <c r="AA32" t="n">
-        <v>1</v>
-      </c>
       <c r="AB32" t="n">
         <v>1</v>
       </c>
-      <c r="AC32" t="n">
-        <v>1</v>
-      </c>
       <c r="AD32" t="n">
         <v>1</v>
       </c>
@@ -2973,16 +3006,16 @@
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
@@ -3006,9 +3039,18 @@
       <c r="G33" t="n">
         <v>6</v>
       </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
       <c r="I33" t="n">
         <v>2</v>
       </c>
+      <c r="J33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
       <c r="L33" t="n">
         <v>9.5</v>
       </c>
@@ -3149,15 +3191,24 @@
       <c r="G35" t="n">
         <v>2</v>
       </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
       <c r="I35" t="n">
         <v>2</v>
       </c>
       <c r="J35" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3</v>
       </c>
       <c r="L35" t="n">
         <v>9.5</v>
       </c>
+      <c r="M35" t="n">
+        <v>2.5</v>
+      </c>
       <c r="O35" t="n">
         <v>1</v>
       </c>
@@ -3222,6 +3273,9 @@
       <c r="G36" t="n">
         <v>8.5</v>
       </c>
+      <c r="H36" t="n">
+        <v>7</v>
+      </c>
       <c r="I36" t="n">
         <v>10</v>
       </c>
@@ -3229,10 +3283,10 @@
         <v>9</v>
       </c>
       <c r="K36" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L36" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M36" t="n">
         <v>7</v>
@@ -3316,6 +3370,9 @@
       <c r="G37" t="n">
         <v>8.5</v>
       </c>
+      <c r="H37" t="n">
+        <v>4</v>
+      </c>
       <c r="I37" t="n">
         <v>8</v>
       </c>
@@ -3323,10 +3380,10 @@
         <v>7</v>
       </c>
       <c r="L37" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="M37" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
@@ -3500,7 +3557,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Observación astronómica en distintas longitudes de onda</t>
+          <t>Caída libre</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3512,13 +3569,61 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G40" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>7</v>
+      </c>
+      <c r="I40" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>7</v>
+      </c>
+      <c r="L40" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M40" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1</v>
       </c>
       <c r="Z40" t="n">
         <v>1</v>
       </c>
+      <c r="AC40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1</v>
+      </c>
       <c r="AF40" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
@@ -3527,14 +3632,14 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Caída libre</t>
+          <t>Calentamiento y enfriamiento</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3543,41 +3648,44 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>8</v>
       </c>
       <c r="G41" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H41" t="n">
+        <v>7</v>
       </c>
       <c r="I41" t="n">
-        <v>9.5</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="L41" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M41" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
       </c>
-      <c r="R41" t="n">
-        <v>1</v>
-      </c>
-      <c r="S41" t="n">
-        <v>1</v>
-      </c>
       <c r="U41" t="n">
         <v>1</v>
       </c>
-      <c r="V41" t="n">
-        <v>1</v>
-      </c>
       <c r="W41" t="n">
         <v>1</v>
       </c>
@@ -3587,17 +3695,14 @@
       <c r="Z41" t="n">
         <v>1</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AB41" t="n">
         <v>1</v>
       </c>
       <c r="AD41" t="n">
         <v>1</v>
       </c>
-      <c r="AE41" t="n">
-        <v>1</v>
-      </c>
       <c r="AF41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
@@ -3613,7 +3718,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Calentamiento y enfriamiento</t>
+          <t>Calor como energía en tránsito</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3627,23 +3732,26 @@
       <c r="D42" t="n">
         <v>9</v>
       </c>
-      <c r="E42" t="n">
-        <v>2</v>
-      </c>
       <c r="F42" t="n">
         <v>8</v>
       </c>
       <c r="G42" t="n">
         <v>6</v>
       </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="J42" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4</v>
       </c>
       <c r="L42" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M42" t="n">
         <v>7</v>
@@ -3654,9 +3762,15 @@
       <c r="P42" t="n">
         <v>1</v>
       </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
       <c r="U42" t="n">
         <v>1</v>
       </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
       <c r="W42" t="n">
         <v>1</v>
       </c>
@@ -3673,7 +3787,7 @@
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -3689,7 +3803,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Calor como energía en tránsito</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3703,23 +3817,32 @@
       <c r="D43" t="n">
         <v>9</v>
       </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
       <c r="F43" t="n">
         <v>8</v>
       </c>
       <c r="G43" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="J43" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2</v>
       </c>
       <c r="L43" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M43" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
@@ -3739,20 +3862,29 @@
       <c r="W43" t="n">
         <v>1</v>
       </c>
+      <c r="X43" t="n">
+        <v>1</v>
+      </c>
       <c r="Y43" t="n">
         <v>1</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
+      <c r="AA43" t="n">
+        <v>1</v>
+      </c>
       <c r="AB43" t="n">
         <v>1</v>
       </c>
+      <c r="AC43" t="n">
+        <v>1</v>
+      </c>
       <c r="AD43" t="n">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -3768,7 +3900,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Campo magnético y magnetismo terrestre</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3777,31 +3909,31 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
         <v>9</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6</v>
+      </c>
+      <c r="H44" t="n">
         <v>2</v>
       </c>
-      <c r="F44" t="n">
-        <v>8</v>
-      </c>
-      <c r="G44" t="n">
-        <v>2</v>
-      </c>
       <c r="I44" t="n">
+        <v>7</v>
+      </c>
+      <c r="J44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L44" t="n">
         <v>3</v>
       </c>
-      <c r="J44" t="n">
-        <v>7</v>
-      </c>
-      <c r="L44" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M44" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O44" t="n">
         <v>1</v>
@@ -3812,6 +3944,9 @@
       <c r="R44" t="n">
         <v>1</v>
       </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
       <c r="U44" t="n">
         <v>1</v>
       </c>
@@ -3821,9 +3956,6 @@
       <c r="W44" t="n">
         <v>1</v>
       </c>
-      <c r="X44" t="n">
-        <v>1</v>
-      </c>
       <c r="Y44" t="n">
         <v>1</v>
       </c>
@@ -3842,8 +3974,11 @@
       <c r="AD44" t="n">
         <v>1</v>
       </c>
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
       <c r="AF44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
@@ -3859,7 +3994,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Campo magnético y magnetismo terrestre</t>
+          <t>Capacidad calorífica y calor específico</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3868,7 +4003,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
         <v>9</v>
@@ -3877,16 +4012,16 @@
         <v>8</v>
       </c>
       <c r="G45" t="n">
-        <v>6</v>
-      </c>
-      <c r="I45" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H45" t="n">
         <v>7</v>
       </c>
       <c r="J45" t="n">
         <v>7</v>
       </c>
       <c r="L45" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M45" t="n">
         <v>7</v>
@@ -3897,18 +4032,6 @@
       <c r="P45" t="n">
         <v>1</v>
       </c>
-      <c r="R45" t="n">
-        <v>1</v>
-      </c>
-      <c r="S45" t="n">
-        <v>1</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1</v>
-      </c>
       <c r="W45" t="n">
         <v>1</v>
       </c>
@@ -3918,9 +4041,6 @@
       <c r="Z45" t="n">
         <v>1</v>
       </c>
-      <c r="AA45" t="n">
-        <v>1</v>
-      </c>
       <c r="AB45" t="n">
         <v>1</v>
       </c>
@@ -3930,11 +4050,8 @@
       <c r="AD45" t="n">
         <v>1</v>
       </c>
-      <c r="AE45" t="n">
-        <v>1</v>
-      </c>
       <c r="AF45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -3950,7 +4067,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Capacidad calorífica y calor específico</t>
+          <t>Carga eléctrica y electrización</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3968,11 +4085,23 @@
         <v>8</v>
       </c>
       <c r="G46" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H46" t="n">
+        <v>7</v>
+      </c>
+      <c r="I46" t="n">
+        <v>7</v>
       </c>
       <c r="J46" t="n">
         <v>7</v>
       </c>
+      <c r="K46" t="n">
+        <v>5</v>
+      </c>
+      <c r="L46" t="n">
+        <v>9.5</v>
+      </c>
       <c r="M46" t="n">
         <v>7</v>
       </c>
@@ -3982,6 +4111,12 @@
       <c r="P46" t="n">
         <v>1</v>
       </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
       <c r="W46" t="n">
         <v>1</v>
       </c>
@@ -3991,17 +4126,20 @@
       <c r="Z46" t="n">
         <v>1</v>
       </c>
+      <c r="AA46" t="n">
+        <v>1</v>
+      </c>
       <c r="AB46" t="n">
         <v>1</v>
       </c>
-      <c r="AC46" t="n">
-        <v>1</v>
-      </c>
       <c r="AD46" t="n">
         <v>1</v>
       </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
       <c r="AF46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -4017,7 +4155,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Carga eléctrica y electrización</t>
+          <t>Centro de gravedad y estabilidad</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4026,50 +4164,20 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>9</v>
-      </c>
-      <c r="F47" t="n">
-        <v>8</v>
-      </c>
-      <c r="G47" t="n">
-        <v>6</v>
-      </c>
-      <c r="I47" t="n">
-        <v>7</v>
-      </c>
-      <c r="J47" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K47" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L47" t="n">
         <v>9.5</v>
       </c>
-      <c r="M47" t="n">
-        <v>7</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1</v>
-      </c>
       <c r="U47" t="n">
         <v>1</v>
       </c>
-      <c r="V47" t="n">
-        <v>1</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1</v>
-      </c>
       <c r="Z47" t="n">
         <v>1</v>
       </c>
@@ -4082,11 +4190,8 @@
       <c r="AD47" t="n">
         <v>1</v>
       </c>
-      <c r="AE47" t="n">
-        <v>1</v>
-      </c>
       <c r="AF47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
@@ -4095,14 +4200,14 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Centro de gravedad y estabilidad</t>
+          <t>Circuito eléctrico simple</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4114,28 +4219,67 @@
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>5</v>
       </c>
       <c r="L48" t="n">
-        <v>9.5</v>
+        <v>5</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
       </c>
       <c r="U48" t="n">
         <v>1</v>
       </c>
+      <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1</v>
+      </c>
       <c r="Z48" t="n">
         <v>1</v>
       </c>
-      <c r="AA48" t="n">
-        <v>1</v>
-      </c>
       <c r="AB48" t="n">
         <v>1</v>
       </c>
+      <c r="AC48" t="n">
+        <v>1</v>
+      </c>
       <c r="AD48" t="n">
         <v>1</v>
       </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
       <c r="AF48" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
@@ -4144,14 +4288,14 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Circuito eléctrico simple</t>
+          <t>Circuitos en serie y en paralelo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4160,34 +4304,34 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
         <v>9</v>
       </c>
-      <c r="E49" t="n">
-        <v>5</v>
-      </c>
       <c r="F49" t="n">
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="H49" t="n">
+        <v>7</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
         <v>7</v>
       </c>
       <c r="K49" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L49" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="M49" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
@@ -4210,9 +4354,6 @@
       <c r="AB49" t="n">
         <v>1</v>
       </c>
-      <c r="AC49" t="n">
-        <v>1</v>
-      </c>
       <c r="AD49" t="n">
         <v>1</v>
       </c>
@@ -4220,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="AF49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
@@ -4236,7 +4377,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Circuitos en serie y en paralelo</t>
+          <t>Color y dispersión de la luz</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4245,10 +4386,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F50" t="n">
         <v>8</v>
@@ -4256,28 +4397,28 @@
       <c r="G50" t="n">
         <v>6</v>
       </c>
-      <c r="I50" t="n">
-        <v>3</v>
+      <c r="H50" t="n">
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>7</v>
       </c>
       <c r="K50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L50" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
+      </c>
+      <c r="M50" t="n">
+        <v>4.5</v>
       </c>
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="P50" t="n">
-        <v>1</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1</v>
-      </c>
-      <c r="W50" t="n">
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="Y50" t="n">
@@ -4289,14 +4430,11 @@
       <c r="AB50" t="n">
         <v>1</v>
       </c>
-      <c r="AD50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE50" t="n">
+      <c r="AC50" t="n">
         <v>1</v>
       </c>
       <c r="AF50" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
@@ -4312,7 +4450,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Color y dispersión de la luz</t>
+          <t>Conductores y aislantes eléctricos</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4321,33 +4459,51 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
         <v>10</v>
       </c>
+      <c r="E51" t="n">
+        <v>5</v>
+      </c>
       <c r="F51" t="n">
         <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>7</v>
       </c>
       <c r="K51" t="n">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="L51" t="n">
+        <v>5</v>
       </c>
       <c r="M51" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O51" t="n">
         <v>1</v>
       </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
       <c r="S51" t="n">
         <v>1</v>
       </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="X51" t="n">
         <v>1</v>
       </c>
       <c r="Y51" t="n">
@@ -4359,11 +4515,11 @@
       <c r="AB51" t="n">
         <v>1</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AD51" t="n">
         <v>1</v>
       </c>
       <c r="AF51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
@@ -4379,7 +4535,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Conductores y aislantes eléctricos</t>
+          <t>Conservación de la energía</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4388,38 +4544,44 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E52" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F52" t="n">
         <v>8</v>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="H52" t="n">
+        <v>7</v>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J52" t="n">
         <v>7</v>
       </c>
       <c r="K52" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L52" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="M52" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
       </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
       <c r="R52" t="n">
         <v>1</v>
       </c>
@@ -4429,7 +4591,10 @@
       <c r="U52" t="n">
         <v>1</v>
       </c>
-      <c r="X52" t="n">
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>1</v>
       </c>
       <c r="Y52" t="n">
@@ -4438,14 +4603,23 @@
       <c r="Z52" t="n">
         <v>1</v>
       </c>
+      <c r="AA52" t="n">
+        <v>1</v>
+      </c>
       <c r="AB52" t="n">
         <v>1</v>
       </c>
+      <c r="AC52" t="n">
+        <v>1</v>
+      </c>
       <c r="AD52" t="n">
         <v>1</v>
       </c>
+      <c r="AE52" t="n">
+        <v>1</v>
+      </c>
       <c r="AF52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -4461,7 +4635,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Conservación de la energía</t>
+          <t>Conservación de la energía mecánica</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4475,14 +4649,11 @@
       <c r="D53" t="n">
         <v>9</v>
       </c>
-      <c r="E53" t="n">
-        <v>8</v>
-      </c>
       <c r="F53" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G53" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I53" t="n">
         <v>8</v>
@@ -4505,16 +4676,7 @@
       <c r="R53" t="n">
         <v>1</v>
       </c>
-      <c r="S53" t="n">
-        <v>1</v>
-      </c>
       <c r="U53" t="n">
-        <v>1</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1</v>
-      </c>
-      <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="Y53" t="n">
@@ -4555,7 +4717,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Conservación de la energía mecánica</t>
+          <t>Conservación del momento lineal</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4564,10 +4726,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F54" t="n">
         <v>10.5</v>
@@ -4575,53 +4737,44 @@
       <c r="G54" t="n">
         <v>8.5</v>
       </c>
-      <c r="I54" t="n">
+      <c r="L54" t="n">
+        <v>11</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="n">
         <v>8</v>
-      </c>
-      <c r="J54" t="n">
-        <v>7</v>
-      </c>
-      <c r="L54" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M54" t="n">
-        <v>7</v>
-      </c>
-      <c r="O54" t="n">
-        <v>1</v>
-      </c>
-      <c r="P54" t="n">
-        <v>1</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>5</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
@@ -4637,7 +4790,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Conservación del momento lineal</t>
+          <t>Corriente, voltaje y resistencia</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4646,19 +4799,34 @@
         </is>
       </c>
       <c r="C55" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" t="n">
+        <v>9</v>
+      </c>
+      <c r="F55" t="n">
         <v>8</v>
       </c>
-      <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="F55" t="n">
-        <v>10.5</v>
-      </c>
       <c r="G55" t="n">
-        <v>8.5</v>
+        <v>4</v>
+      </c>
+      <c r="H55" t="n">
+        <v>7</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K55" t="n">
+        <v>5</v>
       </c>
       <c r="L55" t="n">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="M55" t="n">
+        <v>7</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
@@ -4666,9 +4834,15 @@
       <c r="P55" t="n">
         <v>1</v>
       </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
       <c r="U55" t="n">
         <v>1</v>
       </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
       <c r="W55" t="n">
         <v>1</v>
       </c>
@@ -4694,7 +4868,7 @@
         <v>1</v>
       </c>
       <c r="AF55" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -4710,7 +4884,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Corriente, voltaje y resistencia</t>
+          <t>Expansión del universo y Big Bang</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4719,19 +4893,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
+        <v>11</v>
+      </c>
+      <c r="E56" t="n">
         <v>9</v>
       </c>
       <c r="F56" t="n">
-        <v>8</v>
-      </c>
-      <c r="G56" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H56" t="n">
         <v>4</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J56" t="n">
         <v>7</v>
@@ -4739,22 +4916,19 @@
       <c r="K56" t="n">
         <v>8</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>9.5</v>
       </c>
-      <c r="M56" t="n">
-        <v>7</v>
+      <c r="N56" t="n">
+        <v>1</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
       </c>
-      <c r="P56" t="n">
-        <v>1</v>
-      </c>
       <c r="R56" t="n">
         <v>1</v>
       </c>
-      <c r="U56" t="n">
+      <c r="S56" t="n">
         <v>1</v>
       </c>
       <c r="V56" t="n">
@@ -4763,6 +4937,9 @@
       <c r="W56" t="n">
         <v>1</v>
       </c>
+      <c r="X56" t="n">
+        <v>1</v>
+      </c>
       <c r="Y56" t="n">
         <v>1</v>
       </c>
@@ -4781,11 +4958,8 @@
       <c r="AD56" t="n">
         <v>1</v>
       </c>
-      <c r="AE56" t="n">
-        <v>1</v>
-      </c>
       <c r="AF56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -4801,7 +4975,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Expansión del universo y Big Bang</t>
+          <t>Densidad</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4810,48 +4984,42 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>11</v>
-      </c>
-      <c r="E57" t="n">
         <v>9</v>
       </c>
       <c r="F57" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G57" t="n">
+        <v>6</v>
+      </c>
+      <c r="H57" t="n">
+        <v>7</v>
       </c>
       <c r="I57" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K57" t="n">
+        <v>6</v>
+      </c>
+      <c r="L57" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M57" t="n">
         <v>7</v>
       </c>
-      <c r="K57" t="n">
-        <v>8</v>
-      </c>
-      <c r="M57" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N57" t="n">
-        <v>1</v>
-      </c>
       <c r="O57" t="n">
         <v>1</v>
       </c>
-      <c r="R57" t="n">
-        <v>1</v>
-      </c>
-      <c r="S57" t="n">
-        <v>1</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1</v>
-      </c>
-      <c r="X57" t="n">
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
         <v>1</v>
       </c>
       <c r="Y57" t="n">
@@ -4860,20 +5028,11 @@
       <c r="Z57" t="n">
         <v>1</v>
       </c>
-      <c r="AA57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>1</v>
-      </c>
       <c r="AD57" t="n">
         <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
@@ -4889,7 +5048,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Densidad</t>
+          <t>Dilatación térmica</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4898,10 +5057,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F58" t="n">
         <v>8</v>
@@ -4909,14 +5068,20 @@
       <c r="G58" t="n">
         <v>6</v>
       </c>
+      <c r="H58" t="n">
+        <v>7</v>
+      </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
         <v>7</v>
       </c>
+      <c r="K58" t="n">
+        <v>6</v>
+      </c>
       <c r="L58" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M58" t="n">
         <v>7</v>
@@ -4924,23 +5089,14 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="P58" t="n">
-        <v>1</v>
-      </c>
       <c r="U58" t="n">
         <v>1</v>
       </c>
-      <c r="Y58" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD58" t="n">
+      <c r="AB58" t="n">
         <v>1</v>
       </c>
       <c r="AF58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
@@ -4956,7 +5112,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dilatación térmica</t>
+          <t>Dinámica y energía de rotación</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4965,40 +5121,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
         <v>10</v>
       </c>
-      <c r="F59" t="n">
-        <v>8</v>
-      </c>
-      <c r="G59" t="n">
-        <v>6</v>
-      </c>
-      <c r="I59" t="n">
-        <v>3</v>
-      </c>
-      <c r="J59" t="n">
-        <v>7</v>
-      </c>
-      <c r="L59" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M59" t="n">
-        <v>7</v>
-      </c>
-      <c r="O59" t="n">
-        <v>1</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB59" t="n">
+      <c r="Z59" t="n">
         <v>1</v>
       </c>
       <c r="AF59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
@@ -5014,7 +5146,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Dinámica y energía de rotación</t>
+          <t>Disipación de energía y eficiencia</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5023,16 +5155,76 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E60" t="n">
+        <v>8</v>
+      </c>
+      <c r="F60" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G60" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H60" t="n">
+        <v>7</v>
+      </c>
+      <c r="I60" t="n">
+        <v>8</v>
+      </c>
+      <c r="J60" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2</v>
+      </c>
+      <c r="L60" t="n">
+        <v>6</v>
+      </c>
+      <c r="M60" t="n">
+        <v>7</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1</v>
       </c>
       <c r="Z60" t="n">
         <v>1</v>
       </c>
+      <c r="AB60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>1</v>
+      </c>
       <c r="AF60" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
@@ -5048,7 +5240,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Disipación de energía y eficiencia</t>
+          <t>Efecto Doppler</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5057,73 +5249,31 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D61" t="n">
-        <v>9</v>
-      </c>
-      <c r="E61" t="n">
-        <v>8</v>
-      </c>
-      <c r="F61" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G61" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I61" t="n">
-        <v>8</v>
-      </c>
-      <c r="J61" t="n">
-        <v>7</v>
-      </c>
-      <c r="K61" t="n">
-        <v>8</v>
-      </c>
-      <c r="L61" t="n">
+        <v>11</v>
+      </c>
+      <c r="M61" t="n">
         <v>9.5</v>
       </c>
-      <c r="M61" t="n">
-        <v>7</v>
-      </c>
-      <c r="O61" t="n">
-        <v>1</v>
-      </c>
-      <c r="P61" t="n">
-        <v>1</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1</v>
-      </c>
-      <c r="S61" t="n">
-        <v>1</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1</v>
-      </c>
       <c r="V61" t="n">
         <v>1</v>
       </c>
-      <c r="W61" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>1</v>
-      </c>
       <c r="Z61" t="n">
         <v>1</v>
       </c>
+      <c r="AA61" t="n">
+        <v>1</v>
+      </c>
       <c r="AB61" t="n">
         <v>1</v>
       </c>
       <c r="AC61" t="n">
         <v>1</v>
       </c>
-      <c r="AD61" t="n">
-        <v>1</v>
-      </c>
       <c r="AF61" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
@@ -5132,14 +5282,14 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Efecto Doppler</t>
+          <t>Esfuerzo, deformación y módulo de Young</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5148,31 +5298,28 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
         <v>11</v>
       </c>
+      <c r="G62" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2</v>
+      </c>
       <c r="M62" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V62" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC62" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y62" t="n">
         <v>1</v>
       </c>
       <c r="AF62" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
@@ -5181,14 +5328,14 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Esfuerzo, deformación y módulo de Young</t>
+          <t>Electroimanes y efecto magnético de la corriente</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5197,22 +5344,70 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="F63" t="n">
+        <v>8</v>
       </c>
       <c r="G63" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H63" t="n">
+        <v>5</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J63" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L63" t="n">
+        <v>3</v>
+      </c>
+      <c r="M63" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1</v>
       </c>
       <c r="P63" t="n">
         <v>1</v>
       </c>
+      <c r="U63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1</v>
+      </c>
+      <c r="X63" t="n">
+        <v>1</v>
+      </c>
       <c r="Y63" t="n">
         <v>1</v>
       </c>
+      <c r="Z63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1</v>
+      </c>
       <c r="AF63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
@@ -5228,7 +5423,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Electroimanes y efecto magnético de la corriente</t>
+          <t>Energía cinética</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5237,44 +5432,53 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>9</v>
-      </c>
-      <c r="F64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="n">
+        <v>7</v>
+      </c>
+      <c r="G64" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H64" t="n">
+        <v>4</v>
+      </c>
+      <c r="I64" t="n">
         <v>8</v>
-      </c>
-      <c r="G64" t="n">
-        <v>6</v>
-      </c>
-      <c r="I64" t="n">
-        <v>4</v>
       </c>
       <c r="J64" t="n">
         <v>7</v>
       </c>
+      <c r="K64" t="n">
+        <v>4</v>
+      </c>
       <c r="L64" t="n">
         <v>9.5</v>
       </c>
       <c r="M64" t="n">
-        <v>7</v>
-      </c>
-      <c r="O64" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="P64" t="n">
         <v>1</v>
       </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
       <c r="U64" t="n">
         <v>1</v>
       </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
       <c r="W64" t="n">
         <v>1</v>
       </c>
-      <c r="X64" t="n">
-        <v>1</v>
-      </c>
       <c r="Y64" t="n">
         <v>1</v>
       </c>
@@ -5297,7 +5501,7 @@
         <v>1</v>
       </c>
       <c r="AF64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
@@ -5313,7 +5517,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Energía cinética</t>
+          <t>Energía potencial gravitatoria y elástica</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5322,7 +5526,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
         <v>10</v>
@@ -5331,7 +5535,10 @@
         <v>7</v>
       </c>
       <c r="G65" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H65" t="n">
+        <v>4</v>
       </c>
       <c r="I65" t="n">
         <v>8</v>
@@ -5339,6 +5546,9 @@
       <c r="J65" t="n">
         <v>7</v>
       </c>
+      <c r="K65" t="n">
+        <v>4</v>
+      </c>
       <c r="L65" t="n">
         <v>9.5</v>
       </c>
@@ -5351,15 +5561,9 @@
       <c r="R65" t="n">
         <v>1</v>
       </c>
-      <c r="S65" t="n">
-        <v>1</v>
-      </c>
       <c r="U65" t="n">
         <v>1</v>
       </c>
-      <c r="V65" t="n">
-        <v>1</v>
-      </c>
       <c r="W65" t="n">
         <v>1</v>
       </c>
@@ -5367,9 +5571,6 @@
         <v>1</v>
       </c>
       <c r="Z65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA65" t="n">
         <v>1</v>
       </c>
       <c r="AB65" t="n">
@@ -5401,7 +5602,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Energía potencial gravitatoria y elástica</t>
+          <t>La energía y sus usos</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5410,28 +5611,37 @@
         </is>
       </c>
       <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="n">
+        <v>9</v>
+      </c>
+      <c r="F66" t="n">
+        <v>8</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2</v>
+      </c>
+      <c r="I66" t="n">
         <v>5</v>
       </c>
-      <c r="D66" t="n">
-        <v>10</v>
-      </c>
-      <c r="E66" t="n">
-        <v>7</v>
-      </c>
-      <c r="G66" t="n">
-        <v>6</v>
-      </c>
-      <c r="I66" t="n">
-        <v>8</v>
-      </c>
       <c r="J66" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2</v>
       </c>
       <c r="L66" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M66" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
       </c>
       <c r="P66" t="n">
         <v>1</v>
@@ -5442,7 +5652,7 @@
       <c r="U66" t="n">
         <v>1</v>
       </c>
-      <c r="W66" t="n">
+      <c r="V66" t="n">
         <v>1</v>
       </c>
       <c r="Y66" t="n">
@@ -5457,14 +5667,8 @@
       <c r="AC66" t="n">
         <v>1</v>
       </c>
-      <c r="AD66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>1</v>
-      </c>
       <c r="AF66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
@@ -5473,14 +5677,14 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>La energía y sus usos</t>
+          <t>Condiciones de equilibrio estático</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5489,31 +5693,31 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D67" t="n">
-        <v>9</v>
-      </c>
-      <c r="F67" t="n">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="E67" t="n">
+        <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J67" t="n">
         <v>7</v>
       </c>
+      <c r="K67" t="n">
+        <v>2</v>
+      </c>
       <c r="L67" t="n">
         <v>9.5</v>
       </c>
       <c r="M67" t="n">
-        <v>7</v>
-      </c>
-      <c r="O67" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="P67" t="n">
         <v>1</v>
@@ -5524,23 +5728,26 @@
       <c r="U67" t="n">
         <v>1</v>
       </c>
-      <c r="V67" t="n">
-        <v>1</v>
-      </c>
       <c r="Y67" t="n">
         <v>1</v>
       </c>
       <c r="Z67" t="n">
         <v>1</v>
       </c>
+      <c r="AA67" t="n">
+        <v>1</v>
+      </c>
       <c r="AB67" t="n">
         <v>1</v>
       </c>
-      <c r="AC67" t="n">
+      <c r="AD67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE67" t="n">
         <v>1</v>
       </c>
       <c r="AF67" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
@@ -5549,14 +5756,14 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Condiciones de equilibrio estático</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5565,28 +5772,40 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E68" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="F68" t="n">
+        <v>8</v>
       </c>
       <c r="G68" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K68" t="n">
+        <v>2</v>
       </c>
       <c r="L68" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M68" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="O68" t="n">
+        <v>1</v>
       </c>
       <c r="P68" t="n">
         <v>1</v>
@@ -5609,14 +5828,14 @@
       <c r="AB68" t="n">
         <v>1</v>
       </c>
+      <c r="AC68" t="n">
+        <v>1</v>
+      </c>
       <c r="AD68" t="n">
         <v>1</v>
       </c>
-      <c r="AE68" t="n">
-        <v>1</v>
-      </c>
       <c r="AF68" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
@@ -5632,7 +5851,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Flotación y hundimiento</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5646,23 +5865,20 @@
       <c r="D69" t="n">
         <v>9</v>
       </c>
-      <c r="E69" t="n">
-        <v>2</v>
-      </c>
       <c r="F69" t="n">
         <v>8</v>
       </c>
       <c r="G69" t="n">
+        <v>6</v>
+      </c>
+      <c r="H69" t="n">
         <v>2</v>
       </c>
-      <c r="I69" t="n">
+      <c r="K69" t="n">
+        <v>2</v>
+      </c>
+      <c r="L69" t="n">
         <v>3</v>
-      </c>
-      <c r="J69" t="n">
-        <v>7</v>
-      </c>
-      <c r="L69" t="n">
-        <v>9.5</v>
       </c>
       <c r="M69" t="n">
         <v>7</v>
@@ -5670,31 +5886,7 @@
       <c r="O69" t="n">
         <v>1</v>
       </c>
-      <c r="P69" t="n">
-        <v>1</v>
-      </c>
-      <c r="R69" t="n">
-        <v>1</v>
-      </c>
-      <c r="U69" t="n">
-        <v>1</v>
-      </c>
       <c r="Y69" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD69" t="n">
         <v>1</v>
       </c>
       <c r="AF69" t="n">
@@ -5714,7 +5906,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Flotación y hundimiento</t>
+          <t>Formas de energía</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5726,7 +5918,10 @@
         <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E70" t="n">
+        <v>7</v>
       </c>
       <c r="F70" t="n">
         <v>8</v>
@@ -5734,13 +5929,52 @@
       <c r="G70" t="n">
         <v>6</v>
       </c>
+      <c r="H70" t="n">
+        <v>2</v>
+      </c>
+      <c r="I70" t="n">
+        <v>5</v>
+      </c>
+      <c r="J70" t="n">
+        <v>7</v>
+      </c>
+      <c r="K70" t="n">
+        <v>2</v>
+      </c>
+      <c r="L70" t="n">
+        <v>4</v>
+      </c>
       <c r="M70" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O70" t="n">
         <v>1</v>
       </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1</v>
+      </c>
       <c r="Y70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE70" t="n">
         <v>1</v>
       </c>
       <c r="AF70" t="n">
@@ -5760,7 +5994,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Formas de energía</t>
+          <t>Fuentes de energía renovables y no renovables</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5772,28 +6006,31 @@
         <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>10</v>
-      </c>
-      <c r="E71" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F71" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G71" t="n">
         <v>6</v>
       </c>
+      <c r="H71" t="n">
+        <v>3</v>
+      </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J71" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K71" t="n">
+        <v>2</v>
       </c>
       <c r="L71" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="M71" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O71" t="n">
         <v>1</v>
@@ -5801,13 +6038,19 @@
       <c r="P71" t="n">
         <v>1</v>
       </c>
-      <c r="U71" t="n">
+      <c r="R71" t="n">
+        <v>1</v>
+      </c>
+      <c r="S71" t="n">
         <v>1</v>
       </c>
       <c r="V71" t="n">
         <v>1</v>
       </c>
       <c r="W71" t="n">
+        <v>1</v>
+      </c>
+      <c r="X71" t="n">
         <v>1</v>
       </c>
       <c r="Y71" t="n">
@@ -5842,7 +6085,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Fuentes de energía renovables y no renovables</t>
+          <t>Fuerza elástica y ley de Hooke</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5851,10 +6094,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F72" t="n">
         <v>8</v>
@@ -5862,17 +6105,20 @@
       <c r="G72" t="n">
         <v>6</v>
       </c>
+      <c r="H72" t="n">
+        <v>7</v>
+      </c>
       <c r="I72" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
-        <v>9</v>
-      </c>
-      <c r="K72" t="n">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="L72" t="n">
+        <v>6</v>
       </c>
       <c r="M72" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -5883,22 +6129,16 @@
       <c r="R72" t="n">
         <v>1</v>
       </c>
-      <c r="S72" t="n">
+      <c r="U72" t="n">
         <v>1</v>
       </c>
       <c r="V72" t="n">
         <v>1</v>
       </c>
-      <c r="W72" t="n">
-        <v>1</v>
-      </c>
-      <c r="X72" t="n">
-        <v>1</v>
-      </c>
       <c r="Y72" t="n">
         <v>1</v>
       </c>
-      <c r="Z72" t="n">
+      <c r="AB72" t="n">
         <v>1</v>
       </c>
       <c r="AC72" t="n">
@@ -5911,7 +6151,7 @@
         <v>1</v>
       </c>
       <c r="AF72" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
@@ -5927,7 +6167,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Fuerza elástica y ley de Hooke</t>
+          <t>Fuerza como empuje o tirón</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5936,61 +6176,58 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
         <v>10</v>
       </c>
+      <c r="E73" t="n">
+        <v>2</v>
+      </c>
       <c r="F73" t="n">
         <v>8</v>
       </c>
       <c r="G73" t="n">
         <v>6</v>
       </c>
+      <c r="H73" t="n">
+        <v>2</v>
+      </c>
       <c r="I73" t="n">
         <v>2</v>
       </c>
       <c r="J73" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K73" t="n">
+        <v>2</v>
       </c>
       <c r="L73" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M73" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="P73" t="n">
-        <v>1</v>
-      </c>
       <c r="R73" t="n">
         <v>1</v>
       </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
       <c r="U73" t="n">
         <v>1</v>
       </c>
-      <c r="V73" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB73" t="n">
+      <c r="Z73" t="n">
         <v>1</v>
       </c>
       <c r="AC73" t="n">
         <v>1</v>
       </c>
-      <c r="AD73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE73" t="n">
-        <v>1</v>
-      </c>
       <c r="AF73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
@@ -6006,7 +6243,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Fuerza como empuje o tirón</t>
+          <t>Fuerza neta y diagrama de cuerpo libre</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6015,52 +6252,79 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G74" t="n">
         <v>6</v>
       </c>
+      <c r="H74" t="n">
+        <v>7</v>
+      </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J74" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K74" t="n">
+        <v>4</v>
       </c>
       <c r="L74" t="n">
         <v>9.5</v>
       </c>
       <c r="M74" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
       <c r="R74" t="n">
         <v>1</v>
       </c>
-      <c r="S74" t="n">
-        <v>1</v>
-      </c>
       <c r="U74" t="n">
         <v>1</v>
       </c>
+      <c r="W74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1</v>
+      </c>
       <c r="Z74" t="n">
         <v>1</v>
       </c>
+      <c r="AA74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>1</v>
+      </c>
       <c r="AC74" t="n">
         <v>1</v>
       </c>
+      <c r="AD74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
       <c r="AF74" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
@@ -6076,7 +6340,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Fuerza neta y diagrama de cuerpo libre</t>
+          <t>Fuerzas de contacto y a distancia</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6085,37 +6349,34 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E75" t="n">
-        <v>6</v>
-      </c>
-      <c r="F75" t="n">
-        <v>10.5</v>
+        <v>3</v>
       </c>
       <c r="G75" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2</v>
       </c>
       <c r="I75" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="J75" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2</v>
       </c>
       <c r="L75" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="M75" t="n">
-        <v>7</v>
-      </c>
-      <c r="N75" t="n">
-        <v>1</v>
-      </c>
-      <c r="O75" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="P75" t="n">
         <v>1</v>
@@ -6135,12 +6396,6 @@
       <c r="Z75" t="n">
         <v>1</v>
       </c>
-      <c r="AA75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>1</v>
-      </c>
       <c r="AC75" t="n">
         <v>1</v>
       </c>
@@ -6151,7 +6406,7 @@
         <v>1</v>
       </c>
       <c r="AF75" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
@@ -6167,7 +6422,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Fuerzas de contacto y a distancia</t>
+          <t>Fuerzas mecánicas comunes</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6176,24 +6431,36 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D76" t="n">
         <v>10</v>
       </c>
-      <c r="E76" t="n">
-        <v>3</v>
+      <c r="F76" t="n">
+        <v>8</v>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="H76" t="n">
+        <v>7</v>
       </c>
       <c r="I76" t="n">
         <v>9.5</v>
       </c>
+      <c r="J76" t="n">
+        <v>7</v>
+      </c>
+      <c r="K76" t="n">
+        <v>2</v>
+      </c>
       <c r="L76" t="n">
         <v>9.5</v>
       </c>
-      <c r="P76" t="n">
+      <c r="M76" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O76" t="n">
         <v>1</v>
       </c>
       <c r="R76" t="n">
@@ -6202,10 +6469,7 @@
       <c r="U76" t="n">
         <v>1</v>
       </c>
-      <c r="W76" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y76" t="n">
+      <c r="V76" t="n">
         <v>1</v>
       </c>
       <c r="Z76" t="n">
@@ -6217,11 +6481,8 @@
       <c r="AD76" t="n">
         <v>1</v>
       </c>
-      <c r="AE76" t="n">
-        <v>1</v>
-      </c>
       <c r="AF76" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
@@ -6237,7 +6498,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Fuerzas mecánicas comunes</t>
+          <t>Gráficas del movimiento</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6257,37 +6518,49 @@
       <c r="G77" t="n">
         <v>6</v>
       </c>
+      <c r="H77" t="n">
+        <v>7</v>
+      </c>
       <c r="I77" t="n">
         <v>9.5</v>
       </c>
       <c r="J77" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="L77" t="n">
         <v>9.5</v>
       </c>
-      <c r="M77" t="n">
-        <v>7</v>
-      </c>
       <c r="O77" t="n">
         <v>1</v>
       </c>
+      <c r="P77" t="n">
+        <v>1</v>
+      </c>
       <c r="R77" t="n">
         <v>1</v>
       </c>
       <c r="U77" t="n">
         <v>1</v>
       </c>
-      <c r="V77" t="n">
+      <c r="W77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y77" t="n">
         <v>1</v>
       </c>
       <c r="Z77" t="n">
         <v>1</v>
       </c>
+      <c r="AB77" t="n">
+        <v>1</v>
+      </c>
       <c r="AC77" t="n">
         <v>1</v>
       </c>
       <c r="AD77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE77" t="n">
         <v>1</v>
       </c>
       <c r="AF77" t="n">
@@ -6307,7 +6580,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Gráficas del movimiento</t>
+          <t>Gravedad: atracción hacia la Tierra</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6316,16 +6589,22 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
         <v>10</v>
       </c>
+      <c r="E78" t="n">
+        <v>3</v>
+      </c>
       <c r="F78" t="n">
         <v>8</v>
       </c>
       <c r="G78" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2</v>
       </c>
       <c r="I78" t="n">
         <v>9.5</v>
@@ -6333,8 +6612,14 @@
       <c r="J78" t="n">
         <v>7</v>
       </c>
+      <c r="K78" t="n">
+        <v>5</v>
+      </c>
       <c r="L78" t="n">
-        <v>9.5</v>
+        <v>6</v>
+      </c>
+      <c r="M78" t="n">
+        <v>2.5</v>
       </c>
       <c r="O78" t="n">
         <v>1</v>
@@ -6345,6 +6630,9 @@
       <c r="R78" t="n">
         <v>1</v>
       </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
       <c r="U78" t="n">
         <v>1</v>
       </c>
@@ -6357,9 +6645,6 @@
       <c r="Z78" t="n">
         <v>1</v>
       </c>
-      <c r="AB78" t="n">
-        <v>1</v>
-      </c>
       <c r="AC78" t="n">
         <v>1</v>
       </c>
@@ -6370,7 +6655,7 @@
         <v>1</v>
       </c>
       <c r="AF78" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG78" t="inlineStr">
         <is>
@@ -6379,14 +6664,14 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Gravedad: atracción hacia la Tierra</t>
+          <t>Ley de gravitación universal</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6395,24 +6680,18 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D79" t="n">
         <v>10</v>
       </c>
-      <c r="E79" t="n">
-        <v>3</v>
-      </c>
       <c r="F79" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G79" t="n">
-        <v>3</v>
-      </c>
-      <c r="I79" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J79" t="n">
+        <v>6</v>
+      </c>
+      <c r="H79" t="n">
         <v>7</v>
       </c>
       <c r="L79" t="n">
@@ -6424,18 +6703,12 @@
       <c r="O79" t="n">
         <v>1</v>
       </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1</v>
-      </c>
-      <c r="S79" t="n">
-        <v>1</v>
-      </c>
       <c r="U79" t="n">
         <v>1</v>
       </c>
+      <c r="V79" t="n">
+        <v>1</v>
+      </c>
       <c r="W79" t="n">
         <v>1</v>
       </c>
@@ -6445,6 +6718,12 @@
       <c r="Z79" t="n">
         <v>1</v>
       </c>
+      <c r="AA79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1</v>
+      </c>
       <c r="AC79" t="n">
         <v>1</v>
       </c>
@@ -6455,7 +6734,7 @@
         <v>1</v>
       </c>
       <c r="AF79" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
@@ -6464,14 +6743,14 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ley de gravitación universal</t>
+          <t>Imanes y polos magnéticos</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6480,58 +6759,58 @@
         </is>
       </c>
       <c r="C80" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" t="n">
+        <v>11</v>
+      </c>
+      <c r="E80" t="n">
+        <v>3</v>
+      </c>
+      <c r="F80" t="n">
         <v>8</v>
       </c>
-      <c r="D80" t="n">
-        <v>10</v>
-      </c>
-      <c r="F80" t="n">
-        <v>10.5</v>
-      </c>
       <c r="G80" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2</v>
+      </c>
+      <c r="I80" t="n">
+        <v>2</v>
+      </c>
+      <c r="J80" t="n">
+        <v>2.5</v>
       </c>
       <c r="L80" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="M80" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O80" t="n">
         <v>1</v>
       </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
       <c r="U80" t="n">
         <v>1</v>
       </c>
-      <c r="V80" t="n">
-        <v>1</v>
-      </c>
-      <c r="W80" t="n">
-        <v>1</v>
-      </c>
       <c r="Y80" t="n">
         <v>1</v>
       </c>
       <c r="Z80" t="n">
         <v>1</v>
       </c>
-      <c r="AA80" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB80" t="n">
-        <v>1</v>
-      </c>
       <c r="AC80" t="n">
         <v>1</v>
       </c>
       <c r="AD80" t="n">
         <v>1</v>
       </c>
-      <c r="AE80" t="n">
-        <v>1</v>
-      </c>
       <c r="AF80" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
@@ -6547,7 +6826,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Imanes y polos magnéticos</t>
+          <t>Leyes de Kepler</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6556,50 +6835,35 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D81" t="n">
+        <v>9</v>
+      </c>
+      <c r="M81" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V81" t="n">
+        <v>1</v>
+      </c>
+      <c r="W81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF81" t="n">
         <v>11</v>
       </c>
-      <c r="E81" t="n">
-        <v>3</v>
-      </c>
-      <c r="F81" t="n">
-        <v>8</v>
-      </c>
-      <c r="G81" t="n">
-        <v>2</v>
-      </c>
-      <c r="I81" t="n">
-        <v>2</v>
-      </c>
-      <c r="L81" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O81" t="n">
-        <v>1</v>
-      </c>
-      <c r="P81" t="n">
-        <v>1</v>
-      </c>
-      <c r="U81" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF81" t="n">
-        <v>3</v>
-      </c>
       <c r="AG81" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -6607,14 +6871,14 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Leyes de Kepler</t>
+          <t>Magnitudes escalares y vectoriales</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6623,34 +6887,58 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D82" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F82" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G82" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H82" t="n">
+        <v>3</v>
+      </c>
+      <c r="I82" t="n">
+        <v>6</v>
+      </c>
+      <c r="K82" t="n">
+        <v>6</v>
+      </c>
+      <c r="L82" t="n">
+        <v>9.5</v>
       </c>
       <c r="M82" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V82" t="n">
-        <v>1</v>
-      </c>
-      <c r="W82" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y82" t="n">
         <v>1</v>
       </c>
       <c r="Z82" t="n">
         <v>1</v>
       </c>
-      <c r="AA82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB82" t="n">
+      <c r="AC82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD82" t="n">
         <v>1</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
       </c>
       <c r="AF82" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
@@ -6659,14 +6947,14 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Magnitudes escalares y vectoriales</t>
+          <t>Longitud de onda, frecuencia y rapidez</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6675,38 +6963,62 @@
         </is>
       </c>
       <c r="C83" t="n">
+        <v>8</v>
+      </c>
+      <c r="D83" t="n">
+        <v>9</v>
+      </c>
+      <c r="F83" t="n">
         <v>5</v>
       </c>
-      <c r="D83" t="n">
-        <v>10</v>
-      </c>
-      <c r="F83" t="n">
-        <v>10.5</v>
-      </c>
       <c r="G83" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H83" t="n">
+        <v>7</v>
       </c>
       <c r="I83" t="n">
-        <v>6</v>
+        <v>9.5</v>
+      </c>
+      <c r="J83" t="n">
+        <v>7</v>
       </c>
       <c r="L83" t="n">
         <v>9.5</v>
       </c>
+      <c r="M83" t="n">
+        <v>7</v>
+      </c>
       <c r="O83" t="n">
         <v>1</v>
       </c>
       <c r="P83" t="n">
         <v>1</v>
       </c>
+      <c r="R83" t="n">
+        <v>1</v>
+      </c>
       <c r="U83" t="n">
         <v>1</v>
       </c>
+      <c r="V83" t="n">
+        <v>1</v>
+      </c>
+      <c r="W83" t="n">
+        <v>1</v>
+      </c>
       <c r="Y83" t="n">
         <v>1</v>
       </c>
       <c r="Z83" t="n">
         <v>1</v>
       </c>
+      <c r="AA83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>1</v>
+      </c>
       <c r="AC83" t="n">
         <v>1</v>
       </c>
@@ -6717,7 +7029,7 @@
         <v>1</v>
       </c>
       <c r="AF83" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
@@ -6733,7 +7045,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Longitud de onda, frecuencia y rapidez</t>
+          <t>Máquinas simples</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6742,70 +7054,46 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
         <v>8</v>
       </c>
       <c r="G84" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2</v>
       </c>
       <c r="I84" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="J84" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K84" t="n">
+        <v>2</v>
       </c>
       <c r="L84" t="n">
         <v>9.5</v>
       </c>
       <c r="M84" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O84" t="n">
         <v>1</v>
       </c>
-      <c r="P84" t="n">
-        <v>1</v>
-      </c>
-      <c r="R84" t="n">
-        <v>1</v>
-      </c>
       <c r="U84" t="n">
         <v>1</v>
       </c>
-      <c r="V84" t="n">
-        <v>1</v>
-      </c>
-      <c r="W84" t="n">
-        <v>1</v>
-      </c>
       <c r="Y84" t="n">
         <v>1</v>
       </c>
-      <c r="Z84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE84" t="n">
-        <v>1</v>
-      </c>
       <c r="AF84" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG84" t="inlineStr">
         <is>
@@ -6821,7 +7109,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Máquinas simples</t>
+          <t>Masa y peso</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6833,33 +7121,63 @@
         <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F85" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G85" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2</v>
       </c>
       <c r="I85" t="n">
+        <v>2</v>
+      </c>
+      <c r="J85" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K85" t="n">
         <v>5</v>
       </c>
-      <c r="J85" t="n">
-        <v>7</v>
-      </c>
       <c r="L85" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="M85" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O85" t="n">
         <v>1</v>
       </c>
+      <c r="P85" t="n">
+        <v>1</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1</v>
+      </c>
       <c r="U85" t="n">
         <v>1</v>
       </c>
+      <c r="W85" t="n">
+        <v>1</v>
+      </c>
       <c r="Y85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE85" t="n">
         <v>1</v>
       </c>
       <c r="AF85" t="n">
@@ -6879,7 +7197,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Masa y peso</t>
+          <t>Materiales magnéticos</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6888,61 +7206,49 @@
         </is>
       </c>
       <c r="C86" t="n">
+        <v>3</v>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="G86" t="n">
         <v>2</v>
       </c>
-      <c r="D86" t="n">
-        <v>9</v>
-      </c>
-      <c r="F86" t="n">
-        <v>8</v>
-      </c>
-      <c r="G86" t="n">
-        <v>6</v>
+      <c r="H86" t="n">
+        <v>2</v>
       </c>
       <c r="I86" t="n">
         <v>2</v>
       </c>
+      <c r="J86" t="n">
+        <v>2.5</v>
+      </c>
       <c r="L86" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="M86" t="n">
-        <v>7</v>
-      </c>
-      <c r="O86" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="P86" t="n">
         <v>1</v>
       </c>
-      <c r="R86" t="n">
-        <v>1</v>
-      </c>
       <c r="U86" t="n">
         <v>1</v>
       </c>
-      <c r="W86" t="n">
+      <c r="X86" t="n">
         <v>1</v>
       </c>
       <c r="Y86" t="n">
         <v>1</v>
       </c>
-      <c r="Z86" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA86" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC86" t="n">
+      <c r="AB86" t="n">
         <v>1</v>
       </c>
       <c r="AD86" t="n">
         <v>1</v>
       </c>
-      <c r="AE86" t="n">
-        <v>1</v>
-      </c>
       <c r="AF86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
@@ -6958,7 +7264,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Materiales magnéticos</t>
+          <t>Materiales opacos, transparentes y translúcidos</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6967,7 +7273,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
         <v>10</v>
@@ -6975,32 +7281,23 @@
       <c r="G87" t="n">
         <v>2</v>
       </c>
-      <c r="I87" t="n">
+      <c r="H87" t="n">
         <v>2</v>
       </c>
+      <c r="K87" t="n">
+        <v>3</v>
+      </c>
       <c r="L87" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="P87" t="n">
         <v>1</v>
       </c>
-      <c r="U87" t="n">
-        <v>1</v>
-      </c>
-      <c r="X87" t="n">
-        <v>1</v>
-      </c>
       <c r="Y87" t="n">
         <v>1</v>
       </c>
-      <c r="AB87" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD87" t="n">
-        <v>1</v>
-      </c>
       <c r="AF87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
@@ -7016,7 +7313,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Materiales opacos, transparentes y translúcidos</t>
+          <t>Conducción, convección y radiación</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7028,15 +7325,63 @@
         <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E88" t="n">
+        <v>8</v>
+      </c>
+      <c r="F88" t="n">
+        <v>8</v>
       </c>
       <c r="G88" t="n">
+        <v>6</v>
+      </c>
+      <c r="H88" t="n">
         <v>2</v>
       </c>
+      <c r="I88" t="n">
+        <v>3</v>
+      </c>
+      <c r="J88" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K88" t="n">
+        <v>2</v>
+      </c>
+      <c r="L88" t="n">
+        <v>4</v>
+      </c>
+      <c r="M88" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O88" t="n">
+        <v>1</v>
+      </c>
       <c r="P88" t="n">
         <v>1</v>
       </c>
+      <c r="R88" t="n">
+        <v>1</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1</v>
+      </c>
+      <c r="W88" t="n">
+        <v>1</v>
+      </c>
       <c r="Y88" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD88" t="n">
         <v>1</v>
       </c>
       <c r="AF88" t="n">
@@ -7056,7 +7401,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Conducción, convección y radiación</t>
+          <t>Medición de magnitudes con instrumentos</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7070,26 +7415,29 @@
       <c r="D89" t="n">
         <v>9</v>
       </c>
-      <c r="E89" t="n">
-        <v>8</v>
-      </c>
       <c r="F89" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G89" t="n">
         <v>6</v>
       </c>
+      <c r="H89" t="n">
+        <v>2</v>
+      </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>9.5</v>
       </c>
       <c r="J89" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K89" t="n">
+        <v>9</v>
       </c>
       <c r="L89" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M89" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O89" t="n">
         <v>1</v>
@@ -7100,9 +7448,18 @@
       <c r="R89" t="n">
         <v>1</v>
       </c>
+      <c r="S89" t="n">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>1</v>
+      </c>
       <c r="U89" t="n">
         <v>1</v>
       </c>
+      <c r="V89" t="n">
+        <v>1</v>
+      </c>
       <c r="W89" t="n">
         <v>1</v>
       </c>
@@ -7112,13 +7469,13 @@
       <c r="Z89" t="n">
         <v>1</v>
       </c>
-      <c r="AB89" t="n">
-        <v>1</v>
-      </c>
       <c r="AC89" t="n">
         <v>1</v>
       </c>
       <c r="AD89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE89" t="n">
         <v>1</v>
       </c>
       <c r="AF89" t="n">
@@ -7138,7 +7495,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Medición de magnitudes con instrumentos</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7147,10 +7504,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D90" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E90" t="n">
+        <v>4</v>
       </c>
       <c r="F90" t="n">
         <v>8</v>
@@ -7158,17 +7518,20 @@
       <c r="G90" t="n">
         <v>6</v>
       </c>
+      <c r="H90" t="n">
+        <v>7</v>
+      </c>
       <c r="I90" t="n">
         <v>9.5</v>
       </c>
       <c r="J90" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K90" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L90" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M90" t="n">
         <v>7</v>
@@ -7182,12 +7545,6 @@
       <c r="R90" t="n">
         <v>1</v>
       </c>
-      <c r="S90" t="n">
-        <v>1</v>
-      </c>
-      <c r="T90" t="n">
-        <v>1</v>
-      </c>
       <c r="U90" t="n">
         <v>1</v>
       </c>
@@ -7203,6 +7560,12 @@
       <c r="Z90" t="n">
         <v>1</v>
       </c>
+      <c r="AA90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>1</v>
+      </c>
       <c r="AC90" t="n">
         <v>1</v>
       </c>
@@ -7213,7 +7576,7 @@
         <v>1</v>
       </c>
       <c r="AF90" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG90" t="inlineStr">
         <is>
@@ -7229,7 +7592,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Momento lineal e impulso</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7238,76 +7601,64 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D91" t="n">
         <v>10</v>
       </c>
-      <c r="E91" t="n">
-        <v>4</v>
-      </c>
       <c r="F91" t="n">
         <v>8</v>
       </c>
       <c r="G91" t="n">
-        <v>6</v>
-      </c>
-      <c r="I91" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="J91" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K91" t="n">
+        <v>4</v>
+      </c>
+      <c r="L91" t="n">
+        <v>11</v>
+      </c>
+      <c r="O91" t="n">
+        <v>1</v>
+      </c>
+      <c r="P91" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" t="n">
+        <v>1</v>
+      </c>
+      <c r="W91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF91" t="n">
         <v>8</v>
-      </c>
-      <c r="L91" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M91" t="n">
-        <v>7</v>
-      </c>
-      <c r="O91" t="n">
-        <v>1</v>
-      </c>
-      <c r="P91" t="n">
-        <v>1</v>
-      </c>
-      <c r="R91" t="n">
-        <v>1</v>
-      </c>
-      <c r="U91" t="n">
-        <v>1</v>
-      </c>
-      <c r="V91" t="n">
-        <v>1</v>
-      </c>
-      <c r="W91" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF91" t="n">
-        <v>6</v>
       </c>
       <c r="AG91" t="inlineStr">
         <is>
@@ -7323,7 +7674,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Momento lineal e impulso</t>
+          <t>Movimiento armónico simple</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7340,25 +7691,7 @@
       <c r="F92" t="n">
         <v>8</v>
       </c>
-      <c r="G92" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J92" t="n">
-        <v>9</v>
-      </c>
-      <c r="L92" t="n">
-        <v>11</v>
-      </c>
       <c r="O92" t="n">
-        <v>1</v>
-      </c>
-      <c r="P92" t="n">
-        <v>1</v>
-      </c>
-      <c r="S92" t="n">
-        <v>1</v>
-      </c>
-      <c r="U92" t="n">
         <v>1</v>
       </c>
       <c r="W92" t="n">
@@ -7402,7 +7735,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Movimiento armónico simple</t>
+          <t>Movimiento circular y variables angulares</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7411,17 +7744,35 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D93" t="n">
         <v>10</v>
       </c>
       <c r="F93" t="n">
-        <v>8</v>
+        <v>10.5</v>
+      </c>
+      <c r="G93" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K93" t="n">
+        <v>3</v>
+      </c>
+      <c r="L93" t="n">
+        <v>11</v>
+      </c>
+      <c r="M93" t="n">
+        <v>7</v>
       </c>
       <c r="O93" t="n">
         <v>1</v>
       </c>
+      <c r="P93" t="n">
+        <v>1</v>
+      </c>
+      <c r="U93" t="n">
+        <v>1</v>
+      </c>
       <c r="W93" t="n">
         <v>1</v>
       </c>
@@ -7447,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="AF93" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
@@ -7463,7 +7814,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Movimiento circular y variables angulares</t>
+          <t>Cinemática en dos dimensiones y proyectiles</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7472,32 +7823,35 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D94" t="n">
         <v>10</v>
       </c>
-      <c r="F94" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G94" t="n">
-        <v>8.5</v>
+      <c r="I94" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J94" t="n">
+        <v>9</v>
       </c>
       <c r="L94" t="n">
         <v>11</v>
       </c>
       <c r="M94" t="n">
-        <v>7</v>
-      </c>
-      <c r="O94" t="n">
-        <v>1</v>
-      </c>
-      <c r="P94" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1</v>
+      </c>
+      <c r="S94" t="n">
         <v>1</v>
       </c>
       <c r="U94" t="n">
         <v>1</v>
       </c>
+      <c r="V94" t="n">
+        <v>1</v>
+      </c>
       <c r="W94" t="n">
         <v>1</v>
       </c>
@@ -7523,7 +7877,7 @@
         <v>1</v>
       </c>
       <c r="AF94" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
@@ -7539,7 +7893,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cinemática en dos dimensiones y proyectiles</t>
+          <t>Movimiento con aceleración constante</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7553,22 +7907,34 @@
       <c r="D95" t="n">
         <v>10</v>
       </c>
+      <c r="F95" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G95" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H95" t="n">
+        <v>7</v>
+      </c>
       <c r="I95" t="n">
+        <v>8</v>
+      </c>
+      <c r="J95" t="n">
+        <v>7</v>
+      </c>
+      <c r="L95" t="n">
         <v>9.5</v>
-      </c>
-      <c r="J95" t="n">
-        <v>9</v>
-      </c>
-      <c r="L95" t="n">
-        <v>11</v>
       </c>
       <c r="M95" t="n">
         <v>9.5</v>
       </c>
+      <c r="O95" t="n">
+        <v>1</v>
+      </c>
+      <c r="P95" t="n">
+        <v>1</v>
+      </c>
       <c r="R95" t="n">
-        <v>1</v>
-      </c>
-      <c r="S95" t="n">
         <v>1</v>
       </c>
       <c r="U95" t="n">
@@ -7618,7 +7984,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Movimiento con aceleración constante</t>
+          <t>Ondas estacionarias y armónicos</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7630,41 +7996,26 @@
         <v>8</v>
       </c>
       <c r="D96" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F96" t="n">
         <v>10.5</v>
       </c>
-      <c r="G96" t="n">
-        <v>8.5</v>
+      <c r="H96" t="n">
+        <v>7</v>
       </c>
       <c r="I96" t="n">
-        <v>8</v>
-      </c>
-      <c r="J96" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M96" t="n">
         <v>7</v>
       </c>
-      <c r="L96" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M96" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O96" t="n">
         <v>1</v>
       </c>
-      <c r="P96" t="n">
-        <v>1</v>
-      </c>
       <c r="R96" t="n">
         <v>1</v>
       </c>
-      <c r="U96" t="n">
-        <v>1</v>
-      </c>
-      <c r="V96" t="n">
-        <v>1</v>
-      </c>
       <c r="W96" t="n">
         <v>1</v>
       </c>
@@ -7672,9 +8023,6 @@
         <v>1</v>
       </c>
       <c r="Z96" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA96" t="n">
         <v>1</v>
       </c>
       <c r="AB96" t="n">
@@ -7706,7 +8054,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Ondas estacionarias y armónicos</t>
+          <t>Ondas mecánicas transversales y longitudinales</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7715,33 +8063,51 @@
         </is>
       </c>
       <c r="C97" t="n">
+        <v>2</v>
+      </c>
+      <c r="D97" t="n">
+        <v>9</v>
+      </c>
+      <c r="E97" t="n">
         <v>8</v>
       </c>
-      <c r="D97" t="n">
-        <v>11</v>
-      </c>
-      <c r="F97" t="n">
-        <v>10.5</v>
+      <c r="G97" t="n">
+        <v>6</v>
       </c>
       <c r="I97" t="n">
         <v>9.5</v>
       </c>
+      <c r="L97" t="n">
+        <v>9.5</v>
+      </c>
       <c r="M97" t="n">
         <v>7</v>
       </c>
-      <c r="O97" t="n">
+      <c r="P97" t="n">
         <v>1</v>
       </c>
       <c r="R97" t="n">
         <v>1</v>
       </c>
+      <c r="U97" t="n">
+        <v>1</v>
+      </c>
+      <c r="V97" t="n">
+        <v>1</v>
+      </c>
       <c r="W97" t="n">
         <v>1</v>
       </c>
+      <c r="X97" t="n">
+        <v>1</v>
+      </c>
       <c r="Y97" t="n">
         <v>1</v>
       </c>
       <c r="Z97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA97" t="n">
         <v>1</v>
       </c>
       <c r="AB97" t="n">
@@ -7773,7 +8139,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ondas mecánicas transversales y longitudinales</t>
+          <t>Péndulo simple</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7782,45 +8148,21 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D98" t="n">
-        <v>9</v>
-      </c>
-      <c r="E98" t="n">
+        <v>11</v>
+      </c>
+      <c r="F98" t="n">
         <v>8</v>
       </c>
-      <c r="G98" t="n">
-        <v>6</v>
-      </c>
       <c r="I98" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L98" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M98" t="n">
+        <v>4</v>
+      </c>
+      <c r="J98" t="n">
         <v>7</v>
       </c>
-      <c r="P98" t="n">
-        <v>1</v>
-      </c>
-      <c r="R98" t="n">
-        <v>1</v>
-      </c>
-      <c r="U98" t="n">
-        <v>1</v>
-      </c>
-      <c r="V98" t="n">
-        <v>1</v>
-      </c>
-      <c r="W98" t="n">
-        <v>1</v>
-      </c>
-      <c r="X98" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y98" t="n">
+      <c r="O98" t="n">
         <v>1</v>
       </c>
       <c r="Z98" t="n">
@@ -7829,16 +8171,7 @@
       <c r="AA98" t="n">
         <v>1</v>
       </c>
-      <c r="AB98" t="n">
-        <v>1</v>
-      </c>
       <c r="AC98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE98" t="n">
         <v>1</v>
       </c>
       <c r="AF98" t="n">
@@ -7858,7 +8191,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Péndulo simple</t>
+          <t>Posición, desplazamiento y trayectoria</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7867,34 +8200,67 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D99" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F99" t="n">
         <v>8</v>
       </c>
+      <c r="G99" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2</v>
+      </c>
       <c r="I99" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="J99" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K99" t="n">
+        <v>2</v>
+      </c>
+      <c r="L99" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M99" t="n">
+        <v>2.5</v>
       </c>
       <c r="O99" t="n">
         <v>1</v>
       </c>
+      <c r="P99" t="n">
+        <v>1</v>
+      </c>
+      <c r="R99" t="n">
+        <v>1</v>
+      </c>
+      <c r="S99" t="n">
+        <v>1</v>
+      </c>
+      <c r="U99" t="n">
+        <v>1</v>
+      </c>
+      <c r="W99" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>1</v>
+      </c>
       <c r="Z99" t="n">
         <v>1</v>
       </c>
-      <c r="AA99" t="n">
-        <v>1</v>
-      </c>
       <c r="AC99" t="n">
         <v>1</v>
       </c>
+      <c r="AD99" t="n">
+        <v>1</v>
+      </c>
       <c r="AF99" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG99" t="inlineStr">
         <is>
@@ -7910,7 +8276,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Posición, desplazamiento y trayectoria</t>
+          <t>Potencia mecánica</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7925,16 +8291,13 @@
         <v>10</v>
       </c>
       <c r="F100" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G100" t="n">
         <v>8.5</v>
       </c>
       <c r="I100" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J100" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L100" t="n">
         <v>9.5</v>
@@ -7948,18 +8311,9 @@
       <c r="P100" t="n">
         <v>1</v>
       </c>
-      <c r="R100" t="n">
-        <v>1</v>
-      </c>
-      <c r="S100" t="n">
-        <v>1</v>
-      </c>
       <c r="U100" t="n">
         <v>1</v>
       </c>
-      <c r="W100" t="n">
-        <v>1</v>
-      </c>
       <c r="Y100" t="n">
         <v>1</v>
       </c>
@@ -7972,8 +8326,11 @@
       <c r="AD100" t="n">
         <v>1</v>
       </c>
+      <c r="AE100" t="n">
+        <v>1</v>
+      </c>
       <c r="AF100" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG100" t="inlineStr">
         <is>
@@ -7989,7 +8346,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Potencia mecánica</t>
+          <t>Presión</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7998,30 +8355,36 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F101" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G101" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H101" t="n">
+        <v>4</v>
       </c>
       <c r="I101" t="n">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="K101" t="n">
+        <v>4</v>
       </c>
       <c r="L101" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M101" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O101" t="n">
         <v>1</v>
       </c>
-      <c r="P101" t="n">
+      <c r="R101" t="n">
         <v>1</v>
       </c>
       <c r="U101" t="n">
@@ -8033,17 +8396,14 @@
       <c r="Z101" t="n">
         <v>1</v>
       </c>
-      <c r="AC101" t="n">
+      <c r="AA101" t="n">
         <v>1</v>
       </c>
       <c r="AD101" t="n">
         <v>1</v>
       </c>
-      <c r="AE101" t="n">
-        <v>1</v>
-      </c>
       <c r="AF101" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG101" t="inlineStr">
         <is>
@@ -8059,7 +8419,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Presión</t>
+          <t>Presión hidrostática y atmosférica</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8074,36 +8434,30 @@
         <v>9</v>
       </c>
       <c r="F102" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G102" t="n">
         <v>6</v>
       </c>
+      <c r="H102" t="n">
+        <v>4</v>
+      </c>
       <c r="I102" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L102" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M102" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O102" t="n">
         <v>1</v>
       </c>
-      <c r="R102" t="n">
-        <v>1</v>
-      </c>
-      <c r="U102" t="n">
-        <v>1</v>
-      </c>
       <c r="Y102" t="n">
         <v>1</v>
       </c>
       <c r="Z102" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA102" t="n">
         <v>1</v>
       </c>
       <c r="AD102" t="n">
@@ -8126,7 +8480,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Presión hidrostática y atmosférica</t>
+          <t>Primera ley de Newton: inercia</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8135,37 +8489,82 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D103" t="n">
+        <v>10</v>
+      </c>
+      <c r="E103" t="n">
         <v>9</v>
       </c>
       <c r="F103" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G103" t="n">
         <v>6</v>
       </c>
+      <c r="H103" t="n">
+        <v>7</v>
+      </c>
       <c r="I103" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="J103" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K103" t="n">
+        <v>2</v>
+      </c>
+      <c r="L103" t="n">
+        <v>9.5</v>
       </c>
       <c r="M103" t="n">
         <v>7</v>
       </c>
+      <c r="N103" t="n">
+        <v>1</v>
+      </c>
       <c r="O103" t="n">
         <v>1</v>
       </c>
+      <c r="P103" t="n">
+        <v>1</v>
+      </c>
+      <c r="R103" t="n">
+        <v>1</v>
+      </c>
+      <c r="S103" t="n">
+        <v>1</v>
+      </c>
+      <c r="U103" t="n">
+        <v>1</v>
+      </c>
+      <c r="V103" t="n">
+        <v>1</v>
+      </c>
+      <c r="W103" t="n">
+        <v>1</v>
+      </c>
       <c r="Y103" t="n">
         <v>1</v>
       </c>
       <c r="Z103" t="n">
         <v>1</v>
       </c>
+      <c r="AB103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>1</v>
+      </c>
       <c r="AD103" t="n">
         <v>1</v>
       </c>
+      <c r="AE103" t="n">
+        <v>1</v>
+      </c>
       <c r="AF103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG103" t="inlineStr">
         <is>
@@ -8181,7 +8580,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Primera ley de Newton: inercia</t>
+          <t>Principio de Arquímedes: empuje</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8190,76 +8589,52 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D104" t="n">
-        <v>10</v>
-      </c>
-      <c r="E104" t="n">
         <v>9</v>
       </c>
       <c r="F104" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G104" t="n">
         <v>6</v>
       </c>
+      <c r="H104" t="n">
+        <v>5</v>
+      </c>
       <c r="I104" t="n">
         <v>8</v>
       </c>
       <c r="J104" t="n">
         <v>7</v>
       </c>
+      <c r="K104" t="n">
+        <v>7</v>
+      </c>
       <c r="L104" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M104" t="n">
         <v>7</v>
       </c>
-      <c r="N104" t="n">
-        <v>1</v>
-      </c>
       <c r="O104" t="n">
         <v>1</v>
       </c>
-      <c r="P104" t="n">
-        <v>1</v>
-      </c>
       <c r="R104" t="n">
         <v>1</v>
       </c>
-      <c r="S104" t="n">
-        <v>1</v>
-      </c>
-      <c r="U104" t="n">
-        <v>1</v>
-      </c>
-      <c r="V104" t="n">
-        <v>1</v>
-      </c>
-      <c r="W104" t="n">
-        <v>1</v>
-      </c>
       <c r="Y104" t="n">
         <v>1</v>
       </c>
       <c r="Z104" t="n">
         <v>1</v>
       </c>
-      <c r="AB104" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC104" t="n">
-        <v>1</v>
-      </c>
       <c r="AD104" t="n">
         <v>1</v>
       </c>
-      <c r="AE104" t="n">
-        <v>1</v>
-      </c>
       <c r="AF104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG104" t="inlineStr">
         <is>
@@ -8275,7 +8650,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Principio de Arquímedes: empuje</t>
+          <t>Hidrodinámica: continuidad y Bernoulli</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8289,34 +8664,16 @@
       <c r="D105" t="n">
         <v>9</v>
       </c>
-      <c r="F105" t="n">
-        <v>8</v>
-      </c>
-      <c r="G105" t="n">
-        <v>6</v>
-      </c>
-      <c r="I105" t="n">
-        <v>8</v>
-      </c>
-      <c r="J105" t="n">
+      <c r="H105" t="n">
         <v>7</v>
       </c>
-      <c r="M105" t="n">
-        <v>7</v>
-      </c>
-      <c r="O105" t="n">
-        <v>1</v>
-      </c>
-      <c r="R105" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y105" t="n">
+      <c r="K105" t="n">
+        <v>5</v>
+      </c>
+      <c r="X105" t="n">
         <v>1</v>
       </c>
       <c r="Z105" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD105" t="n">
         <v>1</v>
       </c>
       <c r="AF105" t="n">
@@ -8336,7 +8693,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Hidrodinámica: continuidad y Bernoulli</t>
+          <t>Principio de Pascal</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8350,14 +8707,23 @@
       <c r="D106" t="n">
         <v>9</v>
       </c>
-      <c r="X106" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z106" t="n">
+      <c r="F106" t="n">
+        <v>8</v>
+      </c>
+      <c r="K106" t="n">
+        <v>7</v>
+      </c>
+      <c r="M106" t="n">
+        <v>7</v>
+      </c>
+      <c r="O106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD106" t="n">
         <v>1</v>
       </c>
       <c r="AF106" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG106" t="inlineStr">
         <is>
@@ -8366,14 +8732,14 @@
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Principio de Pascal</t>
+          <t>Fuentes de luz, propagación y sombras</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8382,25 +8748,64 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D107" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E107" t="n">
+        <v>4</v>
       </c>
       <c r="F107" t="n">
         <v>8</v>
       </c>
+      <c r="G107" t="n">
+        <v>2</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" t="n">
+        <v>2</v>
+      </c>
+      <c r="J107" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K107" t="n">
+        <v>3</v>
+      </c>
+      <c r="L107" t="n">
+        <v>4</v>
+      </c>
       <c r="M107" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="AD107" t="n">
+      <c r="R107" t="n">
+        <v>1</v>
+      </c>
+      <c r="S107" t="n">
+        <v>1</v>
+      </c>
+      <c r="T107" t="n">
+        <v>1</v>
+      </c>
+      <c r="W107" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA107" t="n">
         <v>1</v>
       </c>
       <c r="AF107" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
@@ -8409,14 +8814,14 @@
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Fuentes de luz, propagación y sombras</t>
+          <t>Rapidez y velocidad</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8428,39 +8833,42 @@
         <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>10</v>
-      </c>
-      <c r="E108" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F108" t="n">
         <v>8</v>
       </c>
       <c r="G108" t="n">
+        <v>6</v>
+      </c>
+      <c r="H108" t="n">
         <v>2</v>
       </c>
       <c r="I108" t="n">
+        <v>8</v>
+      </c>
+      <c r="J108" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K108" t="n">
         <v>2</v>
       </c>
-      <c r="J108" t="n">
-        <v>7</v>
-      </c>
-      <c r="K108" t="n">
-        <v>9</v>
+      <c r="L108" t="n">
+        <v>9.5</v>
       </c>
       <c r="M108" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O108" t="n">
         <v>1</v>
       </c>
+      <c r="P108" t="n">
+        <v>1</v>
+      </c>
       <c r="R108" t="n">
         <v>1</v>
       </c>
-      <c r="S108" t="n">
-        <v>1</v>
-      </c>
-      <c r="T108" t="n">
+      <c r="U108" t="n">
         <v>1</v>
       </c>
       <c r="W108" t="n">
@@ -8472,11 +8880,20 @@
       <c r="Z108" t="n">
         <v>1</v>
       </c>
-      <c r="AA108" t="n">
+      <c r="AB108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE108" t="n">
         <v>1</v>
       </c>
       <c r="AF108" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG108" t="inlineStr">
         <is>
@@ -8492,7 +8909,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Rapidez y velocidad</t>
+          <t>Reflexión de la luz</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8501,28 +8918,37 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D109" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E109" t="n">
+        <v>4</v>
       </c>
       <c r="F109" t="n">
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H109" t="n">
+        <v>3</v>
       </c>
       <c r="I109" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K109" t="n">
+        <v>3</v>
       </c>
       <c r="L109" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M109" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O109" t="n">
         <v>1</v>
@@ -8530,12 +8956,15 @@
       <c r="P109" t="n">
         <v>1</v>
       </c>
-      <c r="R109" t="n">
+      <c r="T109" t="n">
         <v>1</v>
       </c>
       <c r="U109" t="n">
         <v>1</v>
       </c>
+      <c r="V109" t="n">
+        <v>1</v>
+      </c>
       <c r="W109" t="n">
         <v>1</v>
       </c>
@@ -8548,9 +8977,6 @@
       <c r="AB109" t="n">
         <v>1</v>
       </c>
-      <c r="AC109" t="n">
-        <v>1</v>
-      </c>
       <c r="AD109" t="n">
         <v>1</v>
       </c>
@@ -8558,7 +8984,7 @@
         <v>1</v>
       </c>
       <c r="AF109" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG109" t="inlineStr">
         <is>
@@ -8574,7 +9000,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Reflexión de la luz</t>
+          <t>Refracción de la luz</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8583,7 +9009,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D110" t="n">
         <v>10</v>
@@ -8595,58 +9021,67 @@
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="H110" t="n">
+        <v>5</v>
       </c>
       <c r="I110" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J110" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K110" t="n">
+        <v>3</v>
+      </c>
+      <c r="L110" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M110" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O110" t="n">
+        <v>1</v>
+      </c>
+      <c r="P110" t="n">
+        <v>1</v>
+      </c>
+      <c r="S110" t="n">
+        <v>1</v>
+      </c>
+      <c r="T110" t="n">
+        <v>1</v>
+      </c>
+      <c r="U110" t="n">
+        <v>1</v>
+      </c>
+      <c r="V110" t="n">
+        <v>1</v>
+      </c>
+      <c r="W110" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF110" t="n">
         <v>7</v>
-      </c>
-      <c r="K110" t="n">
-        <v>9</v>
-      </c>
-      <c r="L110" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M110" t="n">
-        <v>7</v>
-      </c>
-      <c r="O110" t="n">
-        <v>1</v>
-      </c>
-      <c r="P110" t="n">
-        <v>1</v>
-      </c>
-      <c r="T110" t="n">
-        <v>1</v>
-      </c>
-      <c r="U110" t="n">
-        <v>1</v>
-      </c>
-      <c r="V110" t="n">
-        <v>1</v>
-      </c>
-      <c r="W110" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y110" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF110" t="n">
-        <v>4</v>
       </c>
       <c r="AG110" t="inlineStr">
         <is>
@@ -8662,7 +9097,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Refracción de la luz</t>
+          <t>Resistencia equivalente</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8671,34 +9106,22 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D111" t="n">
-        <v>10</v>
-      </c>
-      <c r="E111" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F111" t="n">
         <v>8</v>
       </c>
       <c r="G111" t="n">
-        <v>6</v>
-      </c>
-      <c r="I111" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="J111" t="n">
         <v>7</v>
       </c>
-      <c r="K111" t="n">
-        <v>9</v>
-      </c>
       <c r="L111" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M111" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="O111" t="n">
         <v>1</v>
@@ -8706,18 +9129,9 @@
       <c r="P111" t="n">
         <v>1</v>
       </c>
-      <c r="S111" t="n">
-        <v>1</v>
-      </c>
-      <c r="T111" t="n">
-        <v>1</v>
-      </c>
       <c r="U111" t="n">
         <v>1</v>
       </c>
-      <c r="V111" t="n">
-        <v>1</v>
-      </c>
       <c r="W111" t="n">
         <v>1</v>
       </c>
@@ -8727,20 +9141,14 @@
       <c r="Z111" t="n">
         <v>1</v>
       </c>
-      <c r="AB111" t="n">
-        <v>1</v>
-      </c>
       <c r="AC111" t="n">
         <v>1</v>
       </c>
       <c r="AD111" t="n">
         <v>1</v>
       </c>
-      <c r="AE111" t="n">
-        <v>1</v>
-      </c>
       <c r="AF111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG111" t="inlineStr">
         <is>
@@ -8756,7 +9164,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Resistencia equivalente</t>
+          <t>Segunda ley de Newton</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8765,32 +9173,59 @@
         </is>
       </c>
       <c r="C112" t="n">
+        <v>5</v>
+      </c>
+      <c r="D112" t="n">
+        <v>10</v>
+      </c>
+      <c r="E112" t="n">
         <v>6</v>
       </c>
-      <c r="D112" t="n">
-        <v>11</v>
-      </c>
       <c r="F112" t="n">
+        <v>5</v>
+      </c>
+      <c r="G112" t="n">
+        <v>6</v>
+      </c>
+      <c r="H112" t="n">
+        <v>7</v>
+      </c>
+      <c r="I112" t="n">
         <v>8</v>
       </c>
-      <c r="G112" t="n">
-        <v>8.5</v>
-      </c>
       <c r="J112" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K112" t="n">
+        <v>4</v>
       </c>
       <c r="L112" t="n">
         <v>9.5</v>
       </c>
+      <c r="M112" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N112" t="n">
+        <v>1</v>
+      </c>
       <c r="O112" t="n">
         <v>1</v>
       </c>
       <c r="P112" t="n">
         <v>1</v>
       </c>
+      <c r="R112" t="n">
+        <v>1</v>
+      </c>
+      <c r="S112" t="n">
+        <v>1</v>
+      </c>
       <c r="U112" t="n">
         <v>1</v>
       </c>
+      <c r="V112" t="n">
+        <v>1</v>
+      </c>
       <c r="W112" t="n">
         <v>1</v>
       </c>
@@ -8800,14 +9235,23 @@
       <c r="Z112" t="n">
         <v>1</v>
       </c>
+      <c r="AA112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>1</v>
+      </c>
       <c r="AC112" t="n">
         <v>1</v>
       </c>
       <c r="AD112" t="n">
         <v>1</v>
       </c>
+      <c r="AE112" t="n">
+        <v>1</v>
+      </c>
       <c r="AF112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
@@ -8823,7 +9267,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Segunda ley de Newton</t>
+          <t>Sistema Internacional de Unidades</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8837,29 +9281,26 @@
       <c r="D113" t="n">
         <v>10</v>
       </c>
-      <c r="E113" t="n">
-        <v>6</v>
-      </c>
       <c r="F113" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G113" t="n">
         <v>6</v>
       </c>
-      <c r="I113" t="n">
+      <c r="H113" t="n">
+        <v>7</v>
+      </c>
+      <c r="J113" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K113" t="n">
         <v>8</v>
       </c>
-      <c r="J113" t="n">
-        <v>7</v>
-      </c>
       <c r="L113" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M113" t="n">
-        <v>7</v>
-      </c>
-      <c r="N113" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O113" t="n">
         <v>1</v>
@@ -8867,12 +9308,12 @@
       <c r="P113" t="n">
         <v>1</v>
       </c>
-      <c r="R113" t="n">
-        <v>1</v>
-      </c>
       <c r="S113" t="n">
         <v>1</v>
       </c>
+      <c r="T113" t="n">
+        <v>1</v>
+      </c>
       <c r="U113" t="n">
         <v>1</v>
       </c>
@@ -8888,19 +9329,10 @@
       <c r="Z113" t="n">
         <v>1</v>
       </c>
-      <c r="AA113" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB113" t="n">
-        <v>1</v>
-      </c>
       <c r="AC113" t="n">
         <v>1</v>
       </c>
       <c r="AD113" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE113" t="n">
         <v>1</v>
       </c>
       <c r="AF113" t="n">
@@ -8920,7 +9352,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sistema Internacional de Unidades</t>
+          <t>El sonido como onda mecánica</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8929,28 +9361,37 @@
         </is>
       </c>
       <c r="C114" t="n">
+        <v>4</v>
+      </c>
+      <c r="D114" t="n">
+        <v>11</v>
+      </c>
+      <c r="E114" t="n">
+        <v>8</v>
+      </c>
+      <c r="F114" t="n">
         <v>5</v>
       </c>
-      <c r="D114" t="n">
-        <v>10</v>
-      </c>
-      <c r="F114" t="n">
-        <v>10.5</v>
-      </c>
       <c r="G114" t="n">
+        <v>2</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2</v>
+      </c>
+      <c r="I114" t="n">
         <v>6</v>
       </c>
       <c r="J114" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="K114" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L114" t="n">
         <v>9.5</v>
       </c>
       <c r="M114" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O114" t="n">
         <v>1</v>
@@ -8958,10 +9399,7 @@
       <c r="P114" t="n">
         <v>1</v>
       </c>
-      <c r="S114" t="n">
-        <v>1</v>
-      </c>
-      <c r="T114" t="n">
+      <c r="R114" t="n">
         <v>1</v>
       </c>
       <c r="U114" t="n">
@@ -8973,20 +9411,32 @@
       <c r="W114" t="n">
         <v>1</v>
       </c>
+      <c r="X114" t="n">
+        <v>1</v>
+      </c>
       <c r="Y114" t="n">
         <v>1</v>
       </c>
       <c r="Z114" t="n">
         <v>1</v>
       </c>
+      <c r="AA114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>1</v>
+      </c>
       <c r="AC114" t="n">
         <v>1</v>
       </c>
       <c r="AD114" t="n">
         <v>1</v>
       </c>
+      <c r="AE114" t="n">
+        <v>1</v>
+      </c>
       <c r="AF114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
@@ -9002,7 +9452,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>El sonido como onda mecánica</t>
+          <t>Suma de vectores y componentes rectangulares</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9011,22 +9461,22 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D115" t="n">
-        <v>11</v>
-      </c>
-      <c r="E115" t="n">
+        <v>10</v>
+      </c>
+      <c r="F115" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G115" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H115" t="n">
+        <v>7</v>
+      </c>
+      <c r="I115" t="n">
         <v>8</v>
-      </c>
-      <c r="F115" t="n">
-        <v>8</v>
-      </c>
-      <c r="G115" t="n">
-        <v>2</v>
-      </c>
-      <c r="I115" t="n">
-        <v>6</v>
       </c>
       <c r="J115" t="n">
         <v>7</v>
@@ -9034,9 +9484,6 @@
       <c r="L115" t="n">
         <v>9.5</v>
       </c>
-      <c r="M115" t="n">
-        <v>7</v>
-      </c>
       <c r="O115" t="n">
         <v>1</v>
       </c>
@@ -9049,15 +9496,9 @@
       <c r="U115" t="n">
         <v>1</v>
       </c>
-      <c r="V115" t="n">
-        <v>1</v>
-      </c>
       <c r="W115" t="n">
         <v>1</v>
       </c>
-      <c r="X115" t="n">
-        <v>1</v>
-      </c>
       <c r="Y115" t="n">
         <v>1</v>
       </c>
@@ -9080,7 +9521,7 @@
         <v>1</v>
       </c>
       <c r="AF115" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG115" t="inlineStr">
         <is>
@@ -9096,7 +9537,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Suma de vectores y componentes rectangulares</t>
+          <t>Temperatura y escalas termométricas</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9105,36 +9546,42 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D116" t="n">
         <v>10</v>
       </c>
       <c r="F116" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="G116" t="n">
-        <v>8.5</v>
+        <v>2</v>
+      </c>
+      <c r="H116" t="n">
+        <v>2</v>
       </c>
       <c r="I116" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="J116" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="L116" t="n">
-        <v>9.5</v>
+        <v>4</v>
+      </c>
+      <c r="M116" t="n">
+        <v>2.5</v>
       </c>
       <c r="O116" t="n">
         <v>1</v>
       </c>
-      <c r="P116" t="n">
-        <v>1</v>
-      </c>
       <c r="R116" t="n">
         <v>1</v>
       </c>
-      <c r="U116" t="n">
+      <c r="S116" t="n">
+        <v>1</v>
+      </c>
+      <c r="V116" t="n">
         <v>1</v>
       </c>
       <c r="W116" t="n">
@@ -9146,15 +9593,6 @@
       <c r="Z116" t="n">
         <v>1</v>
       </c>
-      <c r="AA116" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB116" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC116" t="n">
-        <v>1</v>
-      </c>
       <c r="AD116" t="n">
         <v>1</v>
       </c>
@@ -9162,7 +9600,7 @@
         <v>1</v>
       </c>
       <c r="AF116" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG116" t="inlineStr">
         <is>
@@ -9178,7 +9616,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Temperatura y escalas termométricas</t>
+          <t>Tensión superficial y capilaridad</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9187,55 +9625,22 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D117" t="n">
         <v>10</v>
       </c>
       <c r="F117" t="n">
-        <v>8</v>
-      </c>
-      <c r="G117" t="n">
-        <v>2</v>
-      </c>
-      <c r="I117" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J117" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="M117" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="O117" t="n">
         <v>1</v>
       </c>
-      <c r="R117" t="n">
-        <v>1</v>
-      </c>
-      <c r="S117" t="n">
-        <v>1</v>
-      </c>
-      <c r="V117" t="n">
-        <v>1</v>
-      </c>
-      <c r="W117" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y117" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z117" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD117" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE117" t="n">
-        <v>1</v>
-      </c>
       <c r="AF117" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG117" t="inlineStr">
         <is>
@@ -9251,7 +9656,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Tensión superficial y capilaridad</t>
+          <t>Tercera ley de Newton: acción y reacción</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9260,19 +9665,76 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D118" t="n">
         <v>10</v>
       </c>
+      <c r="E118" t="n">
+        <v>9</v>
+      </c>
       <c r="F118" t="n">
         <v>10.5</v>
       </c>
+      <c r="G118" t="n">
+        <v>6</v>
+      </c>
+      <c r="H118" t="n">
+        <v>4</v>
+      </c>
+      <c r="I118" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K118" t="n">
+        <v>4</v>
+      </c>
+      <c r="L118" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M118" t="n">
+        <v>7</v>
+      </c>
+      <c r="N118" t="n">
+        <v>1</v>
+      </c>
       <c r="O118" t="n">
         <v>1</v>
       </c>
+      <c r="P118" t="n">
+        <v>1</v>
+      </c>
+      <c r="R118" t="n">
+        <v>1</v>
+      </c>
+      <c r="U118" t="n">
+        <v>1</v>
+      </c>
+      <c r="V118" t="n">
+        <v>1</v>
+      </c>
+      <c r="W118" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>1</v>
+      </c>
       <c r="AF118" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG118" t="inlineStr">
         <is>
@@ -9288,7 +9750,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Tercera ley de Newton: acción y reacción</t>
+          <t>Características del sonido: tono, intensidad y eco</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9297,53 +9759,44 @@
         </is>
       </c>
       <c r="C119" t="n">
+        <v>2</v>
+      </c>
+      <c r="D119" t="n">
+        <v>11</v>
+      </c>
+      <c r="F119" t="n">
         <v>5</v>
       </c>
-      <c r="D119" t="n">
-        <v>10</v>
-      </c>
-      <c r="E119" t="n">
-        <v>9</v>
-      </c>
-      <c r="F119" t="n">
-        <v>10.5</v>
-      </c>
       <c r="G119" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H119" t="n">
+        <v>2</v>
       </c>
       <c r="I119" t="n">
-        <v>9.5</v>
+        <v>2</v>
+      </c>
+      <c r="J119" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K119" t="n">
+        <v>3</v>
       </c>
       <c r="L119" t="n">
         <v>9.5</v>
       </c>
       <c r="M119" t="n">
-        <v>7</v>
-      </c>
-      <c r="N119" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O119" t="n">
         <v>1</v>
       </c>
-      <c r="P119" t="n">
-        <v>1</v>
-      </c>
-      <c r="R119" t="n">
-        <v>1</v>
-      </c>
       <c r="U119" t="n">
         <v>1</v>
       </c>
-      <c r="V119" t="n">
-        <v>1</v>
-      </c>
       <c r="W119" t="n">
         <v>1</v>
       </c>
-      <c r="Y119" t="n">
-        <v>1</v>
-      </c>
       <c r="Z119" t="n">
         <v>1</v>
       </c>
@@ -9360,7 +9813,7 @@
         <v>1</v>
       </c>
       <c r="AF119" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG119" t="inlineStr">
         <is>
@@ -9376,7 +9829,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Características del sonido: tono, intensidad y eco</t>
+          <t>Torque o momento de fuerza</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9385,47 +9838,47 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D120" t="n">
-        <v>11</v>
-      </c>
-      <c r="F120" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G120" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="H120" t="n">
+        <v>5</v>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
-      </c>
-      <c r="J120" t="n">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="K120" t="n">
+        <v>6</v>
       </c>
       <c r="L120" t="n">
         <v>9.5</v>
       </c>
       <c r="M120" t="n">
-        <v>7</v>
-      </c>
-      <c r="O120" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P120" t="n">
         <v>1</v>
       </c>
       <c r="U120" t="n">
         <v>1</v>
       </c>
-      <c r="W120" t="n">
+      <c r="Y120" t="n">
         <v>1</v>
       </c>
       <c r="Z120" t="n">
         <v>1</v>
       </c>
+      <c r="AA120" t="n">
+        <v>1</v>
+      </c>
       <c r="AB120" t="n">
         <v>1</v>
       </c>
-      <c r="AC120" t="n">
-        <v>1</v>
-      </c>
       <c r="AD120" t="n">
         <v>1</v>
       </c>
@@ -9433,7 +9886,7 @@
         <v>1</v>
       </c>
       <c r="AF120" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG120" t="inlineStr">
         <is>
@@ -9449,7 +9902,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Torque o momento de fuerza</t>
+          <t>Trabajo mecánico</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9458,41 +9911,62 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D121" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="F121" t="n">
+        <v>8</v>
       </c>
       <c r="G121" t="n">
         <v>6</v>
       </c>
       <c r="I121" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="J121" t="n">
+        <v>7</v>
+      </c>
+      <c r="K121" t="n">
+        <v>7</v>
       </c>
       <c r="L121" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M121" t="n">
         <v>7</v>
       </c>
+      <c r="O121" t="n">
+        <v>1</v>
+      </c>
       <c r="P121" t="n">
         <v>1</v>
       </c>
+      <c r="R121" t="n">
+        <v>1</v>
+      </c>
       <c r="U121" t="n">
         <v>1</v>
       </c>
+      <c r="V121" t="n">
+        <v>1</v>
+      </c>
+      <c r="W121" t="n">
+        <v>1</v>
+      </c>
       <c r="Y121" t="n">
         <v>1</v>
       </c>
       <c r="Z121" t="n">
         <v>1</v>
       </c>
-      <c r="AA121" t="n">
-        <v>1</v>
-      </c>
       <c r="AB121" t="n">
         <v>1</v>
       </c>
+      <c r="AC121" t="n">
+        <v>1</v>
+      </c>
       <c r="AD121" t="n">
         <v>1</v>
       </c>
@@ -9500,7 +9974,7 @@
         <v>1</v>
       </c>
       <c r="AF121" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG121" t="inlineStr">
         <is>
@@ -9516,7 +9990,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Trabajo mecánico</t>
+          <t>Transformaciones de la energía</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9525,28 +9999,37 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D122" t="n">
         <v>9</v>
       </c>
+      <c r="E122" t="n">
+        <v>5</v>
+      </c>
       <c r="F122" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G122" t="n">
         <v>6</v>
       </c>
+      <c r="H122" t="n">
+        <v>2</v>
+      </c>
       <c r="I122" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J122" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K122" t="n">
+        <v>2</v>
       </c>
       <c r="L122" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="M122" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O122" t="n">
         <v>1</v>
@@ -9557,6 +10040,9 @@
       <c r="R122" t="n">
         <v>1</v>
       </c>
+      <c r="S122" t="n">
+        <v>1</v>
+      </c>
       <c r="U122" t="n">
         <v>1</v>
       </c>
@@ -9585,7 +10071,7 @@
         <v>1</v>
       </c>
       <c r="AF122" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
@@ -9601,7 +10087,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Transformaciones de la energía</t>
+          <t>Ventaja mecánica</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9610,31 +10096,28 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D123" t="n">
         <v>9</v>
       </c>
-      <c r="E123" t="n">
-        <v>5</v>
-      </c>
       <c r="F123" t="n">
         <v>8</v>
       </c>
       <c r="G123" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="H123" t="n">
+        <v>2</v>
       </c>
       <c r="I123" t="n">
         <v>5</v>
       </c>
       <c r="J123" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K123" t="n">
-        <v>8</v>
-      </c>
-      <c r="L123" t="n">
-        <v>9.5</v>
+        <v>2</v>
       </c>
       <c r="M123" t="n">
         <v>7</v>
@@ -9642,44 +10125,11 @@
       <c r="O123" t="n">
         <v>1</v>
       </c>
-      <c r="P123" t="n">
-        <v>1</v>
-      </c>
-      <c r="R123" t="n">
-        <v>1</v>
-      </c>
-      <c r="S123" t="n">
-        <v>1</v>
-      </c>
-      <c r="U123" t="n">
-        <v>1</v>
-      </c>
-      <c r="V123" t="n">
-        <v>1</v>
-      </c>
-      <c r="W123" t="n">
-        <v>1</v>
-      </c>
       <c r="Y123" t="n">
         <v>1</v>
       </c>
-      <c r="Z123" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB123" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC123" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD123" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE123" t="n">
-        <v>1</v>
-      </c>
       <c r="AF123" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG123" t="inlineStr">
         <is>
@@ -9695,49 +10145,64 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Ventaja mecánica</t>
+          <t>Cuantización de la energía</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D124" t="n">
         <v>9</v>
       </c>
-      <c r="F124" t="n">
-        <v>8</v>
-      </c>
-      <c r="G124" t="n">
-        <v>3</v>
-      </c>
-      <c r="I124" t="n">
-        <v>5</v>
-      </c>
       <c r="M124" t="n">
-        <v>7</v>
-      </c>
-      <c r="O124" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V124" t="n">
+        <v>1</v>
+      </c>
+      <c r="W124" t="n">
+        <v>1</v>
+      </c>
+      <c r="X124" t="n">
         <v>1</v>
       </c>
       <c r="Y124" t="n">
         <v>1</v>
       </c>
+      <c r="Z124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>1</v>
+      </c>
       <c r="AF124" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10551,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Capacitancia y condensadores</t>
+          <t>Observación astronómica en distintas longitudes de onda</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10095,30 +10560,12 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D131" t="n">
-        <v>9</v>
-      </c>
-      <c r="F131" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="O131" t="n">
-        <v>1</v>
-      </c>
-      <c r="X131" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD131" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z131" t="n">
         <v>1</v>
       </c>
       <c r="AF131" t="n">
@@ -10126,19 +10573,19 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Cuantización de la energía</t>
+          <t>Capacitancia y condensadores</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10152,13 +10599,10 @@
       <c r="D132" t="n">
         <v>9</v>
       </c>
-      <c r="M132" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V132" t="n">
-        <v>1</v>
-      </c>
-      <c r="W132" t="n">
+      <c r="F132" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O132" t="n">
         <v>1</v>
       </c>
       <c r="X132" t="n">
@@ -10167,22 +10611,13 @@
       <c r="Y132" t="n">
         <v>1</v>
       </c>
-      <c r="Z132" t="n">
-        <v>1</v>
-      </c>
       <c r="AA132" t="n">
         <v>1</v>
       </c>
       <c r="AB132" t="n">
         <v>1</v>
       </c>
-      <c r="AC132" t="n">
-        <v>1</v>
-      </c>
       <c r="AD132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE132" t="n">
         <v>1</v>
       </c>
       <c r="AF132" t="n">
@@ -10562,7 +10997,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Procesos termodinámicos</t>
+          <t>Energía potencial y potencial eléctrico</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10571,18 +11006,39 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D139" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F139" t="n">
         <v>10.5</v>
       </c>
+      <c r="G139" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H139" t="n">
+        <v>7</v>
+      </c>
+      <c r="L139" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O139" t="n">
         <v>1</v>
       </c>
-      <c r="X139" t="n">
+      <c r="P139" t="n">
+        <v>1</v>
+      </c>
+      <c r="U139" t="n">
+        <v>1</v>
+      </c>
+      <c r="W139" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z139" t="n">
         <v>1</v>
       </c>
       <c r="AA139" t="n">
@@ -10591,15 +11047,21 @@
       <c r="AB139" t="n">
         <v>1</v>
       </c>
+      <c r="AC139" t="n">
+        <v>1</v>
+      </c>
       <c r="AD139" t="n">
         <v>1</v>
       </c>
+      <c r="AE139" t="n">
+        <v>1</v>
+      </c>
       <c r="AF139" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH139" t="inlineStr">
@@ -10611,7 +11073,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Radiación térmica y cuerpo negro</t>
+          <t>Procesos termodinámicos</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10620,40 +11082,31 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D140" t="n">
-        <v>10</v>
-      </c>
-      <c r="J140" t="n">
-        <v>7</v>
-      </c>
-      <c r="L140" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="U140" t="n">
-        <v>1</v>
-      </c>
-      <c r="W140" t="n">
+        <v>9</v>
+      </c>
+      <c r="F140" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O140" t="n">
         <v>1</v>
       </c>
       <c r="X140" t="n">
         <v>1</v>
       </c>
-      <c r="Y140" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z140" t="n">
+      <c r="AA140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB140" t="n">
         <v>1</v>
       </c>
       <c r="AD140" t="n">
         <v>1</v>
       </c>
-      <c r="AE140" t="n">
-        <v>1</v>
-      </c>
       <c r="AF140" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG140" t="inlineStr">
         <is>
@@ -10669,7 +11122,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Reflexión interna total</t>
+          <t>Radiación térmica y cuerpo negro</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10683,13 +11136,28 @@
       <c r="D141" t="n">
         <v>10</v>
       </c>
+      <c r="H141" t="n">
+        <v>7</v>
+      </c>
+      <c r="J141" t="n">
+        <v>7</v>
+      </c>
       <c r="K141" t="n">
-        <v>9</v>
-      </c>
-      <c r="T141" t="n">
+        <v>6</v>
+      </c>
+      <c r="L141" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U141" t="n">
+        <v>1</v>
+      </c>
+      <c r="W141" t="n">
         <v>1</v>
       </c>
       <c r="X141" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y141" t="n">
         <v>1</v>
       </c>
       <c r="Z141" t="n">
@@ -10731,6 +11199,9 @@
       </c>
       <c r="D142" t="n">
         <v>9</v>
+      </c>
+      <c r="K142" t="n">
+        <v>7</v>
       </c>
       <c r="X142" t="n">
         <v>1</v>

--- a/internacional/Contraste_fisica.xlsx
+++ b/internacional/Contraste_fisica.xlsx
@@ -2523,7 +2523,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Reflexión interna total</t>
+          <t>Rapidez de la luz</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2537,21 +2537,45 @@
       <c r="D26" t="n">
         <v>10</v>
       </c>
+      <c r="G26" t="n">
+        <v>6</v>
+      </c>
       <c r="H26" t="n">
         <v>7</v>
       </c>
       <c r="K26" t="n">
         <v>9</v>
       </c>
+      <c r="L26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M26" t="n">
+        <v>7</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
-      <c r="X26" t="n">
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
+      <c r="AB26" t="n">
+        <v>1</v>
+      </c>
       <c r="AD26" t="n">
         <v>1</v>
       </c>
@@ -2559,23 +2583,23 @@
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Relaciones presión-volumen-temperatura en gases</t>
+          <t>Reflexión interna total</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2584,42 +2608,24 @@
         </is>
       </c>
       <c r="C27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="H27" t="n">
+        <v>7</v>
+      </c>
+      <c r="K27" t="n">
         <v>9</v>
       </c>
-      <c r="D27" t="n">
-        <v>9</v>
-      </c>
-      <c r="F27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G27" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>7</v>
-      </c>
-      <c r="M27" t="n">
-        <v>7</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="T27" t="n">
         <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
       </c>
-      <c r="Y27" t="n">
-        <v>1</v>
-      </c>
       <c r="Z27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB27" t="n">
         <v>1</v>
       </c>
       <c r="AD27" t="n">
@@ -2633,19 +2639,19 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Segunda ley de la termodinámica</t>
+          <t>Relaciones presión-volumen-temperatura en gases</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2654,7 +2660,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
         <v>9</v>
@@ -2662,22 +2668,19 @@
       <c r="F28" t="n">
         <v>10.5</v>
       </c>
-      <c r="I28" t="n">
-        <v>9.5</v>
+      <c r="G28" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>7</v>
       </c>
       <c r="M28" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
-      <c r="W28" t="n">
+      <c r="P28" t="n">
         <v>1</v>
       </c>
       <c r="X28" t="n">
@@ -2686,18 +2689,27 @@
       <c r="Y28" t="n">
         <v>1</v>
       </c>
+      <c r="Z28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1</v>
+      </c>
       <c r="AB28" t="n">
         <v>1</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AD28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -2709,7 +2721,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Semiconductores y electrónica básica</t>
+          <t>Segunda ley de la termodinámica</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2718,7 +2730,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
         <v>9</v>
@@ -2726,49 +2738,34 @@
       <c r="F29" t="n">
         <v>10.5</v>
       </c>
-      <c r="G29" t="n">
-        <v>8.5</v>
-      </c>
       <c r="I29" t="n">
         <v>9.5</v>
       </c>
-      <c r="J29" t="n">
-        <v>7</v>
-      </c>
-      <c r="L29" t="n">
-        <v>11</v>
+      <c r="M29" t="n">
+        <v>9.5</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
       </c>
-      <c r="P29" t="n">
-        <v>1</v>
-      </c>
       <c r="R29" t="n">
         <v>1</v>
       </c>
-      <c r="S29" t="n">
-        <v>1</v>
-      </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
-      <c r="Z29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="n">
+      <c r="Y29" t="n">
         <v>1</v>
       </c>
       <c r="AB29" t="n">
         <v>1</v>
       </c>
       <c r="AC29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD29" t="n">
         <v>1</v>
       </c>
       <c r="AF29" t="n">
@@ -2776,7 +2773,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -2788,7 +2785,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Superposición e interferencia de ondas</t>
+          <t>Semiconductores y electrónica básica</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2797,36 +2794,42 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F30" t="n">
         <v>10.5</v>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I30" t="n">
         <v>9.5</v>
       </c>
-      <c r="M30" t="n">
-        <v>9.5</v>
+      <c r="J30" t="n">
+        <v>7</v>
+      </c>
+      <c r="L30" t="n">
+        <v>11</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
       </c>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
       <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="V30" t="n">
-        <v>1</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y30" t="n">
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
         <v>1</v>
       </c>
       <c r="Z30" t="n">
@@ -2844,27 +2847,24 @@
       <c r="AD30" t="n">
         <v>1</v>
       </c>
-      <c r="AE30" t="n">
-        <v>1</v>
-      </c>
       <c r="AF30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gas ideal y teoría cinética</t>
+          <t>Superposición e interferencia de ondas</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F31" t="n">
         <v>10.5</v>
@@ -2887,18 +2887,12 @@
       <c r="I31" t="n">
         <v>9.5</v>
       </c>
-      <c r="J31" t="n">
-        <v>2.5</v>
-      </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>9.5</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
       </c>
-      <c r="P31" t="n">
-        <v>1</v>
-      </c>
       <c r="R31" t="n">
         <v>1</v>
       </c>
@@ -2930,58 +2924,58 @@
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Rapidez de la luz</t>
+          <t>Gas ideal y teoría cinética</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="F32" t="n">
+        <v>10.5</v>
       </c>
       <c r="G32" t="n">
         <v>6</v>
       </c>
-      <c r="H32" t="n">
-        <v>7</v>
-      </c>
-      <c r="K32" t="n">
-        <v>9</v>
-      </c>
-      <c r="L32" t="n">
-        <v>7.5</v>
+      <c r="I32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.5</v>
       </c>
       <c r="M32" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="T32" t="n">
-        <v>1</v>
-      </c>
-      <c r="U32" t="n">
+      <c r="R32" t="n">
         <v>1</v>
       </c>
       <c r="V32" t="n">
@@ -2996,9 +2990,15 @@
       <c r="Z32" t="n">
         <v>1</v>
       </c>
+      <c r="AA32" t="n">
+        <v>1</v>
+      </c>
       <c r="AB32" t="n">
         <v>1</v>
       </c>
+      <c r="AC32" t="n">
+        <v>1</v>
+      </c>
       <c r="AD32" t="n">
         <v>1</v>
       </c>
@@ -3006,16 +3006,16 @@
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
           <t>alineado</t>
-        </is>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>tardio</t>
         </is>
       </c>
     </row>

--- a/internacional/Contraste_fisica.xlsx
+++ b/internacional/Contraste_fisica.xlsx
@@ -1852,7 +1852,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lentes delgadas e imágenes</t>
+          <t>Inducción electromagnética: Faraday y Lenz</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1861,53 +1861,62 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
         <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
-      </c>
-      <c r="H18" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K18" t="n">
         <v>9</v>
       </c>
-      <c r="L18" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
       </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
         <v>1</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
       <c r="Y18" t="n">
         <v>1</v>
       </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
       <c r="AB18" t="n">
         <v>1</v>
       </c>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
       <c r="AD18" t="n">
         <v>1</v>
       </c>
@@ -1915,23 +1924,23 @@
         <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ley de Coulomb</t>
+          <t>Lentes delgadas e imágenes</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1940,50 +1949,53 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
         <v>8</v>
       </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>9</v>
       </c>
       <c r="L19" t="n">
         <v>9.5</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
       </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
       <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="V19" t="n">
-        <v>1</v>
-      </c>
       <c r="W19" t="n">
         <v>1</v>
       </c>
       <c r="Y19" t="n">
         <v>1</v>
       </c>
-      <c r="Z19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1</v>
-      </c>
       <c r="AB19" t="n">
         <v>1</v>
       </c>
-      <c r="AC19" t="n">
-        <v>1</v>
-      </c>
       <c r="AD19" t="n">
         <v>1</v>
       </c>
@@ -1991,11 +2003,11 @@
         <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -2007,7 +2019,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ley de Ohm</t>
+          <t>Ley de Coulomb</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2016,31 +2028,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F20" t="n">
         <v>8</v>
       </c>
-      <c r="G20" t="n">
-        <v>6</v>
-      </c>
-      <c r="H20" t="n">
-        <v>7</v>
-      </c>
-      <c r="I20" t="n">
-        <v>7</v>
-      </c>
       <c r="J20" t="n">
         <v>7</v>
       </c>
-      <c r="K20" t="n">
-        <v>8</v>
-      </c>
       <c r="L20" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="M20" t="n">
         <v>7</v>
@@ -2048,21 +2048,15 @@
       <c r="O20" t="n">
         <v>1</v>
       </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
       <c r="U20" t="n">
         <v>1</v>
       </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
       <c r="W20" t="n">
         <v>1</v>
       </c>
-      <c r="X20" t="n">
-        <v>1</v>
-      </c>
       <c r="Y20" t="n">
         <v>1</v>
       </c>
@@ -2085,7 +2079,7 @@
         <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -2094,7 +2088,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
@@ -3314,55 +3308,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Fuentes de energía renovables y no renovables</t>
+          <t>Modelo estándar de partículas</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
-      </c>
-      <c r="F37" t="n">
-        <v>5</v>
-      </c>
-      <c r="G37" t="n">
-        <v>6</v>
-      </c>
-      <c r="H37" t="n">
-        <v>3</v>
-      </c>
-      <c r="I37" t="n">
-        <v>8</v>
-      </c>
-      <c r="J37" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2</v>
-      </c>
-      <c r="L37" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="M37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="V37" t="n">
         <v>1</v>
@@ -3373,127 +3334,61 @@
       <c r="X37" t="n">
         <v>1</v>
       </c>
-      <c r="Y37" t="n">
-        <v>1</v>
-      </c>
       <c r="Z37" t="n">
         <v>1</v>
       </c>
+      <c r="AA37" t="n">
+        <v>1</v>
+      </c>
       <c r="AC37" t="n">
         <v>1</v>
       </c>
       <c r="AD37" t="n">
         <v>1</v>
       </c>
-      <c r="AE37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>2</v>
-      </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Inducción electromagnética: Faraday y Lenz</t>
+          <t>Momento angular y su conservación</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>incierto</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>4</v>
-      </c>
-      <c r="D38" t="n">
-        <v>9</v>
-      </c>
-      <c r="F38" t="n">
-        <v>8</v>
-      </c>
-      <c r="G38" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I38" t="n">
-        <v>7</v>
-      </c>
-      <c r="J38" t="n">
-        <v>9</v>
-      </c>
-      <c r="M38" t="n">
-        <v>7</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1</v>
+          <t>no_aplica</t>
+        </is>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
-      <c r="AA38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1</v>
-      </c>
       <c r="AE38" t="n">
         <v>1</v>
       </c>
-      <c r="AF38" t="n">
-        <v>11</v>
-      </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Momento angular y su conservación</t>
+          <t>Niveles de energía atómicos y espectros</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3501,15 +3396,66 @@
           <t>no_aplica</t>
         </is>
       </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="F39" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>9</v>
+      </c>
+      <c r="M39" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1</v>
+      </c>
       <c r="Z39" t="n">
         <v>1</v>
       </c>
+      <c r="AA39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1</v>
+      </c>
       <c r="AE39" t="n">
         <v>1</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -3521,31 +3467,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Niveles de energía atómicos y espectros</t>
+          <t>Calentamiento y enfriamiento</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G40" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H40" t="n">
+        <v>7</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>9</v>
+        <v>4.5</v>
+      </c>
+      <c r="L40" t="n">
+        <v>4</v>
       </c>
       <c r="M40" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
@@ -3553,38 +3511,26 @@
       <c r="P40" t="n">
         <v>1</v>
       </c>
-      <c r="S40" t="n">
-        <v>1</v>
-      </c>
-      <c r="V40" t="n">
+      <c r="U40" t="n">
         <v>1</v>
       </c>
       <c r="W40" t="n">
         <v>1</v>
       </c>
-      <c r="X40" t="n">
-        <v>1</v>
-      </c>
       <c r="Y40" t="n">
         <v>1</v>
       </c>
       <c r="Z40" t="n">
         <v>1</v>
       </c>
-      <c r="AA40" t="n">
-        <v>1</v>
-      </c>
       <c r="AB40" t="n">
         <v>1</v>
       </c>
-      <c r="AC40" t="n">
-        <v>1</v>
-      </c>
       <c r="AD40" t="n">
         <v>1</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1</v>
+      <c r="AF40" t="n">
+        <v>2</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
@@ -3593,14 +3539,14 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Calentamiento y enfriamiento</t>
+          <t>Dinámica y energía de rotación</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3609,61 +3555,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>9</v>
-      </c>
-      <c r="E41" t="n">
-        <v>2</v>
-      </c>
-      <c r="F41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="n">
         <v>8</v>
-      </c>
-      <c r="G41" t="n">
-        <v>6</v>
-      </c>
-      <c r="H41" t="n">
-        <v>7</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L41" t="n">
-        <v>4</v>
-      </c>
-      <c r="M41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
@@ -3679,7 +3580,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Dinámica y energía de rotación</t>
+          <t>Movimiento, reposo y tipos de trayectoria</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3688,20 +3589,53 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>6</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
       <c r="Z42" t="n">
         <v>1</v>
       </c>
+      <c r="AC42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1</v>
+      </c>
       <c r="AF42" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
@@ -3713,7 +3647,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Movimiento, reposo y tipos de trayectoria</t>
+          <t>Fuentes de luz, propagación y sombras</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3724,11 +3658,17 @@
       <c r="C43" t="n">
         <v>2</v>
       </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
       <c r="E43" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" t="n">
+        <v>8</v>
+      </c>
+      <c r="G43" t="n">
         <v>2</v>
-      </c>
-      <c r="G43" t="n">
-        <v>6</v>
       </c>
       <c r="H43" t="n">
         <v>2</v>
@@ -3740,27 +3680,36 @@
         <v>4.5</v>
       </c>
       <c r="K43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L43" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M43" t="n">
-        <v>7</v>
-      </c>
-      <c r="P43" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y43" t="n">
         <v>1</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
-      <c r="AC43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD43" t="n">
+      <c r="AA43" t="n">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
@@ -3768,7 +3717,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -3780,7 +3729,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Fuentes de luz, propagación y sombras</t>
+          <t>El sonido se produce por vibraciones</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3791,11 +3740,8 @@
       <c r="C44" t="n">
         <v>2</v>
       </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
@@ -3810,13 +3756,13 @@
         <v>2</v>
       </c>
       <c r="J44" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K44" t="n">
         <v>3</v>
       </c>
       <c r="L44" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="M44" t="n">
         <v>2.5</v>
@@ -3824,16 +3770,7 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
-      <c r="R44" t="n">
-        <v>1</v>
-      </c>
-      <c r="S44" t="n">
-        <v>1</v>
-      </c>
-      <c r="T44" t="n">
-        <v>1</v>
-      </c>
-      <c r="W44" t="n">
+      <c r="U44" t="n">
         <v>1</v>
       </c>
       <c r="Y44" t="n">
@@ -3842,7 +3779,16 @@
       <c r="Z44" t="n">
         <v>1</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AB44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE44" t="n">
         <v>1</v>
       </c>
       <c r="AF44" t="n">
@@ -3850,7 +3796,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
@@ -3862,50 +3808,77 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>El sonido se produce por vibraciones</t>
+          <t>Absorción de radiación y efecto invernadero</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F45" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="K45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L45" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M45" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
       </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
       <c r="U45" t="n">
         <v>1</v>
       </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1</v>
+      </c>
       <c r="Y45" t="n">
         <v>1</v>
       </c>
@@ -3918,30 +3891,24 @@
       <c r="AC45" t="n">
         <v>1</v>
       </c>
-      <c r="AD45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1</v>
-      </c>
       <c r="AF45" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Absorción de radiación y efecto invernadero</t>
+          <t>Aceleración</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3950,14 +3917,11 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
         <v>10</v>
       </c>
-      <c r="E46" t="n">
-        <v>9</v>
-      </c>
       <c r="F46" t="n">
         <v>10.5</v>
       </c>
@@ -3965,68 +3929,65 @@
         <v>8.5</v>
       </c>
       <c r="H46" t="n">
+        <v>4</v>
+      </c>
+      <c r="I46" t="n">
+        <v>8</v>
+      </c>
+      <c r="J46" t="n">
         <v>7</v>
       </c>
-      <c r="I46" t="n">
-        <v>10</v>
-      </c>
-      <c r="J46" t="n">
-        <v>9</v>
-      </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
+        <v>6</v>
+      </c>
+      <c r="M46" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="n">
         <v>5</v>
       </c>
-      <c r="L46" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M46" t="n">
-        <v>7</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
-      <c r="S46" t="n">
-        <v>1</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>7</v>
-      </c>
       <c r="AG46" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -4034,14 +3995,14 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Aceleración</t>
+          <t>Aplicaciones de las leyes de Newton</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4050,76 +4011,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
         <v>10</v>
       </c>
-      <c r="F47" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G47" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H47" t="n">
-        <v>4</v>
-      </c>
-      <c r="I47" t="n">
+      <c r="W47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="n">
         <v>8</v>
-      </c>
-      <c r="J47" t="n">
-        <v>7</v>
-      </c>
-      <c r="L47" t="n">
-        <v>6</v>
-      </c>
-      <c r="M47" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
-      <c r="S47" t="n">
-        <v>1</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>5</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
@@ -4135,7 +4045,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Aplicaciones de las leyes de Newton</t>
+          <t>Caída libre</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4144,21 +4054,60 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
         <v>10</v>
       </c>
+      <c r="G48" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>7</v>
+      </c>
+      <c r="I48" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J48" t="n">
+        <v>7</v>
+      </c>
+      <c r="L48" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M48" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
       <c r="W48" t="n">
         <v>1</v>
       </c>
+      <c r="Y48" t="n">
+        <v>1</v>
+      </c>
       <c r="Z48" t="n">
         <v>1</v>
       </c>
-      <c r="AB48" t="n">
-        <v>1</v>
-      </c>
       <c r="AC48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE48" t="n">
         <v>1</v>
       </c>
       <c r="AF48" t="n">
@@ -4178,7 +4127,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Caída libre</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4187,28 +4136,40 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2</v>
       </c>
       <c r="L49" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M49" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -4216,9 +4177,6 @@
       <c r="R49" t="n">
         <v>1</v>
       </c>
-      <c r="S49" t="n">
-        <v>1</v>
-      </c>
       <c r="U49" t="n">
         <v>1</v>
       </c>
@@ -4228,23 +4186,29 @@
       <c r="W49" t="n">
         <v>1</v>
       </c>
+      <c r="X49" t="n">
+        <v>1</v>
+      </c>
       <c r="Y49" t="n">
         <v>1</v>
       </c>
       <c r="Z49" t="n">
         <v>1</v>
       </c>
+      <c r="AA49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1</v>
+      </c>
       <c r="AC49" t="n">
         <v>1</v>
       </c>
       <c r="AD49" t="n">
         <v>1</v>
       </c>
-      <c r="AE49" t="n">
-        <v>1</v>
-      </c>
       <c r="AF49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
@@ -4260,7 +4224,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Campo magnético y magnetismo terrestre</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4269,37 +4233,31 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
         <v>9</v>
       </c>
-      <c r="E50" t="n">
-        <v>2</v>
-      </c>
       <c r="F50" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H50" t="n">
         <v>2</v>
       </c>
       <c r="I50" t="n">
+        <v>7</v>
+      </c>
+      <c r="J50" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L50" t="n">
         <v>3</v>
       </c>
-      <c r="J50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2</v>
-      </c>
-      <c r="L50" t="n">
-        <v>4</v>
-      </c>
       <c r="M50" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O50" t="n">
         <v>1</v>
@@ -4310,6 +4268,9 @@
       <c r="R50" t="n">
         <v>1</v>
       </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
       <c r="U50" t="n">
         <v>1</v>
       </c>
@@ -4319,9 +4280,6 @@
       <c r="W50" t="n">
         <v>1</v>
       </c>
-      <c r="X50" t="n">
-        <v>1</v>
-      </c>
       <c r="Y50" t="n">
         <v>1</v>
       </c>
@@ -4340,8 +4298,11 @@
       <c r="AD50" t="n">
         <v>1</v>
       </c>
+      <c r="AE50" t="n">
+        <v>1</v>
+      </c>
       <c r="AF50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
@@ -4357,7 +4318,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Campo magnético y magnetismo terrestre</t>
+          <t>Capacidad calorífica y calor específico</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4366,76 +4327,55 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
         <v>9</v>
       </c>
       <c r="F51" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>7</v>
+      </c>
+      <c r="J51" t="n">
+        <v>7</v>
+      </c>
+      <c r="L51" t="n">
+        <v>4</v>
+      </c>
+      <c r="M51" t="n">
+        <v>7</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF51" t="n">
         <v>6</v>
-      </c>
-      <c r="H51" t="n">
-        <v>2</v>
-      </c>
-      <c r="I51" t="n">
-        <v>7</v>
-      </c>
-      <c r="J51" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L51" t="n">
-        <v>3</v>
-      </c>
-      <c r="M51" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1</v>
-      </c>
-      <c r="P51" t="n">
-        <v>1</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
-      <c r="S51" t="n">
-        <v>1</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>5</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
@@ -4451,7 +4391,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Capacidad calorífica y calor específico</t>
+          <t>Centro de gravedad y estabilidad</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4460,55 +4400,34 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>9</v>
-      </c>
-      <c r="F52" t="n">
-        <v>8</v>
-      </c>
-      <c r="G52" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H52" t="n">
-        <v>7</v>
-      </c>
-      <c r="J52" t="n">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2</v>
       </c>
       <c r="L52" t="n">
-        <v>4</v>
-      </c>
-      <c r="M52" t="n">
-        <v>7</v>
-      </c>
-      <c r="O52" t="n">
-        <v>1</v>
-      </c>
-      <c r="P52" t="n">
-        <v>1</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y52" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="U52" t="n">
         <v>1</v>
       </c>
       <c r="Z52" t="n">
         <v>1</v>
       </c>
+      <c r="AA52" t="n">
+        <v>1</v>
+      </c>
       <c r="AB52" t="n">
         <v>1</v>
       </c>
-      <c r="AC52" t="n">
-        <v>1</v>
-      </c>
       <c r="AD52" t="n">
         <v>1</v>
       </c>
       <c r="AF52" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -4517,14 +4436,14 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Centro de gravedad y estabilidad</t>
+          <t>Circuito eléctrico simple</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4536,32 +4455,68 @@
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E53" t="n">
+        <v>5</v>
+      </c>
+      <c r="F53" t="n">
+        <v>8</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" t="n">
+        <v>3</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2</v>
+      </c>
+      <c r="J53" t="n">
+        <v>4.5</v>
       </c>
       <c r="K53" t="n">
+        <v>5</v>
+      </c>
+      <c r="L53" t="n">
+        <v>5</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="n">
         <v>2</v>
       </c>
-      <c r="L53" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>10</v>
-      </c>
       <c r="AG53" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -4569,14 +4524,14 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Circuito eléctrico simple</t>
+          <t>Circuitos en serie y en paralelo</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4585,28 +4540,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
         <v>9</v>
       </c>
-      <c r="E54" t="n">
-        <v>5</v>
-      </c>
       <c r="F54" t="n">
         <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H54" t="n">
+        <v>7</v>
+      </c>
+      <c r="I54" t="n">
         <v>3</v>
       </c>
-      <c r="I54" t="n">
-        <v>2</v>
-      </c>
       <c r="J54" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K54" t="n">
         <v>5</v>
@@ -4638,9 +4590,6 @@
       <c r="AB54" t="n">
         <v>1</v>
       </c>
-      <c r="AC54" t="n">
-        <v>1</v>
-      </c>
       <c r="AD54" t="n">
         <v>1</v>
       </c>
@@ -4648,7 +4597,7 @@
         <v>1</v>
       </c>
       <c r="AF54" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
@@ -4664,7 +4613,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Circuitos en serie y en paralelo</t>
+          <t>Color y dispersión de la luz</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4673,10 +4622,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F55" t="n">
         <v>8</v>
@@ -4685,33 +4634,27 @@
         <v>6</v>
       </c>
       <c r="H55" t="n">
-        <v>7</v>
-      </c>
-      <c r="I55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>7</v>
       </c>
       <c r="K55" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L55" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="M55" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
-      <c r="P55" t="n">
-        <v>1</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1</v>
-      </c>
-      <c r="W55" t="n">
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="Y55" t="n">
@@ -4723,14 +4666,11 @@
       <c r="AB55" t="n">
         <v>1</v>
       </c>
-      <c r="AD55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE55" t="n">
+      <c r="AC55" t="n">
         <v>1</v>
       </c>
       <c r="AF55" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -4746,7 +4686,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Color y dispersión de la luz</t>
+          <t>Conductores y aislantes eléctricos</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4755,39 +4695,51 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E56" t="n">
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H56" t="n">
+        <v>4</v>
+      </c>
+      <c r="I56" t="n">
         <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>7</v>
       </c>
       <c r="K56" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L56" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M56" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
       </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
       <c r="S56" t="n">
         <v>1</v>
       </c>
-      <c r="T56" t="n">
+      <c r="U56" t="n">
+        <v>1</v>
+      </c>
+      <c r="X56" t="n">
         <v>1</v>
       </c>
       <c r="Y56" t="n">
@@ -4799,11 +4751,11 @@
       <c r="AB56" t="n">
         <v>1</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AD56" t="n">
         <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -4819,7 +4771,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Conductores y aislantes eléctricos</t>
+          <t>Conservación de la energía</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4828,67 +4780,82 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F57" t="n">
         <v>8</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H57" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J57" t="n">
         <v>7</v>
       </c>
       <c r="K57" t="n">
+        <v>4</v>
+      </c>
+      <c r="L57" t="n">
+        <v>6</v>
+      </c>
+      <c r="M57" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF57" t="n">
         <v>5</v>
-      </c>
-      <c r="L57" t="n">
-        <v>5</v>
-      </c>
-      <c r="M57" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O57" t="n">
-        <v>1</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1</v>
-      </c>
-      <c r="S57" t="n">
-        <v>1</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1</v>
-      </c>
-      <c r="X57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>4</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
@@ -4904,7 +4871,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Conservación de la energía</t>
+          <t>Conservación de la energía mecánica</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4918,17 +4885,11 @@
       <c r="D58" t="n">
         <v>10</v>
       </c>
-      <c r="E58" t="n">
-        <v>8</v>
-      </c>
       <c r="F58" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G58" t="n">
-        <v>6</v>
-      </c>
-      <c r="H58" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="I58" t="n">
         <v>8</v>
@@ -4936,14 +4897,11 @@
       <c r="J58" t="n">
         <v>7</v>
       </c>
-      <c r="K58" t="n">
-        <v>4</v>
-      </c>
       <c r="L58" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="M58" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
@@ -4954,16 +4912,7 @@
       <c r="R58" t="n">
         <v>1</v>
       </c>
-      <c r="S58" t="n">
-        <v>1</v>
-      </c>
       <c r="U58" t="n">
-        <v>1</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1</v>
-      </c>
-      <c r="W58" t="n">
         <v>1</v>
       </c>
       <c r="Y58" t="n">
@@ -5004,7 +4953,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Conservación de la energía mecánica</t>
+          <t>Conservación del momento lineal</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5013,7 +4962,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D59" t="n">
         <v>10</v>
@@ -5024,53 +4973,44 @@
       <c r="G59" t="n">
         <v>8.5</v>
       </c>
-      <c r="I59" t="n">
+      <c r="L59" t="n">
+        <v>11</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF59" t="n">
         <v>8</v>
-      </c>
-      <c r="J59" t="n">
-        <v>7</v>
-      </c>
-      <c r="L59" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M59" t="n">
-        <v>7</v>
-      </c>
-      <c r="O59" t="n">
-        <v>1</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>5</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
@@ -5086,7 +5026,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Conservación del momento lineal</t>
+          <t>Corriente, voltaje y resistencia</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5095,19 +5035,34 @@
         </is>
       </c>
       <c r="C60" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" t="n">
+        <v>9</v>
+      </c>
+      <c r="F60" t="n">
         <v>8</v>
       </c>
-      <c r="D60" t="n">
-        <v>10</v>
-      </c>
-      <c r="F60" t="n">
-        <v>10.5</v>
-      </c>
       <c r="G60" t="n">
-        <v>8.5</v>
+        <v>4</v>
+      </c>
+      <c r="H60" t="n">
+        <v>7</v>
+      </c>
+      <c r="I60" t="n">
+        <v>3</v>
+      </c>
+      <c r="J60" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>5</v>
       </c>
       <c r="L60" t="n">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="M60" t="n">
+        <v>7</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
@@ -5115,9 +5070,15 @@
       <c r="P60" t="n">
         <v>1</v>
       </c>
+      <c r="R60" t="n">
+        <v>1</v>
+      </c>
       <c r="U60" t="n">
         <v>1</v>
       </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
       <c r="W60" t="n">
         <v>1</v>
       </c>
@@ -5143,7 +5104,7 @@
         <v>1</v>
       </c>
       <c r="AF60" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
@@ -5159,7 +5120,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Corriente, voltaje y resistencia</t>
+          <t>Expansión del universo y Big Bang</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5168,76 +5129,73 @@
         </is>
       </c>
       <c r="C61" t="n">
+        <v>5</v>
+      </c>
+      <c r="D61" t="n">
+        <v>11</v>
+      </c>
+      <c r="E61" t="n">
+        <v>9</v>
+      </c>
+      <c r="F61" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H61" t="n">
         <v>4</v>
       </c>
-      <c r="D61" t="n">
-        <v>9</v>
-      </c>
-      <c r="F61" t="n">
+      <c r="I61" t="n">
+        <v>10</v>
+      </c>
+      <c r="J61" t="n">
+        <v>7</v>
+      </c>
+      <c r="K61" t="n">
         <v>8</v>
       </c>
-      <c r="G61" t="n">
-        <v>4</v>
-      </c>
-      <c r="H61" t="n">
-        <v>7</v>
-      </c>
-      <c r="I61" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K61" t="n">
+      <c r="M61" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1</v>
+      </c>
+      <c r="X61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF61" t="n">
         <v>5</v>
-      </c>
-      <c r="L61" t="n">
-        <v>5</v>
-      </c>
-      <c r="M61" t="n">
-        <v>7</v>
-      </c>
-      <c r="O61" t="n">
-        <v>1</v>
-      </c>
-      <c r="P61" t="n">
-        <v>1</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1</v>
-      </c>
-      <c r="V61" t="n">
-        <v>1</v>
-      </c>
-      <c r="W61" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>6</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
@@ -5253,7 +5211,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Expansión del universo y Big Bang</t>
+          <t>Densidad</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5262,51 +5220,42 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>11</v>
-      </c>
-      <c r="E62" t="n">
         <v>9</v>
       </c>
       <c r="F62" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G62" t="n">
+        <v>6</v>
       </c>
       <c r="H62" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I62" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K62" t="n">
+        <v>6</v>
+      </c>
+      <c r="L62" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M62" t="n">
         <v>7</v>
       </c>
-      <c r="K62" t="n">
-        <v>8</v>
-      </c>
-      <c r="M62" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N62" t="n">
-        <v>1</v>
-      </c>
       <c r="O62" t="n">
         <v>1</v>
       </c>
-      <c r="R62" t="n">
-        <v>1</v>
-      </c>
-      <c r="S62" t="n">
-        <v>1</v>
-      </c>
-      <c r="V62" t="n">
-        <v>1</v>
-      </c>
-      <c r="W62" t="n">
-        <v>1</v>
-      </c>
-      <c r="X62" t="n">
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
         <v>1</v>
       </c>
       <c r="Y62" t="n">
@@ -5315,20 +5264,11 @@
       <c r="Z62" t="n">
         <v>1</v>
       </c>
-      <c r="AA62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>1</v>
-      </c>
       <c r="AD62" t="n">
         <v>1</v>
       </c>
       <c r="AF62" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
@@ -5344,7 +5284,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Densidad</t>
+          <t>Dilatación térmica</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5353,10 +5293,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F63" t="n">
         <v>8</v>
@@ -5368,16 +5308,16 @@
         <v>7</v>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K63" t="n">
         <v>6</v>
       </c>
       <c r="L63" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M63" t="n">
         <v>7</v>
@@ -5385,23 +5325,14 @@
       <c r="O63" t="n">
         <v>1</v>
       </c>
-      <c r="P63" t="n">
-        <v>1</v>
-      </c>
       <c r="U63" t="n">
         <v>1</v>
       </c>
-      <c r="Y63" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD63" t="n">
+      <c r="AB63" t="n">
         <v>1</v>
       </c>
       <c r="AF63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
@@ -5417,7 +5348,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Dilatación térmica</t>
+          <t>Disipación de energía y eficiencia</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5426,31 +5357,34 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E64" t="n">
+        <v>8</v>
       </c>
       <c r="F64" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G64" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H64" t="n">
         <v>7</v>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J64" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K64" t="n">
+        <v>2</v>
+      </c>
+      <c r="L64" t="n">
         <v>6</v>
-      </c>
-      <c r="L64" t="n">
-        <v>4</v>
       </c>
       <c r="M64" t="n">
         <v>7</v>
@@ -5458,14 +5392,41 @@
       <c r="O64" t="n">
         <v>1</v>
       </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
       <c r="U64" t="n">
         <v>1</v>
       </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>1</v>
+      </c>
       <c r="AB64" t="n">
         <v>1</v>
       </c>
+      <c r="AC64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1</v>
+      </c>
       <c r="AF64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
@@ -5481,7 +5442,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Disipación de energía y eficiencia</t>
+          <t>Efecto Doppler</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5490,76 +5451,31 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D65" t="n">
-        <v>9</v>
-      </c>
-      <c r="E65" t="n">
-        <v>8</v>
-      </c>
-      <c r="F65" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G65" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H65" t="n">
-        <v>7</v>
-      </c>
-      <c r="I65" t="n">
-        <v>8</v>
-      </c>
-      <c r="J65" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K65" t="n">
-        <v>2</v>
-      </c>
-      <c r="L65" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M65" t="n">
-        <v>7</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" t="n">
-        <v>1</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1</v>
-      </c>
-      <c r="S65" t="n">
-        <v>1</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="V65" t="n">
         <v>1</v>
       </c>
-      <c r="W65" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>1</v>
-      </c>
       <c r="Z65" t="n">
         <v>1</v>
       </c>
+      <c r="AA65" t="n">
+        <v>1</v>
+      </c>
       <c r="AB65" t="n">
         <v>1</v>
       </c>
       <c r="AC65" t="n">
         <v>1</v>
       </c>
-      <c r="AD65" t="n">
-        <v>1</v>
-      </c>
       <c r="AF65" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
@@ -5568,14 +5484,14 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Efecto Doppler</t>
+          <t>Esfuerzo, deformación y módulo de Young</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5584,31 +5500,28 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
         <v>11</v>
       </c>
+      <c r="G66" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2</v>
+      </c>
       <c r="M66" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC66" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y66" t="n">
         <v>1</v>
       </c>
       <c r="AF66" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
@@ -5617,14 +5530,14 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Esfuerzo, deformación y módulo de Young</t>
+          <t>Electroimanes y efecto magnético de la corriente</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5633,28 +5546,70 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D67" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="F67" t="n">
+        <v>8</v>
       </c>
       <c r="G67" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K67" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="H67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I67" t="n">
+        <v>4</v>
+      </c>
+      <c r="J67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L67" t="n">
+        <v>3</v>
       </c>
       <c r="M67" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
       </c>
       <c r="P67" t="n">
         <v>1</v>
       </c>
+      <c r="U67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1</v>
+      </c>
+      <c r="X67" t="n">
+        <v>1</v>
+      </c>
       <c r="Y67" t="n">
         <v>1</v>
       </c>
+      <c r="Z67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1</v>
+      </c>
       <c r="AF67" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
@@ -5670,7 +5625,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Electroimanes y efecto magnético de la corriente</t>
+          <t>Energía cinética</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5679,47 +5634,53 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
         <v>9</v>
       </c>
-      <c r="F68" t="n">
+      <c r="E68" t="n">
+        <v>7</v>
+      </c>
+      <c r="G68" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H68" t="n">
+        <v>4</v>
+      </c>
+      <c r="I68" t="n">
         <v>8</v>
       </c>
-      <c r="G68" t="n">
-        <v>6</v>
-      </c>
-      <c r="H68" t="n">
-        <v>5</v>
-      </c>
-      <c r="I68" t="n">
+      <c r="J68" t="n">
+        <v>7</v>
+      </c>
+      <c r="K68" t="n">
         <v>4</v>
       </c>
-      <c r="J68" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L68" t="n">
-        <v>3</v>
+        <v>9.5</v>
       </c>
       <c r="M68" t="n">
         <v>4.5</v>
       </c>
-      <c r="O68" t="n">
-        <v>1</v>
-      </c>
       <c r="P68" t="n">
         <v>1</v>
       </c>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
       <c r="U68" t="n">
         <v>1</v>
       </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
       <c r="W68" t="n">
         <v>1</v>
       </c>
-      <c r="X68" t="n">
-        <v>1</v>
-      </c>
       <c r="Y68" t="n">
         <v>1</v>
       </c>
@@ -5742,7 +5703,7 @@
         <v>1</v>
       </c>
       <c r="AF68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
@@ -5758,7 +5719,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Energía cinética</t>
+          <t>Energía potencial gravitatoria y elástica</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5767,16 +5728,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E69" t="n">
         <v>7</v>
       </c>
       <c r="G69" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H69" t="n">
         <v>4</v>
@@ -5794,7 +5755,7 @@
         <v>9.5</v>
       </c>
       <c r="M69" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="P69" t="n">
         <v>1</v>
@@ -5802,15 +5763,9 @@
       <c r="R69" t="n">
         <v>1</v>
       </c>
-      <c r="S69" t="n">
-        <v>1</v>
-      </c>
       <c r="U69" t="n">
         <v>1</v>
       </c>
-      <c r="V69" t="n">
-        <v>1</v>
-      </c>
       <c r="W69" t="n">
         <v>1</v>
       </c>
@@ -5818,9 +5773,6 @@
         <v>1</v>
       </c>
       <c r="Z69" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA69" t="n">
         <v>1</v>
       </c>
       <c r="AB69" t="n">
@@ -5852,7 +5804,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Energía potencial gravitatoria y elástica</t>
+          <t>La energía y sus usos</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5861,34 +5813,37 @@
         </is>
       </c>
       <c r="C70" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" t="n">
+        <v>9</v>
+      </c>
+      <c r="F70" t="n">
+        <v>8</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2</v>
+      </c>
+      <c r="I70" t="n">
         <v>5</v>
       </c>
-      <c r="D70" t="n">
-        <v>10</v>
-      </c>
-      <c r="E70" t="n">
-        <v>7</v>
-      </c>
-      <c r="G70" t="n">
-        <v>6</v>
-      </c>
-      <c r="H70" t="n">
+      <c r="J70" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K70" t="n">
+        <v>2</v>
+      </c>
+      <c r="L70" t="n">
         <v>4</v>
       </c>
-      <c r="I70" t="n">
-        <v>8</v>
-      </c>
-      <c r="J70" t="n">
-        <v>7</v>
-      </c>
-      <c r="K70" t="n">
-        <v>4</v>
-      </c>
-      <c r="L70" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M70" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
       </c>
       <c r="P70" t="n">
         <v>1</v>
@@ -5899,7 +5854,7 @@
       <c r="U70" t="n">
         <v>1</v>
       </c>
-      <c r="W70" t="n">
+      <c r="V70" t="n">
         <v>1</v>
       </c>
       <c r="Y70" t="n">
@@ -5914,14 +5869,8 @@
       <c r="AC70" t="n">
         <v>1</v>
       </c>
-      <c r="AD70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>1</v>
-      </c>
       <c r="AF70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
@@ -5930,14 +5879,14 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>La energía y sus usos</t>
+          <t>Condiciones de equilibrio estático</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5949,34 +5898,28 @@
         <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>9</v>
-      </c>
-      <c r="F71" t="n">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="E71" t="n">
+        <v>6</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
-      </c>
-      <c r="H71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J71" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K71" t="n">
         <v>2</v>
       </c>
       <c r="L71" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="M71" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O71" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
@@ -5987,19 +5930,22 @@
       <c r="U71" t="n">
         <v>1</v>
       </c>
-      <c r="V71" t="n">
-        <v>1</v>
-      </c>
       <c r="Y71" t="n">
         <v>1</v>
       </c>
       <c r="Z71" t="n">
         <v>1</v>
       </c>
+      <c r="AA71" t="n">
+        <v>1</v>
+      </c>
       <c r="AB71" t="n">
         <v>1</v>
       </c>
-      <c r="AC71" t="n">
+      <c r="AD71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE71" t="n">
         <v>1</v>
       </c>
       <c r="AF71" t="n">
@@ -6012,14 +5958,14 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Condiciones de equilibrio estático</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6031,28 +5977,37 @@
         <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E72" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="F72" t="n">
+        <v>8</v>
       </c>
       <c r="G72" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K72" t="n">
         <v>2</v>
       </c>
       <c r="L72" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M72" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
       </c>
       <c r="P72" t="n">
         <v>1</v>
@@ -6075,10 +6030,10 @@
       <c r="AB72" t="n">
         <v>1</v>
       </c>
+      <c r="AC72" t="n">
+        <v>1</v>
+      </c>
       <c r="AD72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE72" t="n">
         <v>1</v>
       </c>
       <c r="AF72" t="n">
@@ -6098,7 +6053,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Flotación y hundimiento</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6112,61 +6067,28 @@
       <c r="D73" t="n">
         <v>9</v>
       </c>
-      <c r="E73" t="n">
-        <v>2</v>
-      </c>
       <c r="F73" t="n">
         <v>8</v>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H73" t="n">
         <v>2</v>
       </c>
-      <c r="I73" t="n">
-        <v>3</v>
-      </c>
-      <c r="J73" t="n">
-        <v>2.5</v>
-      </c>
       <c r="K73" t="n">
         <v>2</v>
       </c>
       <c r="L73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M73" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="P73" t="n">
-        <v>1</v>
-      </c>
-      <c r="R73" t="n">
-        <v>1</v>
-      </c>
-      <c r="U73" t="n">
-        <v>1</v>
-      </c>
       <c r="Y73" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD73" t="n">
         <v>1</v>
       </c>
       <c r="AF73" t="n">
@@ -6186,7 +6108,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Flotación y hundimiento</t>
+          <t>Formas de energía</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6198,7 +6120,10 @@
         <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E74" t="n">
+        <v>7</v>
       </c>
       <c r="F74" t="n">
         <v>8</v>
@@ -6209,19 +6134,49 @@
       <c r="H74" t="n">
         <v>2</v>
       </c>
+      <c r="I74" t="n">
+        <v>5</v>
+      </c>
+      <c r="J74" t="n">
+        <v>7</v>
+      </c>
       <c r="K74" t="n">
         <v>2</v>
       </c>
       <c r="L74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M74" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
+      </c>
+      <c r="V74" t="n">
+        <v>1</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1</v>
+      </c>
       <c r="Y74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE74" t="n">
         <v>1</v>
       </c>
       <c r="AF74" t="n">
@@ -6241,7 +6196,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Formas de energía</t>
+          <t>Fuentes de energía renovables y no renovables</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6253,34 +6208,31 @@
         <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>10</v>
-      </c>
-      <c r="E75" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F75" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G75" t="n">
         <v>6</v>
       </c>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I75" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J75" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K75" t="n">
         <v>2</v>
       </c>
       <c r="L75" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M75" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O75" t="n">
         <v>1</v>
@@ -6288,13 +6240,19 @@
       <c r="P75" t="n">
         <v>1</v>
       </c>
-      <c r="U75" t="n">
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
         <v>1</v>
       </c>
       <c r="V75" t="n">
         <v>1</v>
       </c>
       <c r="W75" t="n">
+        <v>1</v>
+      </c>
+      <c r="X75" t="n">
         <v>1</v>
       </c>
       <c r="Y75" t="n">
@@ -6322,7 +6280,7 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6946,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Leyes de Kepler</t>
+          <t>Ley de Ohm</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6997,20 +6955,56 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D84" t="n">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="F84" t="n">
+        <v>8</v>
+      </c>
+      <c r="G84" t="n">
+        <v>6</v>
+      </c>
+      <c r="H84" t="n">
+        <v>7</v>
+      </c>
+      <c r="I84" t="n">
+        <v>7</v>
+      </c>
+      <c r="J84" t="n">
+        <v>7</v>
+      </c>
+      <c r="K84" t="n">
+        <v>8</v>
+      </c>
+      <c r="L84" t="n">
+        <v>7.5</v>
       </c>
       <c r="M84" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V84" t="n">
+        <v>7</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
+      <c r="P84" t="n">
+        <v>1</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
         <v>1</v>
       </c>
       <c r="W84" t="n">
         <v>1</v>
       </c>
+      <c r="X84" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>1</v>
+      </c>
       <c r="Z84" t="n">
         <v>1</v>
       </c>
@@ -7020,11 +7014,17 @@
       <c r="AB84" t="n">
         <v>1</v>
       </c>
+      <c r="AC84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>1</v>
+      </c>
       <c r="AE84" t="n">
         <v>1</v>
       </c>
       <c r="AF84" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AG84" t="inlineStr">
         <is>
@@ -7033,14 +7033,14 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Magnitudes escalares y vectoriales</t>
+          <t>Leyes de Kepler</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7049,58 +7049,34 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D85" t="n">
-        <v>10</v>
-      </c>
-      <c r="F85" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G85" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H85" t="n">
-        <v>3</v>
-      </c>
-      <c r="I85" t="n">
-        <v>6</v>
-      </c>
-      <c r="K85" t="n">
-        <v>6</v>
-      </c>
-      <c r="L85" t="n">
+        <v>9</v>
+      </c>
+      <c r="M85" t="n">
         <v>9.5</v>
       </c>
-      <c r="M85" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O85" t="n">
-        <v>1</v>
-      </c>
-      <c r="P85" t="n">
-        <v>1</v>
-      </c>
-      <c r="U85" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y85" t="n">
+      <c r="V85" t="n">
+        <v>1</v>
+      </c>
+      <c r="W85" t="n">
         <v>1</v>
       </c>
       <c r="Z85" t="n">
         <v>1</v>
       </c>
-      <c r="AC85" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD85" t="n">
+      <c r="AA85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB85" t="n">
         <v>1</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
       </c>
       <c r="AF85" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
@@ -7109,14 +7085,14 @@
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Longitud de onda, frecuencia y rapidez</t>
+          <t>Magnitudes escalares y vectoriales</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7125,31 +7101,31 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F86" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="G86" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H86" t="n">
+        <v>3</v>
+      </c>
+      <c r="I86" t="n">
         <v>6</v>
       </c>
-      <c r="H86" t="n">
-        <v>7</v>
-      </c>
-      <c r="I86" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J86" t="n">
-        <v>7</v>
+      <c r="K86" t="n">
+        <v>6</v>
       </c>
       <c r="L86" t="n">
         <v>9.5</v>
       </c>
       <c r="M86" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O86" t="n">
         <v>1</v>
@@ -7157,30 +7133,15 @@
       <c r="P86" t="n">
         <v>1</v>
       </c>
-      <c r="R86" t="n">
-        <v>1</v>
-      </c>
       <c r="U86" t="n">
         <v>1</v>
       </c>
-      <c r="V86" t="n">
-        <v>1</v>
-      </c>
-      <c r="W86" t="n">
-        <v>1</v>
-      </c>
       <c r="Y86" t="n">
         <v>1</v>
       </c>
       <c r="Z86" t="n">
         <v>1</v>
       </c>
-      <c r="AA86" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB86" t="n">
-        <v>1</v>
-      </c>
       <c r="AC86" t="n">
         <v>1</v>
       </c>
@@ -7191,7 +7152,7 @@
         <v>1</v>
       </c>
       <c r="AF86" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
@@ -7207,7 +7168,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Máquinas simples</t>
+          <t>Longitud de onda, frecuencia y rapidez</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7216,46 +7177,73 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D87" t="n">
         <v>9</v>
       </c>
       <c r="F87" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G87" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H87" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="J87" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K87" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L87" t="n">
         <v>9.5</v>
       </c>
       <c r="M87" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O87" t="n">
         <v>1</v>
       </c>
+      <c r="P87" t="n">
+        <v>1</v>
+      </c>
+      <c r="R87" t="n">
+        <v>1</v>
+      </c>
       <c r="U87" t="n">
         <v>1</v>
       </c>
+      <c r="V87" t="n">
+        <v>1</v>
+      </c>
+      <c r="W87" t="n">
+        <v>1</v>
+      </c>
       <c r="Y87" t="n">
         <v>1</v>
       </c>
+      <c r="Z87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>1</v>
+      </c>
       <c r="AF87" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
@@ -7271,7 +7259,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Masa y peso</t>
+          <t>Máquinas simples</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7286,60 +7274,36 @@
         <v>9</v>
       </c>
       <c r="F88" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G88" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H88" t="n">
         <v>2</v>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J88" t="n">
         <v>2.5</v>
       </c>
       <c r="K88" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L88" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="M88" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O88" t="n">
         <v>1</v>
       </c>
-      <c r="P88" t="n">
-        <v>1</v>
-      </c>
-      <c r="R88" t="n">
-        <v>1</v>
-      </c>
       <c r="U88" t="n">
         <v>1</v>
       </c>
-      <c r="W88" t="n">
-        <v>1</v>
-      </c>
       <c r="Y88" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE88" t="n">
         <v>1</v>
       </c>
       <c r="AF88" t="n">
@@ -7359,7 +7323,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Materiales magnéticos</t>
+          <t>Masa y peso</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7368,13 +7332,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2.5</v>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H89" t="n">
         <v>2</v>
@@ -7385,32 +7352,50 @@
       <c r="J89" t="n">
         <v>2.5</v>
       </c>
+      <c r="K89" t="n">
+        <v>5</v>
+      </c>
       <c r="L89" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M89" t="n">
         <v>2.5</v>
       </c>
+      <c r="O89" t="n">
+        <v>1</v>
+      </c>
       <c r="P89" t="n">
         <v>1</v>
       </c>
+      <c r="R89" t="n">
+        <v>1</v>
+      </c>
       <c r="U89" t="n">
         <v>1</v>
       </c>
-      <c r="X89" t="n">
+      <c r="W89" t="n">
         <v>1</v>
       </c>
       <c r="Y89" t="n">
         <v>1</v>
       </c>
-      <c r="AB89" t="n">
+      <c r="Z89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC89" t="n">
         <v>1</v>
       </c>
       <c r="AD89" t="n">
         <v>1</v>
       </c>
+      <c r="AE89" t="n">
+        <v>1</v>
+      </c>
       <c r="AF89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
@@ -7426,7 +7411,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Materiales opacos, transparentes y translúcidos</t>
+          <t>Materiales magnéticos</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7435,7 +7420,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
         <v>10</v>
@@ -7446,20 +7431,38 @@
       <c r="H90" t="n">
         <v>2</v>
       </c>
-      <c r="K90" t="n">
-        <v>3</v>
+      <c r="I90" t="n">
+        <v>2</v>
+      </c>
+      <c r="J90" t="n">
+        <v>2.5</v>
       </c>
       <c r="L90" t="n">
         <v>3</v>
       </c>
+      <c r="M90" t="n">
+        <v>2.5</v>
+      </c>
       <c r="P90" t="n">
         <v>1</v>
       </c>
+      <c r="U90" t="n">
+        <v>1</v>
+      </c>
+      <c r="X90" t="n">
+        <v>1</v>
+      </c>
       <c r="Y90" t="n">
         <v>1</v>
       </c>
+      <c r="AB90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>1</v>
+      </c>
       <c r="AF90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG90" t="inlineStr">
         <is>
@@ -7475,7 +7478,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Conducción, convección y radiación</t>
+          <t>Materiales opacos, transparentes y translúcidos</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7487,63 +7490,24 @@
         <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>9</v>
-      </c>
-      <c r="E91" t="n">
-        <v>8</v>
-      </c>
-      <c r="F91" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H91" t="n">
         <v>2</v>
       </c>
-      <c r="I91" t="n">
+      <c r="K91" t="n">
         <v>3</v>
       </c>
-      <c r="J91" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K91" t="n">
-        <v>2</v>
-      </c>
       <c r="L91" t="n">
-        <v>4</v>
-      </c>
-      <c r="M91" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P91" t="n">
         <v>1</v>
       </c>
-      <c r="R91" t="n">
-        <v>1</v>
-      </c>
-      <c r="U91" t="n">
-        <v>1</v>
-      </c>
-      <c r="W91" t="n">
-        <v>1</v>
-      </c>
       <c r="Y91" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD91" t="n">
         <v>1</v>
       </c>
       <c r="AF91" t="n">
@@ -7563,7 +7527,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Medición de magnitudes con instrumentos</t>
+          <t>Conducción, convección y radiación</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7577,8 +7541,11 @@
       <c r="D92" t="n">
         <v>9</v>
       </c>
+      <c r="E92" t="n">
+        <v>8</v>
+      </c>
       <c r="F92" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G92" t="n">
         <v>6</v>
@@ -7587,13 +7554,13 @@
         <v>2</v>
       </c>
       <c r="I92" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="J92" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K92" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L92" t="n">
         <v>4</v>
@@ -7610,18 +7577,9 @@
       <c r="R92" t="n">
         <v>1</v>
       </c>
-      <c r="S92" t="n">
-        <v>1</v>
-      </c>
-      <c r="T92" t="n">
-        <v>1</v>
-      </c>
       <c r="U92" t="n">
         <v>1</v>
       </c>
-      <c r="V92" t="n">
-        <v>1</v>
-      </c>
       <c r="W92" t="n">
         <v>1</v>
       </c>
@@ -7631,13 +7589,13 @@
       <c r="Z92" t="n">
         <v>1</v>
       </c>
+      <c r="AB92" t="n">
+        <v>1</v>
+      </c>
       <c r="AC92" t="n">
         <v>1</v>
       </c>
       <c r="AD92" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE92" t="n">
         <v>1</v>
       </c>
       <c r="AF92" t="n">
@@ -7657,7 +7615,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Medición de magnitudes con instrumentos</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7666,37 +7624,34 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>10</v>
-      </c>
-      <c r="E93" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G93" t="n">
         <v>6</v>
       </c>
       <c r="H93" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
         <v>9.5</v>
       </c>
       <c r="J93" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K93" t="n">
+        <v>9</v>
+      </c>
+      <c r="L93" t="n">
         <v>4</v>
       </c>
-      <c r="L93" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M93" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O93" t="n">
         <v>1</v>
@@ -7707,6 +7662,12 @@
       <c r="R93" t="n">
         <v>1</v>
       </c>
+      <c r="S93" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" t="n">
+        <v>1</v>
+      </c>
       <c r="U93" t="n">
         <v>1</v>
       </c>
@@ -7722,12 +7683,6 @@
       <c r="Z93" t="n">
         <v>1</v>
       </c>
-      <c r="AA93" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB93" t="n">
-        <v>1</v>
-      </c>
       <c r="AC93" t="n">
         <v>1</v>
       </c>
@@ -7738,7 +7693,7 @@
         <v>1</v>
       </c>
       <c r="AF93" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
@@ -7754,7 +7709,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Momento lineal e impulso</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7763,25 +7718,37 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
         <v>10</v>
       </c>
+      <c r="E94" t="n">
+        <v>4</v>
+      </c>
       <c r="F94" t="n">
         <v>8</v>
       </c>
       <c r="G94" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H94" t="n">
+        <v>7</v>
+      </c>
+      <c r="I94" t="n">
+        <v>9.5</v>
       </c>
       <c r="J94" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K94" t="n">
         <v>4</v>
       </c>
       <c r="L94" t="n">
-        <v>11</v>
+        <v>7.5</v>
+      </c>
+      <c r="M94" t="n">
+        <v>7</v>
       </c>
       <c r="O94" t="n">
         <v>1</v>
@@ -7789,12 +7756,15 @@
       <c r="P94" t="n">
         <v>1</v>
       </c>
-      <c r="S94" t="n">
+      <c r="R94" t="n">
         <v>1</v>
       </c>
       <c r="U94" t="n">
         <v>1</v>
       </c>
+      <c r="V94" t="n">
+        <v>1</v>
+      </c>
       <c r="W94" t="n">
         <v>1</v>
       </c>
@@ -7820,7 +7790,7 @@
         <v>1</v>
       </c>
       <c r="AF94" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
@@ -7836,7 +7806,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Movimiento armónico simple</t>
+          <t>Momento lineal e impulso</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7848,12 +7818,33 @@
         <v>8</v>
       </c>
       <c r="D95" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F95" t="n">
         <v>8</v>
       </c>
+      <c r="G95" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J95" t="n">
+        <v>9</v>
+      </c>
+      <c r="K95" t="n">
+        <v>4</v>
+      </c>
+      <c r="L95" t="n">
+        <v>11</v>
+      </c>
       <c r="O95" t="n">
+        <v>1</v>
+      </c>
+      <c r="P95" t="n">
+        <v>1</v>
+      </c>
+      <c r="S95" t="n">
+        <v>1</v>
+      </c>
+      <c r="U95" t="n">
         <v>1</v>
       </c>
       <c r="W95" t="n">
@@ -7897,7 +7888,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Movimiento circular y variables angulares</t>
+          <t>Movimiento armónico simple</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7906,35 +7897,17 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D96" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F96" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G96" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K96" t="n">
-        <v>3</v>
-      </c>
-      <c r="L96" t="n">
-        <v>11</v>
-      </c>
-      <c r="M96" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
       </c>
-      <c r="P96" t="n">
-        <v>1</v>
-      </c>
-      <c r="U96" t="n">
-        <v>1</v>
-      </c>
       <c r="W96" t="n">
         <v>1</v>
       </c>
@@ -7960,7 +7933,7 @@
         <v>1</v>
       </c>
       <c r="AF96" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
@@ -7976,7 +7949,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cinemática en dos dimensiones y proyectiles</t>
+          <t>Movimiento circular y variables angulares</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7985,35 +7958,35 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D97" t="n">
         <v>10</v>
       </c>
-      <c r="I97" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J97" t="n">
-        <v>9</v>
+      <c r="F97" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G97" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K97" t="n">
+        <v>3</v>
       </c>
       <c r="L97" t="n">
         <v>11</v>
       </c>
       <c r="M97" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R97" t="n">
-        <v>1</v>
-      </c>
-      <c r="S97" t="n">
+        <v>7</v>
+      </c>
+      <c r="O97" t="n">
+        <v>1</v>
+      </c>
+      <c r="P97" t="n">
         <v>1</v>
       </c>
       <c r="U97" t="n">
         <v>1</v>
       </c>
-      <c r="V97" t="n">
-        <v>1</v>
-      </c>
       <c r="W97" t="n">
         <v>1</v>
       </c>
@@ -8039,7 +8012,7 @@
         <v>1</v>
       </c>
       <c r="AF97" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
@@ -8055,7 +8028,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Movimiento con aceleración constante</t>
+          <t>Cinemática en dos dimensiones y proyectiles</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8069,34 +8042,22 @@
       <c r="D98" t="n">
         <v>10</v>
       </c>
-      <c r="F98" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G98" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H98" t="n">
-        <v>7</v>
-      </c>
       <c r="I98" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="J98" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L98" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="M98" t="n">
         <v>9.5</v>
       </c>
-      <c r="O98" t="n">
-        <v>1</v>
-      </c>
-      <c r="P98" t="n">
-        <v>1</v>
-      </c>
       <c r="R98" t="n">
+        <v>1</v>
+      </c>
+      <c r="S98" t="n">
         <v>1</v>
       </c>
       <c r="U98" t="n">
@@ -8146,7 +8107,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ondas estacionarias y armónicos</t>
+          <t>Movimiento con aceleración constante</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8158,26 +8119,44 @@
         <v>8</v>
       </c>
       <c r="D99" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F99" t="n">
         <v>10.5</v>
       </c>
+      <c r="G99" t="n">
+        <v>8.5</v>
+      </c>
       <c r="H99" t="n">
         <v>7</v>
       </c>
       <c r="I99" t="n">
+        <v>8</v>
+      </c>
+      <c r="J99" t="n">
+        <v>7</v>
+      </c>
+      <c r="L99" t="n">
         <v>9.5</v>
       </c>
       <c r="M99" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O99" t="n">
         <v>1</v>
       </c>
+      <c r="P99" t="n">
+        <v>1</v>
+      </c>
       <c r="R99" t="n">
         <v>1</v>
       </c>
+      <c r="U99" t="n">
+        <v>1</v>
+      </c>
+      <c r="V99" t="n">
+        <v>1</v>
+      </c>
       <c r="W99" t="n">
         <v>1</v>
       </c>
@@ -8185,6 +8164,9 @@
         <v>1</v>
       </c>
       <c r="Z99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA99" t="n">
         <v>1</v>
       </c>
       <c r="AB99" t="n">
@@ -8216,7 +8198,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Ondas mecánicas transversales y longitudinales</t>
+          <t>Ondas estacionarias y armónicos</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8225,51 +8207,36 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D100" t="n">
-        <v>9</v>
-      </c>
-      <c r="E100" t="n">
-        <v>8</v>
-      </c>
-      <c r="G100" t="n">
-        <v>6</v>
+        <v>11</v>
+      </c>
+      <c r="F100" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H100" t="n">
+        <v>7</v>
       </c>
       <c r="I100" t="n">
         <v>9.5</v>
       </c>
-      <c r="L100" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M100" t="n">
         <v>7</v>
       </c>
-      <c r="P100" t="n">
+      <c r="O100" t="n">
         <v>1</v>
       </c>
       <c r="R100" t="n">
         <v>1</v>
       </c>
-      <c r="U100" t="n">
-        <v>1</v>
-      </c>
-      <c r="V100" t="n">
-        <v>1</v>
-      </c>
       <c r="W100" t="n">
         <v>1</v>
       </c>
-      <c r="X100" t="n">
-        <v>1</v>
-      </c>
       <c r="Y100" t="n">
         <v>1</v>
       </c>
       <c r="Z100" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA100" t="n">
         <v>1</v>
       </c>
       <c r="AB100" t="n">
@@ -8301,7 +8268,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Péndulo simple</t>
+          <t>Ondas mecánicas transversales y longitudinales</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8310,21 +8277,45 @@
         </is>
       </c>
       <c r="C101" t="n">
+        <v>2</v>
+      </c>
+      <c r="D101" t="n">
+        <v>9</v>
+      </c>
+      <c r="E101" t="n">
         <v>8</v>
       </c>
-      <c r="D101" t="n">
-        <v>10</v>
-      </c>
-      <c r="F101" t="n">
-        <v>8</v>
+      <c r="G101" t="n">
+        <v>6</v>
       </c>
       <c r="I101" t="n">
-        <v>4</v>
-      </c>
-      <c r="J101" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L101" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M101" t="n">
         <v>7</v>
       </c>
-      <c r="O101" t="n">
+      <c r="P101" t="n">
+        <v>1</v>
+      </c>
+      <c r="R101" t="n">
+        <v>1</v>
+      </c>
+      <c r="U101" t="n">
+        <v>1</v>
+      </c>
+      <c r="V101" t="n">
+        <v>1</v>
+      </c>
+      <c r="W101" t="n">
+        <v>1</v>
+      </c>
+      <c r="X101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y101" t="n">
         <v>1</v>
       </c>
       <c r="Z101" t="n">
@@ -8333,7 +8324,16 @@
       <c r="AA101" t="n">
         <v>1</v>
       </c>
+      <c r="AB101" t="n">
+        <v>1</v>
+      </c>
       <c r="AC101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE101" t="n">
         <v>1</v>
       </c>
       <c r="AF101" t="n">
@@ -8353,7 +8353,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Posición, desplazamiento y trayectoria</t>
+          <t>Péndulo simple</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D102" t="n">
         <v>10</v>
@@ -8370,59 +8370,26 @@
       <c r="F102" t="n">
         <v>8</v>
       </c>
-      <c r="G102" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H102" t="n">
-        <v>2</v>
-      </c>
       <c r="I102" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="J102" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K102" t="n">
-        <v>2</v>
-      </c>
-      <c r="L102" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M102" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O102" t="n">
         <v>1</v>
       </c>
-      <c r="P102" t="n">
-        <v>1</v>
-      </c>
-      <c r="R102" t="n">
-        <v>1</v>
-      </c>
-      <c r="S102" t="n">
-        <v>1</v>
-      </c>
-      <c r="U102" t="n">
-        <v>1</v>
-      </c>
-      <c r="W102" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>1</v>
-      </c>
       <c r="Z102" t="n">
         <v>1</v>
       </c>
+      <c r="AA102" t="n">
+        <v>1</v>
+      </c>
       <c r="AC102" t="n">
         <v>1</v>
       </c>
-      <c r="AD102" t="n">
-        <v>1</v>
-      </c>
       <c r="AF102" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG102" t="inlineStr">
         <is>
@@ -8438,7 +8405,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Potencia mecánica</t>
+          <t>Posición, desplazamiento y trayectoria</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8453,19 +8420,28 @@
         <v>10</v>
       </c>
       <c r="F103" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G103" t="n">
         <v>8.5</v>
       </c>
+      <c r="H103" t="n">
+        <v>2</v>
+      </c>
       <c r="I103" t="n">
-        <v>8</v>
+        <v>9.5</v>
+      </c>
+      <c r="J103" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K103" t="n">
+        <v>2</v>
       </c>
       <c r="L103" t="n">
         <v>9.5</v>
       </c>
       <c r="M103" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O103" t="n">
         <v>1</v>
@@ -8473,9 +8449,18 @@
       <c r="P103" t="n">
         <v>1</v>
       </c>
+      <c r="R103" t="n">
+        <v>1</v>
+      </c>
+      <c r="S103" t="n">
+        <v>1</v>
+      </c>
       <c r="U103" t="n">
         <v>1</v>
       </c>
+      <c r="W103" t="n">
+        <v>1</v>
+      </c>
       <c r="Y103" t="n">
         <v>1</v>
       </c>
@@ -8488,11 +8473,8 @@
       <c r="AD103" t="n">
         <v>1</v>
       </c>
-      <c r="AE103" t="n">
-        <v>1</v>
-      </c>
       <c r="AF103" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG103" t="inlineStr">
         <is>
@@ -8508,7 +8490,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Presión</t>
+          <t>Potencia mecánica</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8517,36 +8499,30 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F104" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G104" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I104" t="n">
         <v>8</v>
       </c>
-      <c r="G104" t="n">
-        <v>6</v>
-      </c>
-      <c r="H104" t="n">
-        <v>4</v>
-      </c>
-      <c r="I104" t="n">
-        <v>3</v>
-      </c>
-      <c r="K104" t="n">
-        <v>4</v>
-      </c>
       <c r="L104" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="M104" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O104" t="n">
         <v>1</v>
       </c>
-      <c r="R104" t="n">
+      <c r="P104" t="n">
         <v>1</v>
       </c>
       <c r="U104" t="n">
@@ -8558,14 +8534,17 @@
       <c r="Z104" t="n">
         <v>1</v>
       </c>
-      <c r="AA104" t="n">
+      <c r="AC104" t="n">
         <v>1</v>
       </c>
       <c r="AD104" t="n">
         <v>1</v>
       </c>
+      <c r="AE104" t="n">
+        <v>1</v>
+      </c>
       <c r="AF104" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG104" t="inlineStr">
         <is>
@@ -8581,7 +8560,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Presión hidrostática y atmosférica</t>
+          <t>Presión</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8596,7 +8575,7 @@
         <v>9</v>
       </c>
       <c r="F105" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G105" t="n">
         <v>6</v>
@@ -8605,7 +8584,10 @@
         <v>4</v>
       </c>
       <c r="I105" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="K105" t="n">
+        <v>4</v>
       </c>
       <c r="L105" t="n">
         <v>7.5</v>
@@ -8616,10 +8598,19 @@
       <c r="O105" t="n">
         <v>1</v>
       </c>
+      <c r="R105" t="n">
+        <v>1</v>
+      </c>
+      <c r="U105" t="n">
+        <v>1</v>
+      </c>
       <c r="Y105" t="n">
         <v>1</v>
       </c>
       <c r="Z105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA105" t="n">
         <v>1</v>
       </c>
       <c r="AD105" t="n">
@@ -8642,7 +8633,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Primera ley de Newton: inercia</t>
+          <t>Presión hidrostática y atmosférica</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8651,82 +8642,43 @@
         </is>
       </c>
       <c r="C106" t="n">
+        <v>6</v>
+      </c>
+      <c r="D106" t="n">
+        <v>9</v>
+      </c>
+      <c r="F106" t="n">
         <v>5</v>
-      </c>
-      <c r="D106" t="n">
-        <v>10</v>
-      </c>
-      <c r="E106" t="n">
-        <v>9</v>
-      </c>
-      <c r="F106" t="n">
-        <v>10.5</v>
       </c>
       <c r="G106" t="n">
         <v>6</v>
       </c>
       <c r="H106" t="n">
+        <v>4</v>
+      </c>
+      <c r="I106" t="n">
         <v>7</v>
       </c>
-      <c r="I106" t="n">
-        <v>8</v>
-      </c>
-      <c r="J106" t="n">
+      <c r="L106" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M106" t="n">
         <v>2.5</v>
       </c>
-      <c r="K106" t="n">
-        <v>2</v>
-      </c>
-      <c r="L106" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M106" t="n">
-        <v>7</v>
-      </c>
-      <c r="N106" t="n">
-        <v>1</v>
-      </c>
       <c r="O106" t="n">
         <v>1</v>
       </c>
-      <c r="P106" t="n">
-        <v>1</v>
-      </c>
-      <c r="R106" t="n">
-        <v>1</v>
-      </c>
-      <c r="S106" t="n">
-        <v>1</v>
-      </c>
-      <c r="U106" t="n">
-        <v>1</v>
-      </c>
-      <c r="V106" t="n">
-        <v>1</v>
-      </c>
-      <c r="W106" t="n">
-        <v>1</v>
-      </c>
       <c r="Y106" t="n">
         <v>1</v>
       </c>
       <c r="Z106" t="n">
         <v>1</v>
       </c>
-      <c r="AB106" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC106" t="n">
-        <v>1</v>
-      </c>
       <c r="AD106" t="n">
         <v>1</v>
       </c>
-      <c r="AE106" t="n">
-        <v>1</v>
-      </c>
       <c r="AF106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG106" t="inlineStr">
         <is>
@@ -8742,7 +8694,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Principio de Arquímedes: empuje</t>
+          <t>Primera ley de Newton: inercia</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8751,52 +8703,82 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D107" t="n">
+        <v>10</v>
+      </c>
+      <c r="E107" t="n">
         <v>9</v>
       </c>
       <c r="F107" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G107" t="n">
         <v>6</v>
       </c>
       <c r="H107" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I107" t="n">
         <v>8</v>
       </c>
       <c r="J107" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K107" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L107" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="M107" t="n">
         <v>7</v>
       </c>
+      <c r="N107" t="n">
+        <v>1</v>
+      </c>
       <c r="O107" t="n">
         <v>1</v>
       </c>
+      <c r="P107" t="n">
+        <v>1</v>
+      </c>
       <c r="R107" t="n">
         <v>1</v>
       </c>
+      <c r="S107" t="n">
+        <v>1</v>
+      </c>
+      <c r="U107" t="n">
+        <v>1</v>
+      </c>
+      <c r="V107" t="n">
+        <v>1</v>
+      </c>
+      <c r="W107" t="n">
+        <v>1</v>
+      </c>
       <c r="Y107" t="n">
         <v>1</v>
       </c>
       <c r="Z107" t="n">
         <v>1</v>
       </c>
+      <c r="AB107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>1</v>
+      </c>
       <c r="AD107" t="n">
         <v>1</v>
       </c>
+      <c r="AE107" t="n">
+        <v>1</v>
+      </c>
       <c r="AF107" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
@@ -8812,7 +8794,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Hidrodinámica: continuidad y Bernoulli</t>
+          <t>Principio de Arquímedes: empuje</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8826,16 +8808,43 @@
       <c r="D108" t="n">
         <v>9</v>
       </c>
+      <c r="F108" t="n">
+        <v>8</v>
+      </c>
+      <c r="G108" t="n">
+        <v>6</v>
+      </c>
       <c r="H108" t="n">
+        <v>5</v>
+      </c>
+      <c r="I108" t="n">
+        <v>8</v>
+      </c>
+      <c r="J108" t="n">
         <v>7</v>
       </c>
       <c r="K108" t="n">
-        <v>5</v>
-      </c>
-      <c r="X108" t="n">
+        <v>7</v>
+      </c>
+      <c r="L108" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M108" t="n">
+        <v>7</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1</v>
+      </c>
+      <c r="R108" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y108" t="n">
         <v>1</v>
       </c>
       <c r="Z108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD108" t="n">
         <v>1</v>
       </c>
       <c r="AF108" t="n">
@@ -8855,7 +8864,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Principio de Pascal</t>
+          <t>Hidrodinámica: continuidad y Bernoulli</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8869,23 +8878,20 @@
       <c r="D109" t="n">
         <v>9</v>
       </c>
-      <c r="F109" t="n">
-        <v>8</v>
+      <c r="H109" t="n">
+        <v>7</v>
       </c>
       <c r="K109" t="n">
-        <v>7</v>
-      </c>
-      <c r="M109" t="n">
-        <v>7</v>
-      </c>
-      <c r="O109" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD109" t="n">
+        <v>5</v>
+      </c>
+      <c r="X109" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z109" t="n">
         <v>1</v>
       </c>
       <c r="AF109" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG109" t="inlineStr">
         <is>
@@ -8894,14 +8900,14 @@
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Rapidez y velocidad</t>
+          <t>Principio de Pascal</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8910,7 +8916,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D110" t="n">
         <v>9</v>
@@ -8918,62 +8924,20 @@
       <c r="F110" t="n">
         <v>8</v>
       </c>
-      <c r="G110" t="n">
-        <v>6</v>
-      </c>
-      <c r="H110" t="n">
-        <v>2</v>
-      </c>
-      <c r="I110" t="n">
-        <v>8</v>
-      </c>
-      <c r="J110" t="n">
-        <v>4.5</v>
-      </c>
       <c r="K110" t="n">
-        <v>2</v>
-      </c>
-      <c r="L110" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="M110" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O110" t="n">
         <v>1</v>
       </c>
-      <c r="P110" t="n">
-        <v>1</v>
-      </c>
-      <c r="R110" t="n">
-        <v>1</v>
-      </c>
-      <c r="U110" t="n">
-        <v>1</v>
-      </c>
-      <c r="W110" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y110" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC110" t="n">
-        <v>1</v>
-      </c>
       <c r="AD110" t="n">
         <v>1</v>
       </c>
-      <c r="AE110" t="n">
-        <v>1</v>
-      </c>
       <c r="AF110" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG110" t="inlineStr">
         <is>
@@ -8982,14 +8946,14 @@
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Reflexión de la luz</t>
+          <t>Rapidez y velocidad</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8998,37 +8962,34 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
-        <v>10</v>
-      </c>
-      <c r="E111" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F111" t="n">
         <v>8</v>
       </c>
       <c r="G111" t="n">
+        <v>6</v>
+      </c>
+      <c r="H111" t="n">
         <v>2</v>
       </c>
-      <c r="H111" t="n">
-        <v>3</v>
-      </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J111" t="n">
         <v>4.5</v>
       </c>
       <c r="K111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L111" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="M111" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O111" t="n">
         <v>1</v>
@@ -9036,15 +8997,12 @@
       <c r="P111" t="n">
         <v>1</v>
       </c>
-      <c r="T111" t="n">
+      <c r="R111" t="n">
         <v>1</v>
       </c>
       <c r="U111" t="n">
         <v>1</v>
       </c>
-      <c r="V111" t="n">
-        <v>1</v>
-      </c>
       <c r="W111" t="n">
         <v>1</v>
       </c>
@@ -9057,6 +9015,9 @@
       <c r="AB111" t="n">
         <v>1</v>
       </c>
+      <c r="AC111" t="n">
+        <v>1</v>
+      </c>
       <c r="AD111" t="n">
         <v>1</v>
       </c>
@@ -9064,7 +9025,7 @@
         <v>1</v>
       </c>
       <c r="AF111" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG111" t="inlineStr">
         <is>
@@ -9080,7 +9041,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Refracción de la luz</t>
+          <t>Reflexión de la luz</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9089,7 +9050,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D112" t="n">
         <v>10</v>
@@ -9101,13 +9062,13 @@
         <v>8</v>
       </c>
       <c r="G112" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H112" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I112" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J112" t="n">
         <v>4.5</v>
@@ -9116,10 +9077,10 @@
         <v>3</v>
       </c>
       <c r="L112" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M112" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O112" t="n">
         <v>1</v>
@@ -9127,9 +9088,6 @@
       <c r="P112" t="n">
         <v>1</v>
       </c>
-      <c r="S112" t="n">
-        <v>1</v>
-      </c>
       <c r="T112" t="n">
         <v>1</v>
       </c>
@@ -9151,9 +9109,6 @@
       <c r="AB112" t="n">
         <v>1</v>
       </c>
-      <c r="AC112" t="n">
-        <v>1</v>
-      </c>
       <c r="AD112" t="n">
         <v>1</v>
       </c>
@@ -9161,7 +9116,7 @@
         <v>1</v>
       </c>
       <c r="AF112" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
@@ -9177,7 +9132,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Resistencia equivalente</t>
+          <t>Refracción de la luz</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9186,32 +9141,56 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D113" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="E113" t="n">
+        <v>4</v>
       </c>
       <c r="F113" t="n">
         <v>8</v>
       </c>
       <c r="G113" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H113" t="n">
+        <v>5</v>
+      </c>
+      <c r="I113" t="n">
+        <v>6</v>
       </c>
       <c r="J113" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K113" t="n">
+        <v>3</v>
       </c>
       <c r="L113" t="n">
         <v>7.5</v>
       </c>
+      <c r="M113" t="n">
+        <v>4.5</v>
+      </c>
       <c r="O113" t="n">
         <v>1</v>
       </c>
       <c r="P113" t="n">
         <v>1</v>
       </c>
+      <c r="S113" t="n">
+        <v>1</v>
+      </c>
+      <c r="T113" t="n">
+        <v>1</v>
+      </c>
       <c r="U113" t="n">
         <v>1</v>
       </c>
+      <c r="V113" t="n">
+        <v>1</v>
+      </c>
       <c r="W113" t="n">
         <v>1</v>
       </c>
@@ -9221,14 +9200,20 @@
       <c r="Z113" t="n">
         <v>1</v>
       </c>
+      <c r="AB113" t="n">
+        <v>1</v>
+      </c>
       <c r="AC113" t="n">
         <v>1</v>
       </c>
       <c r="AD113" t="n">
         <v>1</v>
       </c>
+      <c r="AE113" t="n">
+        <v>1</v>
+      </c>
       <c r="AF113" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG113" t="inlineStr">
         <is>
@@ -9244,7 +9229,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Segunda ley de Newton</t>
+          <t>Resistencia equivalente</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9253,85 +9238,49 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D114" t="n">
-        <v>10</v>
-      </c>
-      <c r="E114" t="n">
+        <v>11</v>
+      </c>
+      <c r="F114" t="n">
+        <v>8</v>
+      </c>
+      <c r="G114" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J114" t="n">
+        <v>7</v>
+      </c>
+      <c r="L114" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O114" t="n">
+        <v>1</v>
+      </c>
+      <c r="P114" t="n">
+        <v>1</v>
+      </c>
+      <c r="U114" t="n">
+        <v>1</v>
+      </c>
+      <c r="W114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF114" t="n">
         <v>6</v>
-      </c>
-      <c r="F114" t="n">
-        <v>5</v>
-      </c>
-      <c r="G114" t="n">
-        <v>6</v>
-      </c>
-      <c r="H114" t="n">
-        <v>7</v>
-      </c>
-      <c r="I114" t="n">
-        <v>8</v>
-      </c>
-      <c r="J114" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K114" t="n">
-        <v>4</v>
-      </c>
-      <c r="L114" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M114" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N114" t="n">
-        <v>1</v>
-      </c>
-      <c r="O114" t="n">
-        <v>1</v>
-      </c>
-      <c r="P114" t="n">
-        <v>1</v>
-      </c>
-      <c r="R114" t="n">
-        <v>1</v>
-      </c>
-      <c r="S114" t="n">
-        <v>1</v>
-      </c>
-      <c r="U114" t="n">
-        <v>1</v>
-      </c>
-      <c r="V114" t="n">
-        <v>1</v>
-      </c>
-      <c r="W114" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y114" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z114" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA114" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB114" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC114" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD114" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE114" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF114" t="n">
-        <v>5</v>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
@@ -9347,7 +9296,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sistema Internacional de Unidades</t>
+          <t>Segunda ley de Newton</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9361,8 +9310,11 @@
       <c r="D115" t="n">
         <v>10</v>
       </c>
+      <c r="E115" t="n">
+        <v>6</v>
+      </c>
       <c r="F115" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="G115" t="n">
         <v>6</v>
@@ -9370,30 +9322,36 @@
       <c r="H115" t="n">
         <v>7</v>
       </c>
+      <c r="I115" t="n">
+        <v>8</v>
+      </c>
       <c r="J115" t="n">
         <v>2.5</v>
       </c>
       <c r="K115" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L115" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="M115" t="n">
         <v>2.5</v>
       </c>
+      <c r="N115" t="n">
+        <v>1</v>
+      </c>
       <c r="O115" t="n">
         <v>1</v>
       </c>
       <c r="P115" t="n">
         <v>1</v>
       </c>
+      <c r="R115" t="n">
+        <v>1</v>
+      </c>
       <c r="S115" t="n">
         <v>1</v>
       </c>
-      <c r="T115" t="n">
-        <v>1</v>
-      </c>
       <c r="U115" t="n">
         <v>1</v>
       </c>
@@ -9409,10 +9367,19 @@
       <c r="Z115" t="n">
         <v>1</v>
       </c>
+      <c r="AA115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>1</v>
+      </c>
       <c r="AC115" t="n">
         <v>1</v>
       </c>
       <c r="AD115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE115" t="n">
         <v>1</v>
       </c>
       <c r="AF115" t="n">
@@ -9432,7 +9399,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>El sonido como onda mecánica</t>
+          <t>Sistema Internacional de Unidades</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9441,34 +9408,28 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D116" t="n">
-        <v>11</v>
-      </c>
-      <c r="E116" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F116" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="G116" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H116" t="n">
-        <v>2</v>
-      </c>
-      <c r="I116" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J116" t="n">
         <v>2.5</v>
       </c>
       <c r="K116" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L116" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M116" t="n">
         <v>2.5</v>
@@ -9479,7 +9440,10 @@
       <c r="P116" t="n">
         <v>1</v>
       </c>
-      <c r="R116" t="n">
+      <c r="S116" t="n">
+        <v>1</v>
+      </c>
+      <c r="T116" t="n">
         <v>1</v>
       </c>
       <c r="U116" t="n">
@@ -9491,32 +9455,20 @@
       <c r="W116" t="n">
         <v>1</v>
       </c>
-      <c r="X116" t="n">
-        <v>1</v>
-      </c>
       <c r="Y116" t="n">
         <v>1</v>
       </c>
       <c r="Z116" t="n">
         <v>1</v>
       </c>
-      <c r="AA116" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB116" t="n">
-        <v>1</v>
-      </c>
       <c r="AC116" t="n">
         <v>1</v>
       </c>
       <c r="AD116" t="n">
         <v>1</v>
       </c>
-      <c r="AE116" t="n">
-        <v>1</v>
-      </c>
       <c r="AF116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG116" t="inlineStr">
         <is>
@@ -9532,7 +9484,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Suma de vectores y componentes rectangulares</t>
+          <t>El sonido como onda mecánica</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9541,29 +9493,38 @@
         </is>
       </c>
       <c r="C117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D117" t="n">
+        <v>11</v>
+      </c>
+      <c r="E117" t="n">
+        <v>8</v>
+      </c>
+      <c r="F117" t="n">
         <v>5</v>
       </c>
-      <c r="D117" t="n">
-        <v>10</v>
-      </c>
-      <c r="F117" t="n">
-        <v>10.5</v>
-      </c>
       <c r="G117" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H117" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I117" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J117" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K117" t="n">
+        <v>3</v>
       </c>
       <c r="L117" t="n">
         <v>9.5</v>
       </c>
+      <c r="M117" t="n">
+        <v>2.5</v>
+      </c>
       <c r="O117" t="n">
         <v>1</v>
       </c>
@@ -9576,9 +9537,15 @@
       <c r="U117" t="n">
         <v>1</v>
       </c>
+      <c r="V117" t="n">
+        <v>1</v>
+      </c>
       <c r="W117" t="n">
         <v>1</v>
       </c>
+      <c r="X117" t="n">
+        <v>1</v>
+      </c>
       <c r="Y117" t="n">
         <v>1</v>
       </c>
@@ -9601,7 +9568,7 @@
         <v>1</v>
       </c>
       <c r="AF117" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG117" t="inlineStr">
         <is>
@@ -9617,7 +9584,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Temperatura y escalas termométricas</t>
+          <t>Suma de vectores y componentes rectangulares</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9626,42 +9593,39 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D118" t="n">
         <v>10</v>
       </c>
       <c r="F118" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="G118" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H118" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I118" t="n">
+        <v>8</v>
+      </c>
+      <c r="J118" t="n">
+        <v>7</v>
+      </c>
+      <c r="L118" t="n">
         <v>9.5</v>
       </c>
-      <c r="J118" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L118" t="n">
-        <v>4</v>
-      </c>
-      <c r="M118" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O118" t="n">
         <v>1</v>
       </c>
+      <c r="P118" t="n">
+        <v>1</v>
+      </c>
       <c r="R118" t="n">
         <v>1</v>
       </c>
-      <c r="S118" t="n">
-        <v>1</v>
-      </c>
-      <c r="V118" t="n">
+      <c r="U118" t="n">
         <v>1</v>
       </c>
       <c r="W118" t="n">
@@ -9673,6 +9637,15 @@
       <c r="Z118" t="n">
         <v>1</v>
       </c>
+      <c r="AA118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1</v>
+      </c>
       <c r="AD118" t="n">
         <v>1</v>
       </c>
@@ -9680,7 +9653,7 @@
         <v>1</v>
       </c>
       <c r="AF118" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AG118" t="inlineStr">
         <is>
@@ -9696,7 +9669,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Tensión superficial y capilaridad</t>
+          <t>Temperatura y escalas termométricas</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9705,13 +9678,28 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D119" t="n">
         <v>10</v>
       </c>
       <c r="F119" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2</v>
+      </c>
+      <c r="H119" t="n">
+        <v>2</v>
+      </c>
+      <c r="I119" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J119" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L119" t="n">
+        <v>4</v>
       </c>
       <c r="M119" t="n">
         <v>2.5</v>
@@ -9719,8 +9707,32 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
+      <c r="R119" t="n">
+        <v>1</v>
+      </c>
+      <c r="S119" t="n">
+        <v>1</v>
+      </c>
+      <c r="V119" t="n">
+        <v>1</v>
+      </c>
+      <c r="W119" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>1</v>
+      </c>
       <c r="AF119" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AG119" t="inlineStr">
         <is>
@@ -9736,7 +9748,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Tercera ley de Newton: acción y reacción</t>
+          <t>Tensión superficial y capilaridad</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9745,76 +9757,22 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D120" t="n">
         <v>10</v>
       </c>
-      <c r="E120" t="n">
-        <v>9</v>
-      </c>
       <c r="F120" t="n">
         <v>10.5</v>
       </c>
-      <c r="G120" t="n">
+      <c r="M120" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF120" t="n">
         <v>6</v>
-      </c>
-      <c r="H120" t="n">
-        <v>4</v>
-      </c>
-      <c r="I120" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K120" t="n">
-        <v>4</v>
-      </c>
-      <c r="L120" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M120" t="n">
-        <v>7</v>
-      </c>
-      <c r="N120" t="n">
-        <v>1</v>
-      </c>
-      <c r="O120" t="n">
-        <v>1</v>
-      </c>
-      <c r="P120" t="n">
-        <v>1</v>
-      </c>
-      <c r="R120" t="n">
-        <v>1</v>
-      </c>
-      <c r="U120" t="n">
-        <v>1</v>
-      </c>
-      <c r="V120" t="n">
-        <v>1</v>
-      </c>
-      <c r="W120" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y120" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z120" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB120" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC120" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD120" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE120" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF120" t="n">
-        <v>5</v>
       </c>
       <c r="AG120" t="inlineStr">
         <is>
@@ -9830,7 +9788,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Características del sonido: tono, intensidad y eco</t>
+          <t>Tercera ley de Newton: acción y reacción</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9839,44 +9797,59 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D121" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="E121" t="n">
+        <v>9</v>
       </c>
       <c r="F121" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="G121" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H121" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I121" t="n">
-        <v>2</v>
-      </c>
-      <c r="J121" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="K121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L121" t="n">
         <v>9.5</v>
       </c>
       <c r="M121" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="N121" t="n">
+        <v>1</v>
       </c>
       <c r="O121" t="n">
         <v>1</v>
       </c>
+      <c r="P121" t="n">
+        <v>1</v>
+      </c>
+      <c r="R121" t="n">
+        <v>1</v>
+      </c>
       <c r="U121" t="n">
         <v>1</v>
       </c>
+      <c r="V121" t="n">
+        <v>1</v>
+      </c>
       <c r="W121" t="n">
         <v>1</v>
       </c>
+      <c r="Y121" t="n">
+        <v>1</v>
+      </c>
       <c r="Z121" t="n">
         <v>1</v>
       </c>
@@ -9893,7 +9866,7 @@
         <v>1</v>
       </c>
       <c r="AF121" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG121" t="inlineStr">
         <is>
@@ -9909,7 +9882,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Torque o momento de fuerza</t>
+          <t>Características del sonido: tono, intensidad y eco</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9918,47 +9891,53 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D122" t="n">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="F122" t="n">
+        <v>5</v>
       </c>
       <c r="G122" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H122" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I122" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="J122" t="n">
+        <v>2.5</v>
       </c>
       <c r="K122" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L122" t="n">
         <v>9.5</v>
       </c>
       <c r="M122" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P122" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O122" t="n">
         <v>1</v>
       </c>
       <c r="U122" t="n">
         <v>1</v>
       </c>
-      <c r="Y122" t="n">
+      <c r="W122" t="n">
         <v>1</v>
       </c>
       <c r="Z122" t="n">
         <v>1</v>
       </c>
-      <c r="AA122" t="n">
-        <v>1</v>
-      </c>
       <c r="AB122" t="n">
         <v>1</v>
       </c>
+      <c r="AC122" t="n">
+        <v>1</v>
+      </c>
       <c r="AD122" t="n">
         <v>1</v>
       </c>
@@ -9966,7 +9945,7 @@
         <v>1</v>
       </c>
       <c r="AF122" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
@@ -9982,7 +9961,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Trabajo mecánico</t>
+          <t>Torque o momento de fuerza</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9991,62 +9970,47 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D123" t="n">
         <v>9</v>
       </c>
-      <c r="F123" t="n">
-        <v>8</v>
-      </c>
       <c r="G123" t="n">
         <v>6</v>
       </c>
+      <c r="H123" t="n">
+        <v>5</v>
+      </c>
       <c r="I123" t="n">
-        <v>8</v>
-      </c>
-      <c r="J123" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K123" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L123" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="M123" t="n">
-        <v>7</v>
-      </c>
-      <c r="O123" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="P123" t="n">
         <v>1</v>
       </c>
-      <c r="R123" t="n">
-        <v>1</v>
-      </c>
       <c r="U123" t="n">
         <v>1</v>
       </c>
-      <c r="V123" t="n">
-        <v>1</v>
-      </c>
-      <c r="W123" t="n">
-        <v>1</v>
-      </c>
       <c r="Y123" t="n">
         <v>1</v>
       </c>
       <c r="Z123" t="n">
         <v>1</v>
       </c>
+      <c r="AA123" t="n">
+        <v>1</v>
+      </c>
       <c r="AB123" t="n">
         <v>1</v>
       </c>
-      <c r="AC123" t="n">
-        <v>1</v>
-      </c>
       <c r="AD123" t="n">
         <v>1</v>
       </c>
@@ -10054,7 +10018,7 @@
         <v>1</v>
       </c>
       <c r="AF123" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG123" t="inlineStr">
         <is>
@@ -10070,7 +10034,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Transformaciones de la energía</t>
+          <t>Trabajo mecánico</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10079,37 +10043,31 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D124" t="n">
         <v>9</v>
       </c>
-      <c r="E124" t="n">
-        <v>5</v>
-      </c>
       <c r="F124" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G124" t="n">
         <v>6</v>
       </c>
-      <c r="H124" t="n">
-        <v>2</v>
-      </c>
       <c r="I124" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J124" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K124" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L124" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="M124" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O124" t="n">
         <v>1</v>
@@ -10120,9 +10078,6 @@
       <c r="R124" t="n">
         <v>1</v>
       </c>
-      <c r="S124" t="n">
-        <v>1</v>
-      </c>
       <c r="U124" t="n">
         <v>1</v>
       </c>
@@ -10151,7 +10106,7 @@
         <v>1</v>
       </c>
       <c r="AF124" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG124" t="inlineStr">
         <is>
@@ -10167,22 +10122,61 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Cuantización de la energía</t>
+          <t>Transformaciones de la energía</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D125" t="n">
         <v>9</v>
       </c>
+      <c r="E125" t="n">
+        <v>5</v>
+      </c>
+      <c r="F125" t="n">
+        <v>5</v>
+      </c>
+      <c r="G125" t="n">
+        <v>6</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2</v>
+      </c>
+      <c r="I125" t="n">
+        <v>5</v>
+      </c>
+      <c r="J125" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K125" t="n">
+        <v>2</v>
+      </c>
+      <c r="L125" t="n">
+        <v>4.5</v>
+      </c>
       <c r="M125" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1</v>
+      </c>
+      <c r="P125" t="n">
+        <v>1</v>
+      </c>
+      <c r="R125" t="n">
+        <v>1</v>
+      </c>
+      <c r="S125" t="n">
+        <v>1</v>
+      </c>
+      <c r="U125" t="n">
+        <v>1</v>
       </c>
       <c r="V125" t="n">
         <v>1</v>
@@ -10190,18 +10184,12 @@
       <c r="W125" t="n">
         <v>1</v>
       </c>
-      <c r="X125" t="n">
-        <v>1</v>
-      </c>
       <c r="Y125" t="n">
         <v>1</v>
       </c>
       <c r="Z125" t="n">
         <v>1</v>
       </c>
-      <c r="AA125" t="n">
-        <v>1</v>
-      </c>
       <c r="AB125" t="n">
         <v>1</v>
       </c>
@@ -10215,23 +10203,23 @@
         <v>1</v>
       </c>
       <c r="AF125" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Difracción de ondas y de la luz</t>
+          <t>Cuantización de la energía</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10240,26 +10228,23 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D126" t="n">
-        <v>10</v>
-      </c>
-      <c r="F126" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="M126" t="n">
         <v>9.5</v>
       </c>
-      <c r="O126" t="n">
-        <v>1</v>
-      </c>
       <c r="V126" t="n">
         <v>1</v>
       </c>
       <c r="W126" t="n">
         <v>1</v>
       </c>
+      <c r="X126" t="n">
+        <v>1</v>
+      </c>
       <c r="Y126" t="n">
         <v>1</v>
       </c>
@@ -10282,23 +10267,23 @@
         <v>1</v>
       </c>
       <c r="AF126" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Dualidad onda-partícula</t>
+          <t>Difracción de ondas y de la luz</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10327,9 +10312,6 @@
       <c r="W127" t="n">
         <v>1</v>
       </c>
-      <c r="X127" t="n">
-        <v>1</v>
-      </c>
       <c r="Y127" t="n">
         <v>1</v>
       </c>
@@ -10368,7 +10350,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Fotón y efecto fotoeléctrico</t>
+          <t>Dualidad onda-partícula</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10438,7 +10420,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Interferencia de la luz</t>
+          <t>Fotón y efecto fotoeléctrico</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10467,6 +10449,9 @@
       <c r="W129" t="n">
         <v>1</v>
       </c>
+      <c r="X129" t="n">
+        <v>1</v>
+      </c>
       <c r="Y129" t="n">
         <v>1</v>
       </c>
@@ -10505,29 +10490,62 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Observación astronómica en distintas longitudes de onda</t>
+          <t>Interferencia de la luz</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D130" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="F130" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M130" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O130" t="n">
+        <v>1</v>
+      </c>
+      <c r="V130" t="n">
+        <v>1</v>
+      </c>
+      <c r="W130" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>1</v>
       </c>
       <c r="Z130" t="n">
         <v>1</v>
       </c>
+      <c r="AA130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>1</v>
+      </c>
       <c r="AF130" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH130" t="inlineStr">
@@ -10539,7 +10557,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Capacitancia y condensadores</t>
+          <t>Observación astronómica en distintas longitudes de onda</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10548,50 +10566,32 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D131" t="n">
-        <v>9</v>
-      </c>
-      <c r="F131" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="O131" t="n">
-        <v>1</v>
-      </c>
-      <c r="X131" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD131" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z131" t="n">
         <v>1</v>
       </c>
       <c r="AF131" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Defecto de masa y energía de enlace nuclear</t>
+          <t>Capacitancia y condensadores</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10600,55 +10600,34 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D132" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F132" t="n">
-        <v>8</v>
-      </c>
-      <c r="J132" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O132" t="n">
+        <v>1</v>
+      </c>
+      <c r="X132" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF132" t="n">
         <v>9</v>
-      </c>
-      <c r="L132" t="n">
-        <v>11</v>
-      </c>
-      <c r="M132" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O132" t="n">
-        <v>1</v>
-      </c>
-      <c r="S132" t="n">
-        <v>1</v>
-      </c>
-      <c r="U132" t="n">
-        <v>1</v>
-      </c>
-      <c r="V132" t="n">
-        <v>1</v>
-      </c>
-      <c r="W132" t="n">
-        <v>1</v>
-      </c>
-      <c r="X132" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y132" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF132" t="n">
-        <v>11</v>
       </c>
       <c r="AG132" t="inlineStr">
         <is>
@@ -10664,7 +10643,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Fuerza magnética sobre cargas en movimiento</t>
+          <t>Defecto de masa y energía de enlace nuclear</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10679,20 +10658,35 @@
         <v>11</v>
       </c>
       <c r="F133" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="J133" t="n">
+        <v>9</v>
       </c>
       <c r="L133" t="n">
         <v>11</v>
       </c>
+      <c r="M133" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O133" t="n">
         <v>1</v>
       </c>
+      <c r="S133" t="n">
+        <v>1</v>
+      </c>
       <c r="U133" t="n">
         <v>1</v>
       </c>
+      <c r="V133" t="n">
+        <v>1</v>
+      </c>
       <c r="W133" t="n">
         <v>1</v>
       </c>
+      <c r="X133" t="n">
+        <v>1</v>
+      </c>
       <c r="Y133" t="n">
         <v>1</v>
       </c>
@@ -10702,16 +10696,7 @@
       <c r="AA133" t="n">
         <v>1</v>
       </c>
-      <c r="AB133" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>1</v>
-      </c>
       <c r="AD133" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE133" t="n">
         <v>1</v>
       </c>
       <c r="AF133" t="n">
@@ -10731,7 +10716,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Fuerza electromotriz y leyes de Kirchhoff</t>
+          <t>Fuerza magnética sobre cargas en movimiento</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10749,7 +10734,7 @@
         <v>10.5</v>
       </c>
       <c r="L134" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="O134" t="n">
         <v>1</v>
@@ -10767,6 +10752,9 @@
         <v>1</v>
       </c>
       <c r="AA134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB134" t="n">
         <v>1</v>
       </c>
       <c r="AC134" t="n">
@@ -10795,7 +10783,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Modelo estándar de partículas</t>
+          <t>Fuerza electromotriz y leyes de Kirchhoff</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10804,21 +10792,27 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D135" t="n">
-        <v>10</v>
-      </c>
-      <c r="M135" t="n">
+        <v>11</v>
+      </c>
+      <c r="F135" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L135" t="n">
         <v>9.5</v>
       </c>
-      <c r="V135" t="n">
+      <c r="O135" t="n">
+        <v>1</v>
+      </c>
+      <c r="U135" t="n">
         <v>1</v>
       </c>
       <c r="W135" t="n">
         <v>1</v>
       </c>
-      <c r="X135" t="n">
+      <c r="Y135" t="n">
         <v>1</v>
       </c>
       <c r="Z135" t="n">
@@ -10833,6 +10827,12 @@
       <c r="AD135" t="n">
         <v>1</v>
       </c>
+      <c r="AE135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>11</v>
+      </c>
       <c r="AG135" t="inlineStr">
         <is>
           <t>solo_especializacion</t>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="AH135" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
